--- a/data/chapter2/FRED/subsets/species.xlsx
+++ b/data/chapter2/FRED/subsets/species.xlsx
@@ -4828,10 +4828,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_1" connectionId="2" xr16:uid="{EAA821A2-C94B-4FC7-90E5-1E8F05F04F55}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
   <queryTableRefresh nextId="3">

--- a/data/chapter2/FRED/subsets/species.xlsx
+++ b/data/chapter2/FRED/subsets/species.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://westernsydneyedu-my.sharepoint.com/personal/90963425_westernsydney_edu_au/Documents/PhD/code/data/chapter2/FRED/subsets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="156" documentId="8_{81FDA0CF-33C4-43D2-B8CA-CC5F96143B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F734AB0-0C45-4A3B-B771-2EF4CB6A3323}"/>
+  <xr:revisionPtr revIDLastSave="170" documentId="8_{81FDA0CF-33C4-43D2-B8CA-CC5F96143B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C16EE58C-132F-4521-95C6-CD00E34A73B7}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{A5444074-DC77-415C-A9E2-2BBA8270EAFC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{A5444074-DC77-415C-A9E2-2BBA8270EAFC}"/>
   </bookViews>
   <sheets>
     <sheet name="FRED4" sheetId="8" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3252" uniqueCount="1058">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3276" uniqueCount="1058">
   <si>
     <t>F00645</t>
   </si>
@@ -14835,7 +14835,9 @@
       <c r="B27" s="1" t="s">
         <v>947</v>
       </c>
-      <c r="C27" s="1"/>
+      <c r="C27" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
@@ -14844,7 +14846,9 @@
       <c r="B28" s="1" t="s">
         <v>944</v>
       </c>
-      <c r="C28" s="1"/>
+      <c r="C28" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
@@ -14853,7 +14857,9 @@
       <c r="B29" s="1" t="s">
         <v>945</v>
       </c>
-      <c r="C29" s="1"/>
+      <c r="C29" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
@@ -15016,7 +15022,9 @@
       <c r="B44" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C44" s="1"/>
+      <c r="C44" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
@@ -15025,7 +15033,9 @@
       <c r="B45" s="1" t="s">
         <v>945</v>
       </c>
-      <c r="C45" s="1"/>
+      <c r="C45" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
@@ -15034,7 +15044,9 @@
       <c r="B46" s="1" t="s">
         <v>945</v>
       </c>
-      <c r="C46" s="1"/>
+      <c r="C46" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
@@ -15043,7 +15055,9 @@
       <c r="B47" s="1" t="s">
         <v>947</v>
       </c>
-      <c r="C47" s="1"/>
+      <c r="C47" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
@@ -15052,7 +15066,9 @@
       <c r="B48" s="1" t="s">
         <v>951</v>
       </c>
-      <c r="C48" s="1"/>
+      <c r="C48" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
@@ -15061,7 +15077,9 @@
       <c r="B49" s="1" t="s">
         <v>951</v>
       </c>
-      <c r="C49" s="1"/>
+      <c r="C49" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
@@ -15634,7 +15652,9 @@
       <c r="B110" s="1" t="s">
         <v>951</v>
       </c>
-      <c r="C110" s="1"/>
+      <c r="C110" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
@@ -15643,7 +15663,9 @@
       <c r="B111" s="1" t="s">
         <v>951</v>
       </c>
-      <c r="C111" s="1"/>
+      <c r="C111" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
@@ -15652,7 +15674,9 @@
       <c r="B112" s="1" t="s">
         <v>947</v>
       </c>
-      <c r="C112" s="1"/>
+      <c r="C112" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
@@ -15661,7 +15685,9 @@
       <c r="B113" s="1" t="s">
         <v>951</v>
       </c>
-      <c r="C113" s="1"/>
+      <c r="C113" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
@@ -15670,7 +15696,9 @@
       <c r="B114" s="1" t="s">
         <v>947</v>
       </c>
-      <c r="C114" s="1"/>
+      <c r="C114" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
@@ -15679,7 +15707,9 @@
       <c r="B115" s="1" t="s">
         <v>951</v>
       </c>
-      <c r="C115" s="1"/>
+      <c r="C115" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
@@ -15688,7 +15718,9 @@
       <c r="B116" s="1" t="s">
         <v>947</v>
       </c>
-      <c r="C116" s="1"/>
+      <c r="C116" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
@@ -15697,7 +15729,9 @@
       <c r="B117" s="1" t="s">
         <v>947</v>
       </c>
-      <c r="C117" s="1"/>
+      <c r="C117" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
@@ -15706,7 +15740,9 @@
       <c r="B118" s="1" t="s">
         <v>951</v>
       </c>
-      <c r="C118" s="1"/>
+      <c r="C118" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
@@ -15715,7 +15751,9 @@
       <c r="B119" s="1" t="s">
         <v>951</v>
       </c>
-      <c r="C119" s="1"/>
+      <c r="C119" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
@@ -15742,7 +15780,9 @@
       <c r="B122" s="1" t="s">
         <v>951</v>
       </c>
-      <c r="C122" s="1"/>
+      <c r="C122" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
@@ -15751,7 +15791,9 @@
       <c r="B123" s="1" t="s">
         <v>951</v>
       </c>
-      <c r="C123" s="1"/>
+      <c r="C123" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
@@ -15760,7 +15802,9 @@
       <c r="B124" s="1" t="s">
         <v>951</v>
       </c>
-      <c r="C124" s="1"/>
+      <c r="C124" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" s="1" t="s">
@@ -15769,7 +15813,9 @@
       <c r="B125" s="1" t="s">
         <v>951</v>
       </c>
-      <c r="C125" s="1"/>
+      <c r="C125" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" s="1" t="s">
@@ -15778,7 +15824,9 @@
       <c r="B126" s="1" t="s">
         <v>947</v>
       </c>
-      <c r="C126" s="1"/>
+      <c r="C126" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A1048576">

--- a/data/chapter2/FRED/subsets/species.xlsx
+++ b/data/chapter2/FRED/subsets/species.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://westernsydneyedu-my.sharepoint.com/personal/90963425_westernsydney_edu_au/Documents/PhD/code/data/chapter2/FRED/subsets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="170" documentId="8_{81FDA0CF-33C4-43D2-B8CA-CC5F96143B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C16EE58C-132F-4521-95C6-CD00E34A73B7}"/>
+  <xr:revisionPtr revIDLastSave="188" documentId="8_{81FDA0CF-33C4-43D2-B8CA-CC5F96143B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B902BB1-4096-4F72-A0E2-5ACCFECFFBCF}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{A5444074-DC77-415C-A9E2-2BBA8270EAFC}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3276" uniqueCount="1058">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3297" uniqueCount="1058">
   <si>
     <t>F00645</t>
   </si>
@@ -15088,7 +15088,9 @@
       <c r="B50" s="1" t="s">
         <v>973</v>
       </c>
-      <c r="C50" s="1"/>
+      <c r="C50" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
@@ -15097,7 +15099,9 @@
       <c r="B51" s="1" t="s">
         <v>1043</v>
       </c>
-      <c r="C51" s="1"/>
+      <c r="C51" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
@@ -15106,7 +15110,9 @@
       <c r="B52" s="1" t="s">
         <v>951</v>
       </c>
-      <c r="C52" s="1"/>
+      <c r="C52" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
@@ -15115,7 +15121,9 @@
       <c r="B53" s="1" t="s">
         <v>945</v>
       </c>
-      <c r="C53" s="1"/>
+      <c r="C53" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
@@ -15124,7 +15132,9 @@
       <c r="B54" s="1" t="s">
         <v>945</v>
       </c>
-      <c r="C54" s="1"/>
+      <c r="C54" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
@@ -15133,7 +15143,9 @@
       <c r="B55" s="1" t="s">
         <v>951</v>
       </c>
-      <c r="C55" s="1"/>
+      <c r="C55" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
@@ -15142,7 +15154,9 @@
       <c r="B56" s="1" t="s">
         <v>951</v>
       </c>
-      <c r="C56" s="1"/>
+      <c r="C56" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
@@ -15151,7 +15165,9 @@
       <c r="B57" s="1" t="s">
         <v>944</v>
       </c>
-      <c r="C57" s="1"/>
+      <c r="C57" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
@@ -15160,7 +15176,9 @@
       <c r="B58" s="1" t="s">
         <v>947</v>
       </c>
-      <c r="C58" s="1"/>
+      <c r="C58" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
@@ -15169,7 +15187,9 @@
       <c r="B59" s="1" t="s">
         <v>947</v>
       </c>
-      <c r="C59" s="1"/>
+      <c r="C59" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
@@ -15178,7 +15198,9 @@
       <c r="B60" s="1" t="s">
         <v>947</v>
       </c>
-      <c r="C60" s="1"/>
+      <c r="C60" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
@@ -15187,7 +15209,9 @@
       <c r="B61" s="1" t="s">
         <v>951</v>
       </c>
-      <c r="C61" s="1"/>
+      <c r="C61" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
@@ -15196,7 +15220,9 @@
       <c r="B62" s="1" t="s">
         <v>945</v>
       </c>
-      <c r="C62" s="1"/>
+      <c r="C62" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
@@ -15205,7 +15231,9 @@
       <c r="B63" s="1" t="s">
         <v>951</v>
       </c>
-      <c r="C63" s="1"/>
+      <c r="C63" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
@@ -15214,7 +15242,9 @@
       <c r="B64" s="1" t="s">
         <v>947</v>
       </c>
-      <c r="C64" s="1"/>
+      <c r="C64" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
@@ -15223,7 +15253,9 @@
       <c r="B65" s="1" t="s">
         <v>947</v>
       </c>
-      <c r="C65" s="1"/>
+      <c r="C65" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
@@ -15232,7 +15264,9 @@
       <c r="B66" s="1" t="s">
         <v>951</v>
       </c>
-      <c r="C66" s="1"/>
+      <c r="C66" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
@@ -15241,7 +15275,9 @@
       <c r="B67" s="1" t="s">
         <v>947</v>
       </c>
-      <c r="C67" s="1"/>
+      <c r="C67" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
@@ -15250,7 +15286,9 @@
       <c r="B68" s="1" t="s">
         <v>951</v>
       </c>
-      <c r="C68" s="1"/>
+      <c r="C68" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
@@ -15259,7 +15297,9 @@
       <c r="B69" s="1" t="s">
         <v>951</v>
       </c>
-      <c r="C69" s="1"/>
+      <c r="C69" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
@@ -15268,7 +15308,9 @@
       <c r="B70" s="1" t="s">
         <v>945</v>
       </c>
-      <c r="C70" s="1"/>
+      <c r="C70" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">

--- a/data/chapter2/FRED/subsets/species.xlsx
+++ b/data/chapter2/FRED/subsets/species.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://westernsydneyedu-my.sharepoint.com/personal/90963425_westernsydney_edu_au/Documents/PhD/code/data/chapter2/FRED/subsets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="188" documentId="8_{81FDA0CF-33C4-43D2-B8CA-CC5F96143B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B902BB1-4096-4F72-A0E2-5ACCFECFFBCF}"/>
+  <xr:revisionPtr revIDLastSave="228" documentId="8_{81FDA0CF-33C4-43D2-B8CA-CC5F96143B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A0F7066-243B-4F5A-A8C6-27417CE32066}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{A5444074-DC77-415C-A9E2-2BBA8270EAFC}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="FRED4" sheetId="8" r:id="rId1"/>
     <sheet name="FungalRoot" sheetId="9" r:id="rId2"/>
     <sheet name="Maherali 2016" sheetId="7" r:id="rId3"/>
+    <sheet name="combined" sheetId="10" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="ExternalData_1" localSheetId="0" hidden="1">FRED4!$A$1:$B$936</definedName>
@@ -54,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3297" uniqueCount="1058">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3326" uniqueCount="1057">
   <si>
     <t>F00645</t>
   </si>
@@ -2879,12 +2880,6 @@
     <t>Vitis vulpina</t>
   </si>
   <si>
-    <t>species</t>
-  </si>
-  <si>
-    <t>mycorrhiza type</t>
-  </si>
-  <si>
     <t>Carex tibetikobresia</t>
   </si>
   <si>
@@ -3228,6 +3223,9 @@
   </si>
   <si>
     <t>reconciled_state</t>
+  </si>
+  <si>
+    <t>mycorrhiza_type</t>
   </si>
 </sst>
 </file>
@@ -3881,8 +3879,8 @@
     <sortCondition ref="A1:A126"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{DB834698-488E-491D-9850-AB59BA2D8F59}" uniqueName="1" name="species" queryTableFieldId="1" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{593D5135-0567-42A3-9686-B4214CBDE6C3}" uniqueName="2" name="mycorrhiza type" queryTableFieldId="2" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{DB834698-488E-491D-9850-AB59BA2D8F59}" uniqueName="1" name="binominal" queryTableFieldId="1" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{593D5135-0567-42A3-9686-B4214CBDE6C3}" uniqueName="2" name="mycorrhiza_type" queryTableFieldId="2" dataDxfId="7"/>
     <tableColumn id="3" xr3:uid="{B6A120AA-0C31-42A9-939F-609ED18C193A}" uniqueName="3" name="reconciled_state" queryTableFieldId="3" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -4233,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
@@ -4332,7 +4330,7 @@
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
@@ -4354,7 +4352,7 @@
         <v>2</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
@@ -4398,7 +4396,7 @@
         <v>2</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
@@ -4409,7 +4407,7 @@
         <v>5</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
@@ -4420,7 +4418,7 @@
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
@@ -4431,7 +4429,7 @@
         <v>2</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
@@ -4442,7 +4440,7 @@
         <v>2</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
@@ -4453,7 +4451,7 @@
         <v>5</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
@@ -4464,7 +4462,7 @@
         <v>2</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
@@ -4475,7 +4473,7 @@
         <v>5</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
@@ -4497,7 +4495,7 @@
         <v>2</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
@@ -4508,7 +4506,7 @@
         <v>5</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
@@ -4519,7 +4517,7 @@
         <v>1</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
@@ -4541,7 +4539,7 @@
         <v>2</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
@@ -14544,21 +14542,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>941</v>
+        <v>7</v>
       </c>
       <c r="B1" t="s">
-        <v>942</v>
+        <v>1056</v>
       </c>
       <c r="C1" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2</v>
@@ -14566,10 +14564,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>2</v>
@@ -14577,10 +14575,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>2</v>
@@ -14588,10 +14586,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>2</v>
@@ -14599,10 +14597,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>2</v>
@@ -14610,10 +14608,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -14621,10 +14619,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -14632,10 +14630,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>2</v>
@@ -14643,10 +14641,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>2</v>
@@ -14654,10 +14652,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>4</v>
@@ -14665,10 +14663,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>4</v>
@@ -14676,10 +14674,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>4</v>
@@ -14687,10 +14685,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>4</v>
@@ -14698,10 +14696,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>4</v>
@@ -14709,10 +14707,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>4</v>
@@ -14720,10 +14718,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>2</v>
@@ -14731,10 +14729,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>2</v>
@@ -14742,10 +14740,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>2</v>
@@ -14753,10 +14751,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>2</v>
@@ -14764,10 +14762,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>2</v>
@@ -14775,10 +14773,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>2</v>
@@ -14786,10 +14784,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>2</v>
@@ -14797,10 +14795,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>2</v>
@@ -14808,10 +14806,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>2</v>
@@ -14819,10 +14817,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>2</v>
@@ -14830,10 +14828,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>2</v>
@@ -14841,10 +14839,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>4</v>
@@ -14852,10 +14850,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
+        <v>941</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>943</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>945</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>4</v>
@@ -14863,10 +14861,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>1</v>
@@ -14874,10 +14872,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>1</v>
@@ -14885,10 +14883,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>2</v>
@@ -14896,10 +14894,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>2</v>
@@ -14907,10 +14905,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>2</v>
@@ -14918,10 +14916,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>2</v>
@@ -14929,10 +14927,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>2</v>
@@ -14940,10 +14938,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>2</v>
@@ -14951,10 +14949,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>2</v>
@@ -14962,10 +14960,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>2</v>
@@ -14973,10 +14971,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>2</v>
@@ -14984,10 +14982,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>2</v>
@@ -14995,10 +14993,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>2</v>
@@ -15006,10 +15004,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>2</v>
@@ -15017,7 +15015,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>6</v>
@@ -15028,10 +15026,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>6</v>
@@ -15039,10 +15037,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>5</v>
@@ -15050,10 +15048,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>2</v>
@@ -15061,10 +15059,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>2</v>
@@ -15072,10 +15070,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>2</v>
@@ -15083,10 +15081,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
@@ -15094,10 +15092,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
@@ -15105,10 +15103,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>2</v>
@@ -15116,10 +15114,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>5</v>
@@ -15127,10 +15125,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>5</v>
@@ -15138,10 +15136,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>2</v>
@@ -15149,10 +15147,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
@@ -15160,10 +15158,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
@@ -15171,10 +15169,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>2</v>
@@ -15182,10 +15180,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>2</v>
@@ -15193,10 +15191,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>2</v>
@@ -15204,10 +15202,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>2</v>
@@ -15215,10 +15213,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>5</v>
@@ -15226,10 +15224,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>2</v>
@@ -15237,10 +15235,10 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>2</v>
@@ -15248,10 +15246,10 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>2</v>
@@ -15259,10 +15257,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>2</v>
@@ -15270,10 +15268,10 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>2</v>
@@ -15281,10 +15279,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>2</v>
@@ -15292,10 +15290,10 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>4</v>
@@ -15303,10 +15301,10 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>4</v>
@@ -15314,154 +15312,186 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>951</v>
-      </c>
-      <c r="C71" s="1"/>
+        <v>949</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>973</v>
-      </c>
-      <c r="C72" s="1"/>
+        <v>971</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>945</v>
-      </c>
-      <c r="C73" s="1"/>
+        <v>943</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>947</v>
-      </c>
-      <c r="C74" s="1"/>
+        <v>945</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>951</v>
-      </c>
-      <c r="C75" s="1"/>
+        <v>949</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>951</v>
-      </c>
-      <c r="C76" s="1"/>
+        <v>949</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>951</v>
-      </c>
-      <c r="C77" s="1"/>
+        <v>949</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>951</v>
-      </c>
-      <c r="C78" s="1"/>
+        <v>949</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>951</v>
-      </c>
-      <c r="C79" s="1"/>
+        <v>949</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>951</v>
-      </c>
-      <c r="C80" s="1"/>
+        <v>949</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>947</v>
-      </c>
-      <c r="C81" s="1"/>
+        <v>945</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>945</v>
-      </c>
-      <c r="C82" s="1"/>
+        <v>943</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>947</v>
-      </c>
-      <c r="C83" s="1"/>
+        <v>945</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>951</v>
-      </c>
-      <c r="C84" s="1"/>
+        <v>949</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>947</v>
-      </c>
-      <c r="C85" s="1"/>
+        <v>945</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>945</v>
-      </c>
-      <c r="C86" s="1"/>
+        <v>943</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>5</v>
@@ -15469,10 +15499,10 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>2</v>
@@ -15480,10 +15510,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>2</v>
@@ -15491,10 +15521,10 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>2</v>
@@ -15502,10 +15532,10 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>2</v>
@@ -15513,10 +15543,10 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>2</v>
@@ -15524,10 +15554,10 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>2</v>
@@ -15535,10 +15565,10 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>2</v>
@@ -15546,10 +15576,10 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>2</v>
@@ -15557,10 +15587,10 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>2</v>
@@ -15568,10 +15598,10 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>2</v>
@@ -15579,10 +15609,10 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>5</v>
@@ -15590,109 +15620,131 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>968</v>
-      </c>
-      <c r="C99" s="1"/>
+        <v>966</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>973</v>
-      </c>
-      <c r="C100" s="1"/>
+        <v>971</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>968</v>
-      </c>
-      <c r="C101" s="1"/>
+        <v>966</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>944</v>
-      </c>
-      <c r="C102" s="1"/>
+        <v>942</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>951</v>
-      </c>
-      <c r="C103" s="1"/>
+        <v>949</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C104" s="1"/>
+      <c r="C104" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>951</v>
-      </c>
-      <c r="C105" s="1"/>
+        <v>949</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>973</v>
-      </c>
-      <c r="C106" s="1"/>
+        <v>971</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>944</v>
-      </c>
-      <c r="C107" s="1"/>
+        <v>942</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>951</v>
-      </c>
-      <c r="C108" s="1"/>
+        <v>949</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>945</v>
-      </c>
-      <c r="C109" s="1"/>
+        <v>943</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>2</v>
@@ -15700,10 +15752,10 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>2</v>
@@ -15711,10 +15763,10 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>2</v>
@@ -15722,10 +15774,10 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>2</v>
@@ -15733,10 +15785,10 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>2</v>
@@ -15744,10 +15796,10 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>2</v>
@@ -15755,10 +15807,10 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>2</v>
@@ -15766,10 +15818,10 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>2</v>
@@ -15777,10 +15829,10 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>2</v>
@@ -15788,10 +15840,10 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>2</v>
@@ -15799,28 +15851,32 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>945</v>
-      </c>
-      <c r="C120" s="1"/>
+        <v>943</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>947</v>
-      </c>
-      <c r="C121" s="1"/>
+        <v>945</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" s="1" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>2</v>
@@ -15828,10 +15884,10 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>2</v>
@@ -15839,10 +15895,10 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>2</v>
@@ -15850,10 +15906,10 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" s="1" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>2</v>
@@ -15861,10 +15917,10 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" s="1" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>2</v>
@@ -15900,7 +15956,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>2</v>
@@ -15908,7 +15964,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>25</v>
@@ -15916,7 +15972,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>2</v>
@@ -15924,7 +15980,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>2</v>
@@ -15932,7 +15988,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>2</v>
@@ -15940,7 +15996,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>2</v>
@@ -15948,7 +16004,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>2</v>
@@ -15956,7 +16012,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>14</v>
@@ -15964,7 +16020,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>2</v>
@@ -16436,7 +16492,7 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>2</v>
@@ -16458,6 +16514,15 @@
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC7F2EFF-EAB2-4558-ACFC-8265F7CDC303}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 

--- a/data/chapter2/FRED/subsets/species.xlsx
+++ b/data/chapter2/FRED/subsets/species.xlsx
@@ -8,20 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://westernsydneyedu-my.sharepoint.com/personal/90963425_westernsydney_edu_au/Documents/PhD/code/data/chapter2/FRED/subsets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="228" documentId="8_{81FDA0CF-33C4-43D2-B8CA-CC5F96143B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A0F7066-243B-4F5A-A8C6-27417CE32066}"/>
+  <xr:revisionPtr revIDLastSave="307" documentId="8_{81FDA0CF-33C4-43D2-B8CA-CC5F96143B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFD6CD39-8D94-4943-82B9-80BFBF123A9A}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{A5444074-DC77-415C-A9E2-2BBA8270EAFC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{A5444074-DC77-415C-A9E2-2BBA8270EAFC}"/>
   </bookViews>
   <sheets>
     <sheet name="FRED4" sheetId="8" r:id="rId1"/>
     <sheet name="FungalRoot" sheetId="9" r:id="rId2"/>
-    <sheet name="Maherali 2016" sheetId="7" r:id="rId3"/>
+    <sheet name="Maherali_2016" sheetId="7" r:id="rId3"/>
     <sheet name="combined" sheetId="10" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="ExternalData_1" localSheetId="0" hidden="1">FRED4!$A$1:$B$936</definedName>
     <definedName name="ExternalData_1" localSheetId="1" hidden="1">FungalRoot!$A$1:$B$126</definedName>
-    <definedName name="ExternalData_1" localSheetId="2" hidden="1">'Maherali 2016'!$A$1:$B$70</definedName>
+    <definedName name="ExternalData_1" localSheetId="2" hidden="1">Maherali_2016!$A$1:$B$70</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -4583,7 +4583,7 @@
         <v>2</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
@@ -4594,7 +4594,7 @@
         <v>5</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
@@ -5595,7 +5595,7 @@
         <v>2</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
@@ -5606,7 +5606,7 @@
         <v>5</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.35">
@@ -5716,7 +5716,7 @@
         <v>2</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
@@ -5727,7 +5727,7 @@
         <v>5</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
@@ -5760,7 +5760,7 @@
         <v>2</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
@@ -5771,7 +5771,7 @@
         <v>5</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
@@ -6112,7 +6112,7 @@
         <v>2</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.35">
@@ -6123,7 +6123,7 @@
         <v>5</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.35">
@@ -6211,7 +6211,7 @@
         <v>2</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.35">
@@ -6222,7 +6222,7 @@
         <v>5</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.35">
@@ -6453,7 +6453,7 @@
         <v>2</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.35">
@@ -6464,7 +6464,7 @@
         <v>5</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.35">
@@ -6519,7 +6519,7 @@
         <v>2</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.35">
@@ -6783,7 +6783,7 @@
         <v>2</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.35">
@@ -6794,7 +6794,7 @@
         <v>1</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.35">
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.35">
@@ -7003,7 +7003,7 @@
         <v>5</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.35">
@@ -7058,7 +7058,7 @@
         <v>2</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.35">
@@ -7069,7 +7069,7 @@
         <v>5</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.35">
@@ -7223,7 +7223,7 @@
         <v>2</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.35">
@@ -7476,7 +7476,7 @@
         <v>2</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.35">
@@ -7487,7 +7487,7 @@
         <v>5</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.35">
@@ -7916,7 +7916,7 @@
         <v>5</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.35">
@@ -7927,7 +7927,7 @@
         <v>2</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.35">
@@ -7938,7 +7938,7 @@
         <v>2</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.35">
@@ -7949,7 +7949,7 @@
         <v>1</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.35">
@@ -7960,7 +7960,7 @@
         <v>5</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.35">
@@ -8092,7 +8092,7 @@
         <v>2</v>
       </c>
       <c r="C352" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.35">
@@ -8785,7 +8785,7 @@
         <v>5</v>
       </c>
       <c r="C415" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.35">
@@ -8796,7 +8796,7 @@
         <v>2</v>
       </c>
       <c r="C416" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.35">
@@ -8873,7 +8873,7 @@
         <v>2</v>
       </c>
       <c r="C423" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.35">
@@ -8928,7 +8928,7 @@
         <v>2</v>
       </c>
       <c r="C428" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.35">
@@ -8939,7 +8939,7 @@
         <v>5</v>
       </c>
       <c r="C429" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.35">
@@ -8972,7 +8972,7 @@
         <v>2</v>
       </c>
       <c r="C432" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.35">
@@ -8983,7 +8983,7 @@
         <v>1</v>
       </c>
       <c r="C433" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.35">
@@ -9115,7 +9115,7 @@
         <v>2</v>
       </c>
       <c r="C445" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.35">
@@ -9500,7 +9500,7 @@
         <v>1</v>
       </c>
       <c r="C480" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.35">
@@ -9511,7 +9511,7 @@
         <v>2</v>
       </c>
       <c r="C481" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.35">
@@ -9555,7 +9555,7 @@
         <v>2</v>
       </c>
       <c r="C485" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.35">
@@ -9566,7 +9566,7 @@
         <v>5</v>
       </c>
       <c r="C486" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.35">
@@ -10743,7 +10743,7 @@
         <v>2</v>
       </c>
       <c r="C593" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.35">
@@ -10754,7 +10754,7 @@
         <v>5</v>
       </c>
       <c r="C594" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.35">
@@ -10776,7 +10776,7 @@
         <v>1</v>
       </c>
       <c r="C596" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.35">
@@ -10787,7 +10787,7 @@
         <v>2</v>
       </c>
       <c r="C597" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.35">
@@ -10820,7 +10820,7 @@
         <v>1</v>
       </c>
       <c r="C600" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.35">
@@ -10831,7 +10831,7 @@
         <v>2</v>
       </c>
       <c r="C601" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.35">
@@ -11271,7 +11271,7 @@
         <v>2</v>
       </c>
       <c r="C641" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.35">
@@ -11282,7 +11282,7 @@
         <v>5</v>
       </c>
       <c r="C642" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.35">
@@ -11326,7 +11326,7 @@
         <v>2</v>
       </c>
       <c r="C646" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.35">
@@ -11337,7 +11337,7 @@
         <v>5</v>
       </c>
       <c r="C647" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.35">
@@ -11601,7 +11601,7 @@
         <v>5</v>
       </c>
       <c r="C671" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.35">
@@ -11733,7 +11733,7 @@
         <v>5</v>
       </c>
       <c r="C683" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.35">
@@ -11744,7 +11744,7 @@
         <v>1</v>
       </c>
       <c r="C684" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="685" spans="1:3" x14ac:dyDescent="0.35">
@@ -12316,7 +12316,7 @@
         <v>2</v>
       </c>
       <c r="C736" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="737" spans="1:3" x14ac:dyDescent="0.35">
@@ -12327,7 +12327,7 @@
         <v>5</v>
       </c>
       <c r="C737" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="738" spans="1:3" x14ac:dyDescent="0.35">
@@ -12536,7 +12536,7 @@
         <v>5</v>
       </c>
       <c r="C756" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="757" spans="1:3" x14ac:dyDescent="0.35">
@@ -12668,7 +12668,7 @@
         <v>5</v>
       </c>
       <c r="C768" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="769" spans="1:3" x14ac:dyDescent="0.35">
@@ -12844,7 +12844,7 @@
         <v>2</v>
       </c>
       <c r="C784" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="785" spans="1:3" x14ac:dyDescent="0.35">
@@ -12855,7 +12855,7 @@
         <v>5</v>
       </c>
       <c r="C785" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="786" spans="1:3" x14ac:dyDescent="0.35">
@@ -12910,7 +12910,7 @@
         <v>2</v>
       </c>
       <c r="C790" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="791" spans="1:3" x14ac:dyDescent="0.35">
@@ -12921,7 +12921,7 @@
         <v>5</v>
       </c>
       <c r="C791" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="792" spans="1:3" x14ac:dyDescent="0.35">
@@ -12998,7 +12998,7 @@
         <v>2</v>
       </c>
       <c r="C798" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="799" spans="1:3" x14ac:dyDescent="0.35">
@@ -13009,7 +13009,7 @@
         <v>5</v>
       </c>
       <c r="C799" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="800" spans="1:3" x14ac:dyDescent="0.35">
@@ -13053,7 +13053,7 @@
         <v>1</v>
       </c>
       <c r="C803" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="804" spans="1:3" x14ac:dyDescent="0.35">
@@ -13064,7 +13064,7 @@
         <v>5</v>
       </c>
       <c r="C804" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.35">
@@ -13075,7 +13075,7 @@
         <v>1</v>
       </c>
       <c r="C805" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="806" spans="1:3" x14ac:dyDescent="0.35">
@@ -13141,7 +13141,7 @@
         <v>2</v>
       </c>
       <c r="C811" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="812" spans="1:3" x14ac:dyDescent="0.35">
@@ -13152,7 +13152,7 @@
         <v>5</v>
       </c>
       <c r="C812" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="813" spans="1:3" x14ac:dyDescent="0.35">
@@ -13559,7 +13559,7 @@
         <v>2</v>
       </c>
       <c r="C849" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="850" spans="1:3" x14ac:dyDescent="0.35">
@@ -13900,7 +13900,7 @@
         <v>1</v>
       </c>
       <c r="C880" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="881" spans="1:3" x14ac:dyDescent="0.35">
@@ -13911,7 +13911,7 @@
         <v>2</v>
       </c>
       <c r="C881" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.35">
@@ -13999,7 +13999,7 @@
         <v>1</v>
       </c>
       <c r="C889" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="890" spans="1:3" x14ac:dyDescent="0.35">
@@ -14010,7 +14010,7 @@
         <v>2</v>
       </c>
       <c r="C890" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="891" spans="1:3" x14ac:dyDescent="0.35">
@@ -14076,7 +14076,7 @@
         <v>5</v>
       </c>
       <c r="C896" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="897" spans="1:3" x14ac:dyDescent="0.35">
@@ -14098,7 +14098,7 @@
         <v>1</v>
       </c>
       <c r="C898" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="899" spans="1:3" x14ac:dyDescent="0.35">
@@ -14395,7 +14395,7 @@
         <v>5</v>
       </c>
       <c r="C925" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="926" spans="1:3" x14ac:dyDescent="0.35">
@@ -14472,7 +14472,7 @@
         <v>5</v>
       </c>
       <c r="C932" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="933" spans="1:3" x14ac:dyDescent="0.35">

--- a/data/chapter2/FRED/subsets/species.xlsx
+++ b/data/chapter2/FRED/subsets/species.xlsx
@@ -12676,27 +12676,6 @@
   </cellStyles>
   <dxfs count="18">
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
@@ -12725,6 +12704,27 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -12860,13 +12860,13 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{276A84AE-031F-465C-BBF2-AAF93653128C}" name="species_hand_cleaned" displayName="species_hand_cleaned" ref="A1:G1302" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G1302" xr:uid="{276A84AE-031F-465C-BBF2-AAF93653128C}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{834DA843-A3B2-4812-B21B-A3DEA02361A7}" uniqueName="1" name="binominal" queryTableFieldId="1" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{25E4C45B-B5E0-47D3-B8D2-D8A032C0B3C1}" uniqueName="2" name="F01286" queryTableFieldId="2" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{BE447818-EF6B-414C-96F1-DF58F4E460AA}" uniqueName="3" name="F01287" queryTableFieldId="3" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{66A0A3E8-604C-477F-BD1E-E7B99F2F3D39}" uniqueName="4" name="F01289" queryTableFieldId="4" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{54B8910C-E82C-4055-9898-875B6ED067C7}" uniqueName="5" name="F01290" queryTableFieldId="5" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{97F66733-E6F6-40AB-B471-ECB89590C4B1}" uniqueName="6" name="reconciled_state" queryTableFieldId="6" dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{5BF75914-BDC7-4132-BD06-A237BAE412CF}" uniqueName="7" name="synonyms" queryTableFieldId="7" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{834DA843-A3B2-4812-B21B-A3DEA02361A7}" uniqueName="1" name="binominal" queryTableFieldId="1" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{25E4C45B-B5E0-47D3-B8D2-D8A032C0B3C1}" uniqueName="2" name="F01286" queryTableFieldId="2" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{BE447818-EF6B-414C-96F1-DF58F4E460AA}" uniqueName="3" name="F01287" queryTableFieldId="3" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{66A0A3E8-604C-477F-BD1E-E7B99F2F3D39}" uniqueName="4" name="F01289" queryTableFieldId="4" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{54B8910C-E82C-4055-9898-875B6ED067C7}" uniqueName="5" name="F01290" queryTableFieldId="5" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{97F66733-E6F6-40AB-B471-ECB89590C4B1}" uniqueName="6" name="reconciled_state" queryTableFieldId="6" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{5BF75914-BDC7-4132-BD06-A237BAE412CF}" uniqueName="7" name="synonyms" queryTableFieldId="7" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -23495,7 +23495,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -24902,7 +24902,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -25482,7 +25482,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/data/chapter2/FRED/subsets/species.xlsx
+++ b/data/chapter2/FRED/subsets/species.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://westernsydneyedu-my.sharepoint.com/personal/90963425_westernsydney_edu_au/Documents/PhD/code/data/chapter2/FRED/subsets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="369" documentId="8_{81FDA0CF-33C4-43D2-B8CA-CC5F96143B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A9F6DD7-898A-4156-8F28-74B97087B99F}"/>
+  <xr:revisionPtr revIDLastSave="373" documentId="8_{81FDA0CF-33C4-43D2-B8CA-CC5F96143B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7E43905-9004-4E81-BE57-AEFB2CEE7D6C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{A5444074-DC77-415C-A9E2-2BBA8270EAFC}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15104" uniqueCount="4036">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15125" uniqueCount="4036">
   <si>
     <t>F00645</t>
   </si>
@@ -27453,9 +27453,11 @@
         <v>1083</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I62" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>4035</v>
+      </c>
       <c r="J62" s="1" t="s">
         <v>1083</v>
       </c>
@@ -27633,9 +27635,11 @@
         <v>1083</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I68" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>4035</v>
+      </c>
       <c r="J68" s="1" t="s">
         <v>2991</v>
       </c>
@@ -27933,9 +27937,11 @@
         <v>1083</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I78" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>4035</v>
+      </c>
       <c r="J78" s="1" t="s">
         <v>2996</v>
       </c>
@@ -27963,9 +27969,11 @@
         <v>1083</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I79" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>4035</v>
+      </c>
       <c r="J79" s="1" t="s">
         <v>3947</v>
       </c>

--- a/data/chapter2/FRED/subsets/species.xlsx
+++ b/data/chapter2/FRED/subsets/species.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://westernsydneyedu-my.sharepoint.com/personal/90963425_westernsydney_edu_au/Documents/PhD/code/data/chapter2/FRED/subsets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="373" documentId="8_{81FDA0CF-33C4-43D2-B8CA-CC5F96143B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7E43905-9004-4E81-BE57-AEFB2CEE7D6C}"/>
+  <xr:revisionPtr revIDLastSave="376" documentId="8_{81FDA0CF-33C4-43D2-B8CA-CC5F96143B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{494AE9CA-6E97-4A38-8AAB-644A928A797B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{A5444074-DC77-415C-A9E2-2BBA8270EAFC}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15125" uniqueCount="4036">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15166" uniqueCount="4036">
   <si>
     <t>F00645</t>
   </si>
@@ -29711,9 +29711,11 @@
         <v>1083</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I137" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="I137" s="1" t="s">
+        <v>4035</v>
+      </c>
       <c r="J137" s="1" t="s">
         <v>1390</v>
       </c>
@@ -29861,9 +29863,11 @@
         <v>1083</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I142" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="I142" s="1" t="s">
+        <v>4035</v>
+      </c>
       <c r="J142" s="1" t="s">
         <v>1083</v>
       </c>
@@ -29951,9 +29955,11 @@
         <v>1083</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I145" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="I145" s="1" t="s">
+        <v>4035</v>
+      </c>
       <c r="J145" s="1" t="s">
         <v>1701</v>
       </c>
@@ -30011,9 +30017,11 @@
         <v>1083</v>
       </c>
       <c r="H147" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I147" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="I147" s="1" t="s">
+        <v>4035</v>
+      </c>
       <c r="J147" s="1" t="s">
         <v>1083</v>
       </c>
@@ -30041,9 +30049,11 @@
         <v>1083</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I148" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="I148" s="1" t="s">
+        <v>4035</v>
+      </c>
       <c r="J148" s="1" t="s">
         <v>1916</v>
       </c>
@@ -30491,9 +30501,11 @@
         <v>1083</v>
       </c>
       <c r="H163" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I163" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="I163" s="1" t="s">
+        <v>4035</v>
+      </c>
       <c r="J163" s="1" t="s">
         <v>1919</v>
       </c>
@@ -30521,9 +30533,11 @@
         <v>1083</v>
       </c>
       <c r="H164" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I164" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="I164" s="1" t="s">
+        <v>4035</v>
+      </c>
       <c r="J164" s="1" t="s">
         <v>1083</v>
       </c>
@@ -30581,9 +30595,11 @@
         <v>1083</v>
       </c>
       <c r="H166" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I166" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="I166" s="1" t="s">
+        <v>4035</v>
+      </c>
       <c r="J166" s="1" t="s">
         <v>2142</v>
       </c>
@@ -31151,9 +31167,11 @@
         <v>1083</v>
       </c>
       <c r="H185" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I185" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="I185" s="1" t="s">
+        <v>4035</v>
+      </c>
       <c r="J185" s="1" t="s">
         <v>2145</v>
       </c>
@@ -31391,9 +31409,11 @@
         <v>1083</v>
       </c>
       <c r="H193" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I193" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="I193" s="1" t="s">
+        <v>4035</v>
+      </c>
       <c r="J193" s="1" t="s">
         <v>1083</v>
       </c>
@@ -31421,9 +31441,11 @@
         <v>1083</v>
       </c>
       <c r="H194" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I194" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="I194" s="1" t="s">
+        <v>4035</v>
+      </c>
       <c r="J194" s="1" t="s">
         <v>2418</v>
       </c>
@@ -31631,9 +31653,11 @@
         <v>1083</v>
       </c>
       <c r="H201" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I201" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="I201" s="1" t="s">
+        <v>4035</v>
+      </c>
       <c r="J201" s="1" t="s">
         <v>1083</v>
       </c>
@@ -31961,9 +31985,11 @@
         <v>1083</v>
       </c>
       <c r="H212" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I212" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="I212" s="1" t="s">
+        <v>4035</v>
+      </c>
       <c r="J212" s="1" t="s">
         <v>1083</v>
       </c>
@@ -32171,9 +32197,11 @@
         <v>1083</v>
       </c>
       <c r="H219" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I219" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="I219" s="1" t="s">
+        <v>4035</v>
+      </c>
       <c r="J219" s="1" t="s">
         <v>1083</v>
       </c>
@@ -32231,9 +32259,11 @@
         <v>1083</v>
       </c>
       <c r="H221" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I221" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="I221" s="1" t="s">
+        <v>4035</v>
+      </c>
       <c r="J221" s="1" t="s">
         <v>1083</v>
       </c>
@@ -32471,9 +32501,11 @@
         <v>1083</v>
       </c>
       <c r="H229" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I229" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="I229" s="1" t="s">
+        <v>4035</v>
+      </c>
       <c r="J229" s="1" t="s">
         <v>2434</v>
       </c>
@@ -32501,9 +32533,11 @@
         <v>1083</v>
       </c>
       <c r="H230" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I230" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="I230" s="1" t="s">
+        <v>4035</v>
+      </c>
       <c r="J230" s="1" t="s">
         <v>2438</v>
       </c>
@@ -32651,9 +32685,11 @@
         <v>1083</v>
       </c>
       <c r="H235" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I235" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="I235" s="1" t="s">
+        <v>4035</v>
+      </c>
       <c r="J235" s="1" t="s">
         <v>1083</v>
       </c>
@@ -32681,9 +32717,11 @@
         <v>1083</v>
       </c>
       <c r="H236" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I236" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="I236" s="1" t="s">
+        <v>4035</v>
+      </c>
       <c r="J236" s="1" t="s">
         <v>1083</v>
       </c>
@@ -32711,9 +32749,11 @@
         <v>1083</v>
       </c>
       <c r="H237" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I237" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="I237" s="1" t="s">
+        <v>4035</v>
+      </c>
       <c r="J237" s="1" t="s">
         <v>1083</v>
       </c>
@@ -32741,9 +32781,11 @@
         <v>1083</v>
       </c>
       <c r="H238" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I238" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="I238" s="1" t="s">
+        <v>4035</v>
+      </c>
       <c r="J238" s="1" t="s">
         <v>2452</v>
       </c>
@@ -32891,9 +32933,11 @@
         <v>1083</v>
       </c>
       <c r="H243" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I243" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="I243" s="1" t="s">
+        <v>4035</v>
+      </c>
       <c r="J243" s="1" t="s">
         <v>2455</v>
       </c>
@@ -33131,9 +33175,11 @@
         <v>1083</v>
       </c>
       <c r="H251" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I251" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="I251" s="1" t="s">
+        <v>4035</v>
+      </c>
       <c r="J251" s="1" t="s">
         <v>2458</v>
       </c>
@@ -33521,9 +33567,11 @@
         <v>1083</v>
       </c>
       <c r="H264" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I264" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="I264" s="1" t="s">
+        <v>4035</v>
+      </c>
       <c r="J264" s="1" t="s">
         <v>1083</v>
       </c>
@@ -33701,9 +33749,11 @@
         <v>1083</v>
       </c>
       <c r="H270" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I270" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="I270" s="1" t="s">
+        <v>4035</v>
+      </c>
       <c r="J270" s="1" t="s">
         <v>1083</v>
       </c>
@@ -33731,9 +33781,11 @@
         <v>1083</v>
       </c>
       <c r="H271" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I271" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="I271" s="1" t="s">
+        <v>4035</v>
+      </c>
       <c r="J271" s="1" t="s">
         <v>1083</v>
       </c>
@@ -33821,9 +33873,11 @@
         <v>1083</v>
       </c>
       <c r="H274" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I274" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="I274" s="1" t="s">
+        <v>4035</v>
+      </c>
       <c r="J274" s="1" t="s">
         <v>2670</v>
       </c>
@@ -33911,9 +33965,11 @@
         <v>1083</v>
       </c>
       <c r="H277" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I277" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="I277" s="1" t="s">
+        <v>4035</v>
+      </c>
       <c r="J277" s="1" t="s">
         <v>3217</v>
       </c>
@@ -34031,9 +34087,11 @@
         <v>1083</v>
       </c>
       <c r="H281" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I281" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="I281" s="1" t="s">
+        <v>4035</v>
+      </c>
       <c r="J281" s="1" t="s">
         <v>3737</v>
       </c>
@@ -34061,9 +34119,11 @@
         <v>1083</v>
       </c>
       <c r="H282" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I282" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="I282" s="1" t="s">
+        <v>4035</v>
+      </c>
       <c r="J282" s="1" t="s">
         <v>3798</v>
       </c>
@@ -34121,9 +34181,11 @@
         <v>1083</v>
       </c>
       <c r="H284" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I284" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="I284" s="1" t="s">
+        <v>4035</v>
+      </c>
       <c r="J284" s="1" t="s">
         <v>3808</v>
       </c>

--- a/data/chapter2/FRED/subsets/species.xlsx
+++ b/data/chapter2/FRED/subsets/species.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://westernsydneyedu-my.sharepoint.com/personal/90963425_westernsydney_edu_au/Documents/PhD/code/data/chapter2/FRED/subsets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="402" documentId="8_{81FDA0CF-33C4-43D2-B8CA-CC5F96143B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71C13D13-BED1-40C9-BDC8-65CA0F89DD89}"/>
+  <xr:revisionPtr revIDLastSave="415" documentId="8_{81FDA0CF-33C4-43D2-B8CA-CC5F96143B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F852F72D-3A1E-491E-929D-3CEF7E85B524}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{A5444074-DC77-415C-A9E2-2BBA8270EAFC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="456" activeTab="3" xr2:uid="{A5444074-DC77-415C-A9E2-2BBA8270EAFC}"/>
   </bookViews>
   <sheets>
     <sheet name="FRED4" sheetId="8" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13864" uniqueCount="2975">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13907" uniqueCount="2975">
   <si>
     <t>F00645</t>
   </si>
@@ -35121,9 +35121,11 @@
         <v>1075</v>
       </c>
       <c r="G467" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H467" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H467" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I467" s="1" t="s">
         <v>1075</v>
       </c>
@@ -35175,9 +35177,11 @@
         <v>1075</v>
       </c>
       <c r="G469" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H469" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H469" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I469" s="1" t="s">
         <v>1311</v>
       </c>
@@ -35499,9 +35503,11 @@
         <v>1075</v>
       </c>
       <c r="G481" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H481" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H481" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I481" s="1" t="s">
         <v>1314</v>
       </c>
@@ -35661,9 +35667,11 @@
         <v>1075</v>
       </c>
       <c r="G487" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H487" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H487" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I487" s="1" t="s">
         <v>1393</v>
       </c>
@@ -35688,9 +35696,11 @@
         <v>1075</v>
       </c>
       <c r="G488" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H488" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H488" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I488" s="1" t="s">
         <v>1583</v>
       </c>
@@ -35742,9 +35752,11 @@
         <v>1075</v>
       </c>
       <c r="G490" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H490" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H490" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I490" s="1" t="s">
         <v>1585</v>
       </c>
@@ -35769,9 +35781,11 @@
         <v>1075</v>
       </c>
       <c r="G491" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H491" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H491" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I491" s="1" t="s">
         <v>1632</v>
       </c>
@@ -36338,9 +36352,11 @@
         <v>1075</v>
       </c>
       <c r="G512" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H512" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="H512" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I512" s="1" t="s">
         <v>1075</v>
       </c>
@@ -36392,9 +36408,11 @@
         <v>1075</v>
       </c>
       <c r="G514" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H514" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="H514" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I514" s="1" t="s">
         <v>1441</v>
       </c>
@@ -36419,9 +36437,11 @@
         <v>1075</v>
       </c>
       <c r="G515" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H515" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="H515" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I515" s="1" t="s">
         <v>1075</v>
       </c>
@@ -36446,9 +36466,11 @@
         <v>1075</v>
       </c>
       <c r="G516" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H516" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="H516" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I516" s="1" t="s">
         <v>2141</v>
       </c>
@@ -36473,9 +36495,11 @@
         <v>1075</v>
       </c>
       <c r="G517" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H517" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="H517" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I517" s="1" t="s">
         <v>2145</v>
       </c>
@@ -36662,9 +36686,11 @@
         <v>1075</v>
       </c>
       <c r="G524" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H524" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="H524" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I524" s="1" t="s">
         <v>2148</v>
       </c>
@@ -36743,9 +36769,11 @@
         <v>1075</v>
       </c>
       <c r="G527" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H527" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="H527" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I527" s="1" t="s">
         <v>2151</v>
       </c>
@@ -40772,9 +40800,11 @@
         <v>1075</v>
       </c>
       <c r="G674" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H674" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H674" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I674" s="1" t="s">
         <v>1220</v>
       </c>
@@ -40853,9 +40883,11 @@
         <v>1075</v>
       </c>
       <c r="G677" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H677" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H677" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I677" s="1" t="s">
         <v>1075</v>
       </c>
@@ -41231,9 +41263,11 @@
         <v>1075</v>
       </c>
       <c r="G691" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H691" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H691" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I691" s="1" t="s">
         <v>1075</v>
       </c>
@@ -41258,9 +41292,11 @@
         <v>1075</v>
       </c>
       <c r="G692" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H692" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H692" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I692" s="1" t="s">
         <v>1075</v>
       </c>
@@ -41366,9 +41402,11 @@
         <v>1075</v>
       </c>
       <c r="G696" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H696" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H696" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I696" s="1" t="s">
         <v>1075</v>
       </c>
@@ -41501,9 +41539,11 @@
         <v>1075</v>
       </c>
       <c r="G701" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H701" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H701" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I701" s="1" t="s">
         <v>2254</v>
       </c>
@@ -41555,9 +41595,11 @@
         <v>1075</v>
       </c>
       <c r="G703" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H703" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H703" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I703" s="1" t="s">
         <v>1075</v>
       </c>
@@ -41636,9 +41678,11 @@
         <v>1075</v>
       </c>
       <c r="G706" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H706" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H706" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I706" s="1" t="s">
         <v>2257</v>
       </c>
@@ -41798,9 +41842,11 @@
         <v>1075</v>
       </c>
       <c r="G712" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H712" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H712" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I712" s="1" t="s">
         <v>1075</v>
       </c>
@@ -41825,9 +41871,11 @@
         <v>1075</v>
       </c>
       <c r="G713" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H713" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H713" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I713" s="1" t="s">
         <v>2260</v>
       </c>
@@ -41933,9 +41981,11 @@
         <v>1075</v>
       </c>
       <c r="G717" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H717" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H717" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I717" s="1" t="s">
         <v>2262</v>
       </c>
@@ -42149,9 +42199,11 @@
         <v>1075</v>
       </c>
       <c r="G725" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H725" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H725" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I725" s="1" t="s">
         <v>2521</v>
       </c>

--- a/data/chapter2/FRED/subsets/species.xlsx
+++ b/data/chapter2/FRED/subsets/species.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://westernsydneyedu-my.sharepoint.com/personal/90963425_westernsydney_edu_au/Documents/PhD/code/data/chapter2/FRED/subsets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="415" documentId="8_{81FDA0CF-33C4-43D2-B8CA-CC5F96143B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F852F72D-3A1E-491E-929D-3CEF7E85B524}"/>
+  <xr:revisionPtr revIDLastSave="424" documentId="8_{81FDA0CF-33C4-43D2-B8CA-CC5F96143B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4A5B090-3767-43C1-ADD4-90828592DC7B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="456" activeTab="3" xr2:uid="{A5444074-DC77-415C-A9E2-2BBA8270EAFC}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13907" uniqueCount="2975">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13945" uniqueCount="2975">
   <si>
     <t>F00645</t>
   </si>
@@ -42417,9 +42417,11 @@
         <v>1075</v>
       </c>
       <c r="G733" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H733" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H733" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I733" s="1" t="s">
         <v>1137</v>
       </c>
@@ -43443,9 +43445,11 @@
         <v>1075</v>
       </c>
       <c r="G771" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H771" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H771" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I771" s="1" t="s">
         <v>1075</v>
       </c>
@@ -43470,9 +43474,11 @@
         <v>1075</v>
       </c>
       <c r="G772" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H772" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H772" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I772" s="1" t="s">
         <v>1460</v>
       </c>
@@ -43740,9 +43746,11 @@
         <v>1075</v>
       </c>
       <c r="G782" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H782" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H782" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I782" s="1" t="s">
         <v>1075</v>
       </c>
@@ -43956,9 +43964,11 @@
         <v>1075</v>
       </c>
       <c r="G790" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H790" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H790" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I790" s="1" t="s">
         <v>1075</v>
       </c>
@@ -43983,9 +43993,11 @@
         <v>1075</v>
       </c>
       <c r="G791" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H791" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H791" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I791" s="1" t="s">
         <v>2671</v>
       </c>
@@ -44010,9 +44022,11 @@
         <v>1075</v>
       </c>
       <c r="G792" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H792" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H792" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I792" s="1" t="s">
         <v>1075</v>
       </c>
@@ -44037,9 +44051,11 @@
         <v>1075</v>
       </c>
       <c r="G793" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H793" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H793" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I793" s="1" t="s">
         <v>1075</v>
       </c>
@@ -44064,9 +44080,11 @@
         <v>1075</v>
       </c>
       <c r="G794" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H794" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H794" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I794" s="1" t="s">
         <v>1075</v>
       </c>
@@ -44091,9 +44109,11 @@
         <v>1075</v>
       </c>
       <c r="G795" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H795" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H795" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I795" s="1" t="s">
         <v>1075</v>
       </c>
@@ -44172,9 +44192,11 @@
         <v>1075</v>
       </c>
       <c r="G798" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H798" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H798" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I798" s="1" t="s">
         <v>1075</v>
       </c>
@@ -44442,9 +44464,11 @@
         <v>1075</v>
       </c>
       <c r="G808" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H808" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H808" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I808" s="1" t="s">
         <v>1817</v>
       </c>
@@ -44496,9 +44520,11 @@
         <v>1075</v>
       </c>
       <c r="G810" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H810" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H810" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I810" s="1" t="s">
         <v>1075</v>
       </c>
@@ -44523,9 +44549,11 @@
         <v>1075</v>
       </c>
       <c r="G811" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H811" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H811" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I811" s="1" t="s">
         <v>1075</v>
       </c>
@@ -44550,9 +44578,11 @@
         <v>1075</v>
       </c>
       <c r="G812" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H812" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H812" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I812" s="1" t="s">
         <v>1075</v>
       </c>
@@ -44577,9 +44607,11 @@
         <v>1075</v>
       </c>
       <c r="G813" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H813" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H813" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I813" s="1" t="s">
         <v>1075</v>
       </c>
@@ -45036,9 +45068,11 @@
         <v>1075</v>
       </c>
       <c r="G830" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H830" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H830" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I830" s="1" t="s">
         <v>1964</v>
       </c>
@@ -45117,9 +45151,11 @@
         <v>1075</v>
       </c>
       <c r="G833" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H833" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H833" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I833" s="1" t="s">
         <v>1075</v>
       </c>
@@ -45144,9 +45180,11 @@
         <v>1075</v>
       </c>
       <c r="G834" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H834" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H834" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I834" s="1" t="s">
         <v>1075</v>
       </c>
@@ -45171,9 +45209,11 @@
         <v>1075</v>
       </c>
       <c r="G835" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H835" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H835" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I835" s="1" t="s">
         <v>2598</v>
       </c>
@@ -45819,9 +45859,11 @@
         <v>1075</v>
       </c>
       <c r="G859" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H859" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H859" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I859" s="1" t="s">
         <v>1075</v>
       </c>
@@ -45954,9 +45996,11 @@
         <v>1075</v>
       </c>
       <c r="G864" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H864" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H864" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I864" s="1" t="s">
         <v>1788</v>
       </c>
@@ -46062,9 +46106,11 @@
         <v>1075</v>
       </c>
       <c r="G868" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H868" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H868" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I868" s="1" t="s">
         <v>2305</v>
       </c>
@@ -50868,9 +50914,11 @@
         <v>1075</v>
       </c>
       <c r="G1046" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H1046" s="1"/>
+        <v>5</v>
+      </c>
+      <c r="H1046" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I1046" s="1" t="s">
         <v>1075</v>
       </c>
@@ -50976,9 +51024,11 @@
         <v>1075</v>
       </c>
       <c r="G1050" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H1050" s="1"/>
+        <v>5</v>
+      </c>
+      <c r="H1050" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I1050" s="1" t="s">
         <v>1075</v>
       </c>
@@ -51084,9 +51134,11 @@
         <v>1075</v>
       </c>
       <c r="G1054" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H1054" s="1"/>
+        <v>5</v>
+      </c>
+      <c r="H1054" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I1054" s="1" t="s">
         <v>1075</v>
       </c>
@@ -51381,9 +51433,11 @@
         <v>1075</v>
       </c>
       <c r="G1065" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H1065" s="1"/>
+        <v>5</v>
+      </c>
+      <c r="H1065" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I1065" s="1" t="s">
         <v>1075</v>
       </c>
@@ -52150,9 +52204,11 @@
         <v>1075</v>
       </c>
       <c r="G1092" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H1092" s="1"/>
+        <v>5</v>
+      </c>
+      <c r="H1092" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I1092" s="1" t="s">
         <v>1075</v>
       </c>

--- a/data/chapter2/FRED/subsets/species.xlsx
+++ b/data/chapter2/FRED/subsets/species.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://westernsydneyedu-my.sharepoint.com/personal/90963425_westernsydney_edu_au/Documents/PhD/code/data/chapter2/FRED/subsets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="424" documentId="8_{81FDA0CF-33C4-43D2-B8CA-CC5F96143B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4A5B090-3767-43C1-ADD4-90828592DC7B}"/>
+  <xr:revisionPtr revIDLastSave="446" documentId="8_{81FDA0CF-33C4-43D2-B8CA-CC5F96143B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD15912E-3F11-480A-ACCE-D32D195EEC2D}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="456" activeTab="3" xr2:uid="{A5444074-DC77-415C-A9E2-2BBA8270EAFC}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13945" uniqueCount="2975">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13983" uniqueCount="2975">
   <si>
     <t>F00645</t>
   </si>
@@ -23414,7 +23414,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>2710</v>
       </c>
@@ -23524,7 +23524,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>2131</v>
       </c>
@@ -23553,7 +23553,7 @@
         <v>2132</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>2133</v>
       </c>
@@ -23744,7 +23744,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>2442</v>
       </c>
@@ -23773,7 +23773,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>2732</v>
       </c>
@@ -24072,7 +24072,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>1212</v>
       </c>
@@ -24236,7 +24236,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>2278</v>
       </c>
@@ -24508,7 +24508,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
         <v>2282</v>
       </c>
@@ -24537,7 +24537,7 @@
         <v>2284</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>2907</v>
       </c>
@@ -24593,7 +24593,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
         <v>2289</v>
       </c>
@@ -24622,7 +24622,7 @@
         <v>2291</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
         <v>2866</v>
       </c>
@@ -24651,7 +24651,7 @@
         <v>2868</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>2005</v>
       </c>
@@ -24671,9 +24671,11 @@
         <v>1075</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H83" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I83" s="1" t="s">
         <v>1075</v>
       </c>
@@ -24732,7 +24734,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
         <v>2009</v>
       </c>
@@ -24752,9 +24754,11 @@
         <v>1075</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H86" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I86" s="1" t="s">
         <v>2010</v>
       </c>
@@ -25029,7 +25033,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
         <v>2012</v>
       </c>
@@ -25049,9 +25053,11 @@
         <v>1075</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H97" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I97" s="1" t="s">
         <v>1075</v>
       </c>
@@ -25454,9 +25460,11 @@
         <v>1075</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H112" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H112" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I112" s="1" t="s">
         <v>2388</v>
       </c>
@@ -25616,9 +25624,11 @@
         <v>1075</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H118" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H118" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I118" s="1" t="s">
         <v>2729</v>
       </c>
@@ -26109,7 +26119,7 @@
         <v>1312</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" s="1" t="s">
         <v>1278</v>
       </c>
@@ -26246,7 +26256,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" s="1" t="s">
         <v>1321</v>
       </c>
@@ -26329,7 +26339,7 @@
         <v>1325</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" s="1" t="s">
         <v>1471</v>
       </c>
@@ -26385,7 +26395,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" s="1" t="s">
         <v>1569</v>
       </c>
@@ -26414,7 +26424,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" s="1" t="s">
         <v>1606</v>
       </c>
@@ -26821,7 +26831,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" s="1" t="s">
         <v>1609</v>
       </c>
@@ -26850,7 +26860,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" s="1" t="s">
         <v>1707</v>
       </c>
@@ -26906,7 +26916,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" s="1" t="s">
         <v>1758</v>
       </c>
@@ -27421,7 +27431,7 @@
         <v>1390</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185" s="1" t="s">
         <v>1760</v>
       </c>
@@ -27639,7 +27649,7 @@
         <v>1407</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193" s="1" t="s">
         <v>1928</v>
       </c>
@@ -27668,7 +27678,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" s="1" t="s">
         <v>1930</v>
       </c>
@@ -27859,7 +27869,7 @@
         <v>1416</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201" s="1" t="s">
         <v>1933</v>
       </c>
@@ -28158,7 +28168,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212" s="1" t="s">
         <v>1934</v>
       </c>
@@ -28349,7 +28359,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A219" s="1" t="s">
         <v>1935</v>
       </c>
@@ -28405,7 +28415,7 @@
         <v>1442</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A221" s="1" t="s">
         <v>1937</v>
       </c>
@@ -28623,7 +28633,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229" s="1" t="s">
         <v>1938</v>
       </c>
@@ -28652,7 +28662,7 @@
         <v>1939</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A230" s="1" t="s">
         <v>1940</v>
       </c>
@@ -28789,7 +28799,7 @@
         <v>1466</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" s="1" t="s">
         <v>1942</v>
       </c>
@@ -28818,7 +28828,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A236" s="1" t="s">
         <v>1943</v>
       </c>
@@ -28847,7 +28857,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" s="1" t="s">
         <v>1945</v>
       </c>
@@ -28876,7 +28886,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238" s="1" t="s">
         <v>1947</v>
       </c>
@@ -29013,7 +29023,7 @@
         <v>1483</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243" s="1" t="s">
         <v>1949</v>
       </c>
@@ -29231,7 +29241,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251" s="1" t="s">
         <v>1951</v>
       </c>
@@ -29584,7 +29594,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264" s="1" t="s">
         <v>1953</v>
       </c>
@@ -29748,7 +29758,7 @@
         <v>1525</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A270" s="1" t="s">
         <v>1954</v>
       </c>
@@ -29777,7 +29787,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A271" s="1" t="s">
         <v>1955</v>
       </c>
@@ -29860,7 +29870,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A274" s="1" t="s">
         <v>2080</v>
       </c>
@@ -29943,7 +29953,7 @@
         <v>1533</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277" s="1" t="s">
         <v>2421</v>
       </c>
@@ -30053,7 +30063,7 @@
         <v>1538</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A281" s="1" t="s">
         <v>2760</v>
       </c>
@@ -30082,7 +30092,7 @@
         <v>2761</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A282" s="1" t="s">
         <v>2802</v>
       </c>
@@ -30138,7 +30148,7 @@
         <v>1547</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A284" s="1" t="s">
         <v>2809</v>
       </c>
@@ -30187,9 +30197,11 @@
         <v>1075</v>
       </c>
       <c r="G285" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H285" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H285" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I285" s="1" t="s">
         <v>1643</v>
       </c>
@@ -30214,9 +30226,11 @@
         <v>1075</v>
       </c>
       <c r="G286" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H286" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H286" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I286" s="1" t="s">
         <v>1847</v>
       </c>
@@ -30565,9 +30579,11 @@
         <v>1075</v>
       </c>
       <c r="G299" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H299" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H299" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I299" s="1" t="s">
         <v>1075</v>
       </c>
@@ -31868,7 +31884,7 @@
         <v>1647</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A348" s="1" t="s">
         <v>1526</v>
       </c>
@@ -32059,7 +32075,7 @@
         <v>1665</v>
       </c>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A355" s="1" t="s">
         <v>1528</v>
       </c>
@@ -32385,7 +32401,7 @@
         <v>1690</v>
       </c>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A367" s="1" t="s">
         <v>1531</v>
       </c>
@@ -32468,7 +32484,7 @@
         <v>1698</v>
       </c>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A370" s="1" t="s">
         <v>1924</v>
       </c>
@@ -32551,7 +32567,7 @@
         <v>1704</v>
       </c>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A373" s="1" t="s">
         <v>1926</v>
       </c>
@@ -33255,7 +33271,7 @@
         <v>1737</v>
       </c>
     </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A399" s="1" t="s">
         <v>2940</v>
       </c>
@@ -33284,7 +33300,7 @@
         <v>2942</v>
       </c>
     </row>
-    <row r="400" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A400" s="1" t="s">
         <v>2943</v>
       </c>
@@ -33340,7 +33356,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="402" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A402" s="1" t="s">
         <v>2945</v>
       </c>
@@ -33477,7 +33493,7 @@
         <v>1753</v>
       </c>
     </row>
-    <row r="407" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A407" s="1" t="s">
         <v>2946</v>
       </c>
@@ -33533,7 +33549,7 @@
         <v>1757</v>
       </c>
     </row>
-    <row r="409" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A409" s="1" t="s">
         <v>2947</v>
       </c>
@@ -35101,7 +35117,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="467" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A467" s="1" t="s">
         <v>1308</v>
       </c>
@@ -35157,7 +35173,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="469" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A469" s="1" t="s">
         <v>1310</v>
       </c>
@@ -35483,7 +35499,7 @@
         <v>1835</v>
       </c>
     </row>
-    <row r="481" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A481" s="1" t="s">
         <v>1313</v>
       </c>
@@ -35647,7 +35663,7 @@
         <v>1844</v>
       </c>
     </row>
-    <row r="487" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A487" s="1" t="s">
         <v>1391</v>
       </c>
@@ -35676,7 +35692,7 @@
         <v>1393</v>
       </c>
     </row>
-    <row r="488" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A488" s="1" t="s">
         <v>1581</v>
       </c>
@@ -35732,7 +35748,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="490" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A490" s="1" t="s">
         <v>1584</v>
       </c>
@@ -35761,7 +35777,7 @@
         <v>1585</v>
       </c>
     </row>
-    <row r="491" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A491" s="1" t="s">
         <v>1630</v>
       </c>
@@ -36249,7 +36265,7 @@
         <v>1887</v>
       </c>
     </row>
-    <row r="509" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A509" s="1" t="s">
         <v>2174</v>
       </c>
@@ -36332,7 +36348,7 @@
         <v>2786</v>
       </c>
     </row>
-    <row r="512" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A512" s="1" t="s">
         <v>1434</v>
       </c>
@@ -36388,7 +36404,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="514" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A514" s="1" t="s">
         <v>1440</v>
       </c>
@@ -36417,7 +36433,7 @@
         <v>1441</v>
       </c>
     </row>
-    <row r="515" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A515" s="1" t="s">
         <v>1443</v>
       </c>
@@ -36446,7 +36462,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="516" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A516" s="1" t="s">
         <v>2139</v>
       </c>
@@ -36475,7 +36491,7 @@
         <v>2141</v>
       </c>
     </row>
-    <row r="517" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A517" s="1" t="s">
         <v>2144</v>
       </c>
@@ -36666,7 +36682,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="524" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A524" s="1" t="s">
         <v>2147</v>
       </c>
@@ -36749,7 +36765,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="527" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A527" s="1" t="s">
         <v>2150</v>
       </c>
@@ -36940,7 +36956,7 @@
         <v>1740</v>
       </c>
     </row>
-    <row r="534" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A534" s="1" t="s">
         <v>1125</v>
       </c>
@@ -37023,7 +37039,7 @@
         <v>1932</v>
       </c>
     </row>
-    <row r="537" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A537" s="1" t="s">
         <v>1543</v>
       </c>
@@ -37052,7 +37068,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="538" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A538" s="1" t="s">
         <v>1912</v>
       </c>
@@ -37081,7 +37097,7 @@
         <v>1914</v>
       </c>
     </row>
-    <row r="539" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A539" s="1" t="s">
         <v>2589</v>
       </c>
@@ -37137,7 +37153,7 @@
         <v>1936</v>
       </c>
     </row>
-    <row r="541" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A541" s="1" t="s">
         <v>2740</v>
       </c>
@@ -37166,7 +37182,7 @@
         <v>2742</v>
       </c>
     </row>
-    <row r="542" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A542" s="1" t="s">
         <v>2849</v>
       </c>
@@ -37222,7 +37238,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="544" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A544" s="1" t="s">
         <v>2859</v>
       </c>
@@ -37251,7 +37267,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="545" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A545" s="1" t="s">
         <v>1157</v>
       </c>
@@ -37334,7 +37350,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="548" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A548" s="1" t="s">
         <v>1195</v>
       </c>
@@ -37390,7 +37406,7 @@
         <v>1944</v>
       </c>
     </row>
-    <row r="550" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A550" s="1" t="s">
         <v>1228</v>
       </c>
@@ -37473,7 +37489,7 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="553" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A553" s="1" t="s">
         <v>1233</v>
       </c>
@@ -37502,7 +37518,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="554" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A554" s="1" t="s">
         <v>1332</v>
       </c>
@@ -37531,7 +37547,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="555" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A555" s="1" t="s">
         <v>1521</v>
       </c>
@@ -37560,7 +37576,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="556" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A556" s="1" t="s">
         <v>1612</v>
       </c>
@@ -37589,7 +37605,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="557" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A557" s="1" t="s">
         <v>1614</v>
       </c>
@@ -37618,7 +37634,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="558" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A558" s="1" t="s">
         <v>1733</v>
       </c>
@@ -37782,7 +37798,7 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="564" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A564" s="1" t="s">
         <v>1734</v>
       </c>
@@ -37973,7 +37989,7 @@
         <v>1973</v>
       </c>
     </row>
-    <row r="571" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A571" s="1" t="s">
         <v>2156</v>
       </c>
@@ -38002,7 +38018,7 @@
         <v>2157</v>
       </c>
     </row>
-    <row r="572" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A572" s="1" t="s">
         <v>2158</v>
       </c>
@@ -38031,7 +38047,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="573" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A573" s="1" t="s">
         <v>2162</v>
       </c>
@@ -38060,7 +38076,7 @@
         <v>2163</v>
       </c>
     </row>
-    <row r="574" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A574" s="1" t="s">
         <v>2183</v>
       </c>
@@ -38089,7 +38105,7 @@
         <v>2184</v>
       </c>
     </row>
-    <row r="575" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A575" s="1" t="s">
         <v>2363</v>
       </c>
@@ -38199,7 +38215,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="579" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A579" s="1" t="s">
         <v>2367</v>
       </c>
@@ -38417,7 +38433,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="587" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A587" s="1" t="s">
         <v>2369</v>
       </c>
@@ -38446,7 +38462,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="588" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A588" s="1" t="s">
         <v>2372</v>
       </c>
@@ -38475,7 +38491,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="589" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A589" s="1" t="s">
         <v>2374</v>
       </c>
@@ -38558,7 +38574,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="592" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A592" s="1" t="s">
         <v>2375</v>
       </c>
@@ -38803,7 +38819,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="601" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A601" s="1" t="s">
         <v>2444</v>
       </c>
@@ -38913,7 +38929,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="605" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A605" s="1" t="s">
         <v>2447</v>
       </c>
@@ -39077,7 +39093,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="611" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A611" s="1" t="s">
         <v>2448</v>
       </c>
@@ -40780,7 +40796,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="674" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A674" s="1" t="s">
         <v>1216</v>
       </c>
@@ -40863,7 +40879,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="677" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A677" s="1" t="s">
         <v>1474</v>
       </c>
@@ -41243,7 +41259,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="691" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="691" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A691" s="1" t="s">
         <v>1879</v>
       </c>
@@ -41272,7 +41288,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="692" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="692" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A692" s="1" t="s">
         <v>1880</v>
       </c>
@@ -41382,7 +41398,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="696" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A696" s="1" t="s">
         <v>2242</v>
       </c>
@@ -41519,7 +41535,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="701" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="701" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A701" s="1" t="s">
         <v>2252</v>
       </c>
@@ -41575,7 +41591,7 @@
         <v>2146</v>
       </c>
     </row>
-    <row r="703" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="703" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A703" s="1" t="s">
         <v>2255</v>
       </c>
@@ -41658,7 +41674,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="706" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="706" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A706" s="1" t="s">
         <v>2256</v>
       </c>
@@ -41822,7 +41838,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="712" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="712" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A712" s="1" t="s">
         <v>2258</v>
       </c>
@@ -41851,7 +41867,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="713" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="713" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A713" s="1" t="s">
         <v>2259</v>
       </c>
@@ -41961,7 +41977,7 @@
         <v>2161</v>
       </c>
     </row>
-    <row r="717" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="717" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A717" s="1" t="s">
         <v>2261</v>
       </c>
@@ -42179,7 +42195,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="725" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="725" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A725" s="1" t="s">
         <v>2519</v>
       </c>
@@ -42397,7 +42413,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="733" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="733" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A733" s="1" t="s">
         <v>1134</v>
       </c>
@@ -43425,7 +43441,7 @@
         <v>2224</v>
       </c>
     </row>
-    <row r="771" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="771" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A771" s="1" t="s">
         <v>1138</v>
       </c>
@@ -43454,7 +43470,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="772" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="772" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A772" s="1" t="s">
         <v>1458</v>
       </c>
@@ -43726,7 +43742,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="782" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="782" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A782" s="1" t="s">
         <v>1884</v>
       </c>
@@ -43944,7 +43960,7 @@
         <v>2251</v>
       </c>
     </row>
-    <row r="790" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="790" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A790" s="1" t="s">
         <v>1885</v>
       </c>
@@ -43973,7 +43989,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="791" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="791" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A791" s="1" t="s">
         <v>2669</v>
       </c>
@@ -44002,7 +44018,7 @@
         <v>2671</v>
       </c>
     </row>
-    <row r="792" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="792" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A792" s="1" t="s">
         <v>2883</v>
       </c>
@@ -44031,7 +44047,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="793" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="793" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A793" s="1" t="s">
         <v>1285</v>
       </c>
@@ -44060,7 +44076,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="794" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="794" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A794" s="1" t="s">
         <v>1534</v>
       </c>
@@ -44089,7 +44105,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="795" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="795" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A795" s="1" t="s">
         <v>1813</v>
       </c>
@@ -44172,7 +44188,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="798" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="798" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A798" s="1" t="s">
         <v>1815</v>
       </c>
@@ -44444,7 +44460,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="808" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="808" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A808" s="1" t="s">
         <v>1816</v>
       </c>
@@ -44500,7 +44516,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="810" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="810" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A810" s="1" t="s">
         <v>1818</v>
       </c>
@@ -44529,7 +44545,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="811" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="811" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A811" s="1" t="s">
         <v>1819</v>
       </c>
@@ -44558,7 +44574,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="812" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="812" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A812" s="1" t="s">
         <v>1820</v>
       </c>
@@ -44587,7 +44603,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="813" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="813" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A813" s="1" t="s">
         <v>1821</v>
       </c>
@@ -45048,7 +45064,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="830" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="830" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A830" s="1" t="s">
         <v>1963</v>
       </c>
@@ -45131,7 +45147,7 @@
         <v>2308</v>
       </c>
     </row>
-    <row r="833" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="833" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A833" s="1" t="s">
         <v>2285</v>
       </c>
@@ -45160,7 +45176,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="834" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="834" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A834" s="1" t="s">
         <v>2333</v>
       </c>
@@ -45189,7 +45205,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="835" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="835" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A835" s="1" t="s">
         <v>2597</v>
       </c>
@@ -45839,7 +45855,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="859" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="859" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A859" s="1" t="s">
         <v>1784</v>
       </c>
@@ -45976,7 +45992,7 @@
         <v>2355</v>
       </c>
     </row>
-    <row r="864" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="864" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A864" s="1" t="s">
         <v>1787</v>
       </c>
@@ -46086,7 +46102,7 @@
         <v>2362</v>
       </c>
     </row>
-    <row r="868" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="868" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A868" s="1" t="s">
         <v>2303</v>
       </c>
@@ -48113,7 +48129,7 @@
         <v>2468</v>
       </c>
     </row>
-    <row r="943" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="943" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A943" s="1" t="s">
         <v>1468</v>
       </c>
@@ -48133,9 +48149,11 @@
         <v>1075</v>
       </c>
       <c r="G943" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H943" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H943" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I943" s="1" t="s">
         <v>1470</v>
       </c>
@@ -48248,7 +48266,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="948" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="948" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A948" s="1" t="s">
         <v>1648</v>
       </c>
@@ -48268,14 +48286,16 @@
         <v>1075</v>
       </c>
       <c r="G948" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H948" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H948" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I948" s="1" t="s">
         <v>1650</v>
       </c>
     </row>
-    <row r="949" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="949" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A949" s="1" t="s">
         <v>1721</v>
       </c>
@@ -48295,9 +48315,11 @@
         <v>1075</v>
       </c>
       <c r="G949" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H949" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H949" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I949" s="1" t="s">
         <v>1722</v>
       </c>
@@ -48707,7 +48729,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="965" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="965" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A965" s="1" t="s">
         <v>1808</v>
       </c>
@@ -48727,9 +48749,11 @@
         <v>1075</v>
       </c>
       <c r="G965" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H965" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H965" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I965" s="1" t="s">
         <v>1075</v>
       </c>
@@ -48896,7 +48920,7 @@
         <v>2502</v>
       </c>
     </row>
-    <row r="972" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="972" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A972" s="1" t="s">
         <v>2287</v>
       </c>
@@ -48916,9 +48940,11 @@
         <v>1075</v>
       </c>
       <c r="G972" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H972" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H972" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I972" s="1" t="s">
         <v>1075</v>
       </c>
@@ -48950,7 +48976,7 @@
         <v>2507</v>
       </c>
     </row>
-    <row r="974" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="974" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A974" s="1" t="s">
         <v>2516</v>
       </c>
@@ -48970,9 +48996,11 @@
         <v>1075</v>
       </c>
       <c r="G974" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H974" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H974" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I974" s="1" t="s">
         <v>2518</v>
       </c>
@@ -49085,7 +49113,7 @@
         <v>2515</v>
       </c>
     </row>
-    <row r="979" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="979" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A979" s="1" t="s">
         <v>2618</v>
       </c>
@@ -49105,14 +49133,16 @@
         <v>1075</v>
       </c>
       <c r="G979" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H979" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H979" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I979" s="1" t="s">
         <v>2620</v>
       </c>
     </row>
-    <row r="980" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="980" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A980" s="1" t="s">
         <v>2781</v>
       </c>
@@ -49132,9 +49162,11 @@
         <v>1075</v>
       </c>
       <c r="G980" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H980" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H980" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I980" s="1" t="s">
         <v>2782</v>
       </c>
@@ -50894,7 +50926,7 @@
         <v>2317</v>
       </c>
     </row>
-    <row r="1046" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1046" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1046" s="1" t="s">
         <v>1895</v>
       </c>
@@ -51004,7 +51036,7 @@
         <v>2588</v>
       </c>
     </row>
-    <row r="1050" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1050" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1050" s="1" t="s">
         <v>1896</v>
       </c>
@@ -51114,7 +51146,7 @@
         <v>2596</v>
       </c>
     </row>
-    <row r="1054" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1054" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1054" s="1" t="s">
         <v>1897</v>
       </c>
@@ -51413,7 +51445,7 @@
         <v>2617</v>
       </c>
     </row>
-    <row r="1065" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1065" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1065" s="1" t="s">
         <v>1898</v>
       </c>
@@ -52184,7 +52216,7 @@
         <v>2643</v>
       </c>
     </row>
-    <row r="1092" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1092" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1092" s="1" t="s">
         <v>1899</v>
       </c>
@@ -53428,7 +53460,7 @@
         <v>2709</v>
       </c>
     </row>
-    <row r="1138" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1138" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1138" s="1" t="s">
         <v>1329</v>
       </c>
@@ -53448,9 +53480,11 @@
         <v>1075</v>
       </c>
       <c r="G1138" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H1138" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H1138" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I1138" s="1" t="s">
         <v>1331</v>
       </c>
@@ -53698,7 +53732,7 @@
         <v>2726</v>
       </c>
     </row>
-    <row r="1148" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1148" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1148" s="1" t="s">
         <v>1804</v>
       </c>
@@ -53718,9 +53752,11 @@
         <v>1075</v>
       </c>
       <c r="G1148" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H1148" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H1148" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I1148" s="1" t="s">
         <v>1075</v>
       </c>
@@ -53752,7 +53788,7 @@
         <v>2731</v>
       </c>
     </row>
-    <row r="1150" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1150" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1150" s="1" t="s">
         <v>2002</v>
       </c>
@@ -53772,9 +53808,11 @@
         <v>1075</v>
       </c>
       <c r="G1150" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H1150" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H1150" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I1150" s="1" t="s">
         <v>2004</v>
       </c>
@@ -53860,7 +53898,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="1154" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1154" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1154" s="1" t="s">
         <v>2070</v>
       </c>
@@ -53880,9 +53918,11 @@
         <v>1075</v>
       </c>
       <c r="G1154" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H1154" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H1154" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I1154" s="1" t="s">
         <v>2072</v>
       </c>
@@ -53914,7 +53954,7 @@
         <v>2744</v>
       </c>
     </row>
-    <row r="1156" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1156" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1156" s="1" t="s">
         <v>2412</v>
       </c>
@@ -53934,14 +53974,16 @@
         <v>1075</v>
       </c>
       <c r="G1156" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H1156" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H1156" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I1156" s="1" t="s">
         <v>1075</v>
       </c>
     </row>
-    <row r="1157" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1157" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1157" s="1" t="s">
         <v>2413</v>
       </c>
@@ -53961,14 +54003,16 @@
         <v>1075</v>
       </c>
       <c r="G1157" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H1157" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H1157" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I1157" s="1" t="s">
         <v>2414</v>
       </c>
     </row>
-    <row r="1158" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1158" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1158" s="1" t="s">
         <v>2415</v>
       </c>
@@ -53988,14 +54032,16 @@
         <v>1075</v>
       </c>
       <c r="G1158" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H1158" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H1158" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I1158" s="1" t="s">
         <v>2416</v>
       </c>
     </row>
-    <row r="1159" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1159" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1159" s="1" t="s">
         <v>2266</v>
       </c>
@@ -54015,9 +54061,11 @@
         <v>1075</v>
       </c>
       <c r="G1159" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H1159" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H1159" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I1159" s="1" t="s">
         <v>2268</v>
       </c>
@@ -54157,7 +54205,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="1165" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1165" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1165" s="1" t="s">
         <v>2912</v>
       </c>
@@ -54177,9 +54225,11 @@
         <v>1075</v>
       </c>
       <c r="G1165" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H1165" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H1165" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I1165" s="1" t="s">
         <v>2914</v>
       </c>
@@ -54616,7 +54666,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="1182" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1182" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1182" s="1" t="s">
         <v>1179</v>
       </c>
@@ -54636,9 +54686,11 @@
         <v>1075</v>
       </c>
       <c r="G1182" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H1182" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H1182" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I1182" s="1" t="s">
         <v>1181</v>
       </c>
@@ -54859,7 +54911,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="1191" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1191" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1191" s="1" t="s">
         <v>2225</v>
       </c>
@@ -54879,14 +54931,16 @@
         <v>1075</v>
       </c>
       <c r="G1191" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H1191" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H1191" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I1191" s="1" t="s">
         <v>1075</v>
       </c>
     </row>
-    <row r="1192" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1192" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1192" s="1" t="s">
         <v>2227</v>
       </c>
@@ -54906,9 +54960,11 @@
         <v>1075</v>
       </c>
       <c r="G1192" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H1192" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H1192" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I1192" s="1" t="s">
         <v>1075</v>
       </c>

--- a/data/chapter2/FRED/subsets/species.xlsx
+++ b/data/chapter2/FRED/subsets/species.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://westernsydneyedu-my.sharepoint.com/personal/90963425_westernsydney_edu_au/Documents/PhD/code/data/chapter2/FRED/subsets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="446" documentId="8_{81FDA0CF-33C4-43D2-B8CA-CC5F96143B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD15912E-3F11-480A-ACCE-D32D195EEC2D}"/>
+  <xr:revisionPtr revIDLastSave="468" documentId="8_{81FDA0CF-33C4-43D2-B8CA-CC5F96143B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6BA45933-51B2-4564-A2E2-006DD58694A2}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="456" activeTab="3" xr2:uid="{A5444074-DC77-415C-A9E2-2BBA8270EAFC}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13983" uniqueCount="2975">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14031" uniqueCount="2975">
   <si>
     <t>F00645</t>
   </si>
@@ -25440,7 +25440,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
         <v>2386</v>
       </c>
@@ -25604,7 +25604,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
         <v>2727</v>
       </c>
@@ -26038,7 +26038,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" s="1" t="s">
         <v>1351</v>
       </c>
@@ -26058,14 +26058,16 @@
         <v>1075</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H134" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H134" s="1" t="s">
+        <v>2969</v>
+      </c>
       <c r="I134" s="1" t="s">
         <v>1075</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" s="1" t="s">
         <v>1353</v>
       </c>
@@ -26085,9 +26087,11 @@
         <v>1075</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H135" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H135" s="1" t="s">
+        <v>2969</v>
+      </c>
       <c r="I135" s="1" t="s">
         <v>1075</v>
       </c>
@@ -30177,7 +30181,7 @@
         <v>2810</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A285" s="1" t="s">
         <v>1641</v>
       </c>
@@ -30206,7 +30210,7 @@
         <v>1643</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A286" s="1" t="s">
         <v>1845</v>
       </c>
@@ -30559,7 +30563,7 @@
         <v>1568</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A299" s="1" t="s">
         <v>2881</v>
       </c>
@@ -30804,7 +30808,7 @@
         <v>1580</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A308" s="1" t="s">
         <v>1467</v>
       </c>
@@ -30824,14 +30828,16 @@
         <v>1075</v>
       </c>
       <c r="G308" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H308" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H308" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I308" s="1" t="s">
         <v>1075</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A309" s="1" t="s">
         <v>2799</v>
       </c>
@@ -30851,9 +30857,11 @@
         <v>1075</v>
       </c>
       <c r="G309" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H309" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H309" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I309" s="1" t="s">
         <v>2801</v>
       </c>
@@ -31209,7 +31217,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A323" s="1" t="s">
         <v>1888</v>
       </c>
@@ -31229,14 +31237,16 @@
         <v>1075</v>
       </c>
       <c r="G323" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H323" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H323" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I323" s="1" t="s">
         <v>1890</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A324" s="1" t="s">
         <v>1502</v>
       </c>
@@ -31256,9 +31266,11 @@
         <v>1075</v>
       </c>
       <c r="G324" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H324" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H324" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I324" s="1" t="s">
         <v>1075</v>
       </c>
@@ -31290,7 +31302,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A326" s="1" t="s">
         <v>1918</v>
       </c>
@@ -31310,14 +31322,16 @@
         <v>1075</v>
       </c>
       <c r="G326" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H326" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H326" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I326" s="1" t="s">
         <v>1920</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A327" s="1" t="s">
         <v>1921</v>
       </c>
@@ -31337,9 +31351,11 @@
         <v>1075</v>
       </c>
       <c r="G327" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H327" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H327" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I327" s="1" t="s">
         <v>1075</v>
       </c>
@@ -31587,7 +31603,7 @@
         <v>1625</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A337" s="1" t="s">
         <v>2115</v>
       </c>
@@ -31607,14 +31623,16 @@
         <v>1075</v>
       </c>
       <c r="G337" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H337" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H337" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I337" s="1" t="s">
         <v>1075</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A338" s="1" t="s">
         <v>2116</v>
       </c>
@@ -31634,9 +31652,11 @@
         <v>1075</v>
       </c>
       <c r="G338" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H338" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H338" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I338" s="1" t="s">
         <v>1075</v>
       </c>
@@ -31803,7 +31823,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A345" s="1" t="s">
         <v>2117</v>
       </c>
@@ -31823,9 +31843,11 @@
         <v>1075</v>
       </c>
       <c r="G345" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H345" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H345" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I345" s="1" t="s">
         <v>1075</v>
       </c>
@@ -32596,7 +32618,7 @@
         <v>1927</v>
       </c>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A374" s="1" t="s">
         <v>1539</v>
       </c>
@@ -32616,9 +32638,11 @@
         <v>1075</v>
       </c>
       <c r="G374" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H374" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H374" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I374" s="1" t="s">
         <v>1542</v>
       </c>
@@ -32866,7 +32890,7 @@
         <v>1720</v>
       </c>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A384" s="1" t="s">
         <v>1548</v>
       </c>
@@ -32886,9 +32910,11 @@
         <v>1075</v>
       </c>
       <c r="G384" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H384" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H384" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I384" s="1" t="s">
         <v>1075</v>
       </c>
@@ -33163,7 +33189,7 @@
         <v>1732</v>
       </c>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A395" s="1" t="s">
         <v>1551</v>
       </c>
@@ -33183,14 +33209,16 @@
         <v>1075</v>
       </c>
       <c r="G395" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H395" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H395" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I395" s="1" t="s">
         <v>1075</v>
       </c>
     </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A396" s="1" t="s">
         <v>1552</v>
       </c>
@@ -33210,9 +33238,11 @@
         <v>1075</v>
       </c>
       <c r="G396" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H396" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H396" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I396" s="1" t="s">
         <v>1075</v>
       </c>
@@ -33578,7 +33608,7 @@
         <v>2948</v>
       </c>
     </row>
-    <row r="410" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A410" s="1" t="s">
         <v>1408</v>
       </c>
@@ -33598,9 +33628,11 @@
         <v>1075</v>
       </c>
       <c r="G410" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H410" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="H410" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I410" s="1" t="s">
         <v>1411</v>
       </c>
@@ -33632,7 +33664,7 @@
         <v>1763</v>
       </c>
     </row>
-    <row r="412" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A412" s="1" t="s">
         <v>1412</v>
       </c>
@@ -33652,14 +33684,16 @@
         <v>1075</v>
       </c>
       <c r="G412" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H412" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="H412" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I412" s="1" t="s">
         <v>1413</v>
       </c>
     </row>
-    <row r="413" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A413" s="1" t="s">
         <v>1417</v>
       </c>
@@ -33679,9 +33713,11 @@
         <v>1075</v>
       </c>
       <c r="G413" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H413" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="H413" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I413" s="1" t="s">
         <v>1418</v>
       </c>
@@ -56724,7 +56760,7 @@
         <v>2896</v>
       </c>
     </row>
-    <row r="1258" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1258" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1258" s="1" t="s">
         <v>1484</v>
       </c>
@@ -56744,9 +56780,11 @@
         <v>1075</v>
       </c>
       <c r="G1258" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H1258" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H1258" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I1258" s="1" t="s">
         <v>1075</v>
       </c>
@@ -56940,7 +56978,7 @@
         <v>2906</v>
       </c>
     </row>
-    <row r="1266" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1266" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1266" s="1" t="s">
         <v>2469</v>
       </c>
@@ -56960,9 +56998,11 @@
         <v>1075</v>
       </c>
       <c r="G1266" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H1266" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H1266" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I1266" s="1" t="s">
         <v>1075</v>
       </c>
@@ -57021,7 +57061,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="1269" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1269" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1269" s="1" t="s">
         <v>2950</v>
       </c>
@@ -57041,9 +57081,11 @@
         <v>1075</v>
       </c>
       <c r="G1269" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H1269" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H1269" s="1" t="s">
+        <v>2974</v>
+      </c>
       <c r="I1269" s="1" t="s">
         <v>2952</v>
       </c>

--- a/data/chapter2/FRED/subsets/species.xlsx
+++ b/data/chapter2/FRED/subsets/species.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://westernsydneyedu-my.sharepoint.com/personal/90963425_westernsydney_edu_au/Documents/PhD/code/data/chapter2/FRED/subsets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="468" documentId="8_{81FDA0CF-33C4-43D2-B8CA-CC5F96143B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6BA45933-51B2-4564-A2E2-006DD58694A2}"/>
+  <xr:revisionPtr revIDLastSave="526" documentId="8_{81FDA0CF-33C4-43D2-B8CA-CC5F96143B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D97DE75E-1679-42F4-9C00-D4BEAF07C48B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="456" activeTab="3" xr2:uid="{A5444074-DC77-415C-A9E2-2BBA8270EAFC}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14031" uniqueCount="2975">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14087" uniqueCount="2977">
   <si>
     <t>F00645</t>
   </si>
@@ -8986,14 +8986,43 @@
     <t>Luke</t>
   </si>
   <si>
-    <t>Brundrett &amp; Tedersoo 2018</t>
+    <r>
+      <t xml:space="preserve">(Soudzilovskaia </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>et al.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, 2020)</t>
+    </r>
+  </si>
+  <si>
+    <t>(Soudzilovskaia et al., 2020)</t>
+  </si>
+  <si>
+    <t>(Brundrett and Tedersoo, 2018)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -9130,6 +9159,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -9723,6 +9760,9 @@
     <filterColumn colId="6">
       <filters blank="1"/>
     </filterColumn>
+    <filterColumn colId="7">
+      <filters blank="1"/>
+    </filterColumn>
   </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A38:I1294">
     <sortCondition ref="C2:C1302"/>
@@ -22373,7 +22413,7 @@
     <col min="4" max="4" width="26.453125" customWidth="1"/>
     <col min="5" max="5" width="17.08984375" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="17.26953125" customWidth="1"/>
-    <col min="8" max="8" width="23" customWidth="1"/>
+    <col min="8" max="8" width="26.54296875" customWidth="1"/>
     <col min="9" max="9" width="89.54296875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -23437,7 +23477,7 @@
         <v>2</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>1075</v>
@@ -23547,7 +23587,7 @@
         <v>2</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>2132</v>
@@ -23576,7 +23616,7 @@
         <v>2</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>2134</v>
@@ -23767,7 +23807,7 @@
         <v>2</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>1075</v>
@@ -23796,7 +23836,7 @@
         <v>2</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>1075</v>
@@ -24095,7 +24135,7 @@
         <v>2</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>1075</v>
@@ -24259,7 +24299,7 @@
         <v>2</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>2280</v>
@@ -24531,7 +24571,7 @@
         <v>2</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>2284</v>
@@ -24560,7 +24600,7 @@
         <v>2</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I79" s="1" t="s">
         <v>2909</v>
@@ -24616,7 +24656,7 @@
         <v>2</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I81" s="1" t="s">
         <v>2291</v>
@@ -24645,7 +24685,7 @@
         <v>2</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>2868</v>
@@ -24674,7 +24714,7 @@
         <v>2</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I83" s="1" t="s">
         <v>1075</v>
@@ -24757,7 +24797,7 @@
         <v>2</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>2010</v>
@@ -25056,7 +25096,7 @@
         <v>2</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I97" s="1" t="s">
         <v>1075</v>
@@ -25463,7 +25503,7 @@
         <v>2</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I112" s="1" t="s">
         <v>2388</v>
@@ -25627,7 +25667,7 @@
         <v>2</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I118" s="1" t="s">
         <v>2729</v>
@@ -26061,7 +26101,7 @@
         <v>2</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>2969</v>
+        <v>2975</v>
       </c>
       <c r="I134" s="1" t="s">
         <v>1075</v>
@@ -26090,7 +26130,7 @@
         <v>2</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>2969</v>
+        <v>2975</v>
       </c>
       <c r="I135" s="1" t="s">
         <v>1075</v>
@@ -26146,7 +26186,7 @@
         <v>2</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I137" s="1" t="s">
         <v>1280</v>
@@ -26283,7 +26323,7 @@
         <v>2</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I142" s="1" t="s">
         <v>1075</v>
@@ -26366,7 +26406,7 @@
         <v>2</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I145" s="1" t="s">
         <v>1473</v>
@@ -26422,7 +26462,7 @@
         <v>2</v>
       </c>
       <c r="H147" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I147" s="1" t="s">
         <v>1075</v>
@@ -26451,7 +26491,7 @@
         <v>2</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I148" s="1" t="s">
         <v>1608</v>
@@ -26858,7 +26898,7 @@
         <v>2</v>
       </c>
       <c r="H163" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I163" s="1" t="s">
         <v>1610</v>
@@ -26887,7 +26927,7 @@
         <v>2</v>
       </c>
       <c r="H164" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I164" s="1" t="s">
         <v>1075</v>
@@ -26943,7 +26983,7 @@
         <v>2</v>
       </c>
       <c r="H166" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I166" s="1" t="s">
         <v>1759</v>
@@ -27458,7 +27498,7 @@
         <v>2</v>
       </c>
       <c r="H185" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I185" s="1" t="s">
         <v>1761</v>
@@ -27676,7 +27716,7 @@
         <v>2</v>
       </c>
       <c r="H193" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I193" s="1" t="s">
         <v>1075</v>
@@ -27705,7 +27745,7 @@
         <v>2</v>
       </c>
       <c r="H194" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I194" s="1" t="s">
         <v>1931</v>
@@ -27896,7 +27936,7 @@
         <v>2</v>
       </c>
       <c r="H201" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I201" s="1" t="s">
         <v>1075</v>
@@ -28195,7 +28235,7 @@
         <v>2</v>
       </c>
       <c r="H212" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I212" s="1" t="s">
         <v>1075</v>
@@ -28386,7 +28426,7 @@
         <v>2</v>
       </c>
       <c r="H219" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I219" s="1" t="s">
         <v>1075</v>
@@ -28442,7 +28482,7 @@
         <v>2</v>
       </c>
       <c r="H221" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I221" s="1" t="s">
         <v>1075</v>
@@ -28660,7 +28700,7 @@
         <v>2</v>
       </c>
       <c r="H229" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I229" s="1" t="s">
         <v>1939</v>
@@ -28689,7 +28729,7 @@
         <v>2</v>
       </c>
       <c r="H230" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I230" s="1" t="s">
         <v>1941</v>
@@ -28826,7 +28866,7 @@
         <v>2</v>
       </c>
       <c r="H235" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I235" s="1" t="s">
         <v>1075</v>
@@ -28855,7 +28895,7 @@
         <v>2</v>
       </c>
       <c r="H236" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I236" s="1" t="s">
         <v>1075</v>
@@ -28884,7 +28924,7 @@
         <v>2</v>
       </c>
       <c r="H237" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I237" s="1" t="s">
         <v>1075</v>
@@ -28913,7 +28953,7 @@
         <v>2</v>
       </c>
       <c r="H238" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I238" s="1" t="s">
         <v>1948</v>
@@ -29050,7 +29090,7 @@
         <v>2</v>
       </c>
       <c r="H243" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I243" s="1" t="s">
         <v>1950</v>
@@ -29268,7 +29308,7 @@
         <v>2</v>
       </c>
       <c r="H251" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I251" s="1" t="s">
         <v>1952</v>
@@ -29621,7 +29661,7 @@
         <v>2</v>
       </c>
       <c r="H264" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I264" s="1" t="s">
         <v>1075</v>
@@ -29785,7 +29825,7 @@
         <v>2</v>
       </c>
       <c r="H270" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I270" s="1" t="s">
         <v>1075</v>
@@ -29814,7 +29854,7 @@
         <v>2</v>
       </c>
       <c r="H271" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I271" s="1" t="s">
         <v>1075</v>
@@ -29897,7 +29937,7 @@
         <v>2</v>
       </c>
       <c r="H274" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I274" s="1" t="s">
         <v>2082</v>
@@ -29980,7 +30020,7 @@
         <v>2</v>
       </c>
       <c r="H277" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I277" s="1" t="s">
         <v>2423</v>
@@ -30090,7 +30130,7 @@
         <v>2</v>
       </c>
       <c r="H281" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I281" s="1" t="s">
         <v>2761</v>
@@ -30119,7 +30159,7 @@
         <v>2</v>
       </c>
       <c r="H282" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I282" s="1" t="s">
         <v>2804</v>
@@ -30175,7 +30215,7 @@
         <v>2</v>
       </c>
       <c r="H284" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I284" s="1" t="s">
         <v>2810</v>
@@ -30204,7 +30244,7 @@
         <v>2</v>
       </c>
       <c r="H285" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I285" s="1" t="s">
         <v>1643</v>
@@ -30233,7 +30273,7 @@
         <v>2</v>
       </c>
       <c r="H286" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I286" s="1" t="s">
         <v>1847</v>
@@ -30586,7 +30626,7 @@
         <v>2</v>
       </c>
       <c r="H299" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I299" s="1" t="s">
         <v>1075</v>
@@ -30831,7 +30871,7 @@
         <v>2</v>
       </c>
       <c r="H308" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I308" s="1" t="s">
         <v>1075</v>
@@ -30860,7 +30900,7 @@
         <v>2</v>
       </c>
       <c r="H309" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I309" s="1" t="s">
         <v>2801</v>
@@ -31240,7 +31280,7 @@
         <v>2</v>
       </c>
       <c r="H323" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I323" s="1" t="s">
         <v>1890</v>
@@ -31269,7 +31309,7 @@
         <v>2</v>
       </c>
       <c r="H324" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I324" s="1" t="s">
         <v>1075</v>
@@ -31325,7 +31365,7 @@
         <v>2</v>
       </c>
       <c r="H326" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I326" s="1" t="s">
         <v>1920</v>
@@ -31354,7 +31394,7 @@
         <v>2</v>
       </c>
       <c r="H327" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I327" s="1" t="s">
         <v>1075</v>
@@ -31626,7 +31666,7 @@
         <v>2</v>
       </c>
       <c r="H337" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I337" s="1" t="s">
         <v>1075</v>
@@ -31655,7 +31695,7 @@
         <v>2</v>
       </c>
       <c r="H338" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I338" s="1" t="s">
         <v>1075</v>
@@ -31846,7 +31886,7 @@
         <v>2</v>
       </c>
       <c r="H345" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I345" s="1" t="s">
         <v>1075</v>
@@ -31929,7 +31969,7 @@
         <v>1</v>
       </c>
       <c r="H348" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I348" s="1" t="s">
         <v>1527</v>
@@ -32120,7 +32160,7 @@
         <v>1</v>
       </c>
       <c r="H355" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I355" s="1" t="s">
         <v>1529</v>
@@ -32446,7 +32486,7 @@
         <v>1</v>
       </c>
       <c r="H367" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I367" s="1" t="s">
         <v>1075</v>
@@ -32529,7 +32569,7 @@
         <v>1</v>
       </c>
       <c r="H370" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I370" s="1" t="s">
         <v>1925</v>
@@ -32612,7 +32652,7 @@
         <v>1</v>
       </c>
       <c r="H373" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I373" s="1" t="s">
         <v>1927</v>
@@ -32641,7 +32681,7 @@
         <v>2</v>
       </c>
       <c r="H374" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I374" s="1" t="s">
         <v>1542</v>
@@ -32913,7 +32953,7 @@
         <v>2</v>
       </c>
       <c r="H384" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I384" s="1" t="s">
         <v>1075</v>
@@ -33212,7 +33252,7 @@
         <v>2</v>
       </c>
       <c r="H395" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I395" s="1" t="s">
         <v>1075</v>
@@ -33241,7 +33281,7 @@
         <v>2</v>
       </c>
       <c r="H396" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I396" s="1" t="s">
         <v>1075</v>
@@ -33324,7 +33364,7 @@
         <v>2</v>
       </c>
       <c r="H399" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I399" s="1" t="s">
         <v>2942</v>
@@ -33353,7 +33393,7 @@
         <v>2</v>
       </c>
       <c r="H400" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I400" s="1" t="s">
         <v>2944</v>
@@ -33409,7 +33449,7 @@
         <v>2</v>
       </c>
       <c r="H402" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I402" s="1" t="s">
         <v>1075</v>
@@ -33546,7 +33586,7 @@
         <v>2</v>
       </c>
       <c r="H407" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I407" s="1" t="s">
         <v>1075</v>
@@ -33602,7 +33642,7 @@
         <v>2</v>
       </c>
       <c r="H409" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I409" s="1" t="s">
         <v>2948</v>
@@ -33631,7 +33671,7 @@
         <v>4</v>
       </c>
       <c r="H410" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I410" s="1" t="s">
         <v>1411</v>
@@ -33687,7 +33727,7 @@
         <v>4</v>
       </c>
       <c r="H412" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I412" s="1" t="s">
         <v>1413</v>
@@ -33716,7 +33756,7 @@
         <v>4</v>
       </c>
       <c r="H413" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I413" s="1" t="s">
         <v>1418</v>
@@ -34147,9 +34187,11 @@
         <v>1075</v>
       </c>
       <c r="G429" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H429" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H429" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="I429" s="1" t="s">
         <v>1629</v>
       </c>
@@ -34336,9 +34378,11 @@
         <v>1075</v>
       </c>
       <c r="G436" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H436" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="H436" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="I436" s="1" t="s">
         <v>2662</v>
       </c>
@@ -34498,9 +34542,11 @@
         <v>1075</v>
       </c>
       <c r="G442" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H442" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="H442" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="I442" s="1" t="s">
         <v>2676</v>
       </c>
@@ -34660,9 +34706,11 @@
         <v>1075</v>
       </c>
       <c r="G448" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H448" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H448" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="I448" s="1" t="s">
         <v>1075</v>
       </c>
@@ -34822,9 +34870,11 @@
         <v>1075</v>
       </c>
       <c r="G454" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H454" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H454" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="I454" s="1" t="s">
         <v>1075</v>
       </c>
@@ -34929,10 +34979,12 @@
       <c r="F458" s="1" t="s">
         <v>1075</v>
       </c>
-      <c r="G458" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H458" s="1"/>
+      <c r="G458" t="s">
+        <v>2</v>
+      </c>
+      <c r="H458" t="s">
+        <v>2975</v>
+      </c>
       <c r="I458" s="1" t="s">
         <v>1075</v>
       </c>
@@ -35065,9 +35117,11 @@
         <v>1075</v>
       </c>
       <c r="G463" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H463" s="1"/>
+        <v>6</v>
+      </c>
+      <c r="H463" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="I463" s="1" t="s">
         <v>1755</v>
       </c>
@@ -35176,7 +35230,7 @@
         <v>2</v>
       </c>
       <c r="H467" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I467" s="1" t="s">
         <v>1075</v>
@@ -35232,7 +35286,7 @@
         <v>2</v>
       </c>
       <c r="H469" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I469" s="1" t="s">
         <v>1311</v>
@@ -35558,7 +35612,7 @@
         <v>2</v>
       </c>
       <c r="H481" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I481" s="1" t="s">
         <v>1314</v>
@@ -35722,7 +35776,7 @@
         <v>2</v>
       </c>
       <c r="H487" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I487" s="1" t="s">
         <v>1393</v>
@@ -35751,7 +35805,7 @@
         <v>2</v>
       </c>
       <c r="H488" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I488" s="1" t="s">
         <v>1583</v>
@@ -35807,7 +35861,7 @@
         <v>2</v>
       </c>
       <c r="H490" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I490" s="1" t="s">
         <v>1585</v>
@@ -35836,7 +35890,7 @@
         <v>2</v>
       </c>
       <c r="H491" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I491" s="1" t="s">
         <v>1632</v>
@@ -36324,7 +36378,7 @@
         <v>5</v>
       </c>
       <c r="H509" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I509" s="1" t="s">
         <v>1075</v>
@@ -36407,7 +36461,7 @@
         <v>1</v>
       </c>
       <c r="H512" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I512" s="1" t="s">
         <v>1075</v>
@@ -36463,7 +36517,7 @@
         <v>1</v>
       </c>
       <c r="H514" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I514" s="1" t="s">
         <v>1441</v>
@@ -36492,7 +36546,7 @@
         <v>1</v>
       </c>
       <c r="H515" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I515" s="1" t="s">
         <v>1075</v>
@@ -36521,7 +36575,7 @@
         <v>1</v>
       </c>
       <c r="H516" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I516" s="1" t="s">
         <v>2141</v>
@@ -36550,7 +36604,7 @@
         <v>1</v>
       </c>
       <c r="H517" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I517" s="1" t="s">
         <v>2145</v>
@@ -36741,7 +36795,7 @@
         <v>1</v>
       </c>
       <c r="H524" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I524" s="1" t="s">
         <v>2148</v>
@@ -36824,7 +36878,7 @@
         <v>1</v>
       </c>
       <c r="H527" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I527" s="1" t="s">
         <v>2151</v>
@@ -37015,7 +37069,7 @@
         <v>2</v>
       </c>
       <c r="H534" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I534" s="1" t="s">
         <v>1129</v>
@@ -37098,7 +37152,7 @@
         <v>2</v>
       </c>
       <c r="H537" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I537" s="1" t="s">
         <v>1545</v>
@@ -37127,7 +37181,7 @@
         <v>2</v>
       </c>
       <c r="H538" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I538" s="1" t="s">
         <v>1914</v>
@@ -37156,7 +37210,7 @@
         <v>2</v>
       </c>
       <c r="H539" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I539" s="1" t="s">
         <v>2591</v>
@@ -37212,7 +37266,7 @@
         <v>2</v>
       </c>
       <c r="H541" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I541" s="1" t="s">
         <v>2742</v>
@@ -37241,7 +37295,7 @@
         <v>2</v>
       </c>
       <c r="H542" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I542" s="1" t="s">
         <v>1075</v>
@@ -37297,7 +37351,7 @@
         <v>2</v>
       </c>
       <c r="H544" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I544" s="1" t="s">
         <v>1075</v>
@@ -37326,7 +37380,7 @@
         <v>2</v>
       </c>
       <c r="H545" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I545" s="1" t="s">
         <v>1159</v>
@@ -37409,7 +37463,7 @@
         <v>2</v>
       </c>
       <c r="H548" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I548" s="1" t="s">
         <v>1197</v>
@@ -37465,7 +37519,7 @@
         <v>2</v>
       </c>
       <c r="H550" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I550" s="1" t="s">
         <v>1230</v>
@@ -37548,7 +37602,7 @@
         <v>2</v>
       </c>
       <c r="H553" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I553" s="1" t="s">
         <v>1234</v>
@@ -37577,7 +37631,7 @@
         <v>2</v>
       </c>
       <c r="H554" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I554" s="1" t="s">
         <v>1075</v>
@@ -37606,7 +37660,7 @@
         <v>2</v>
       </c>
       <c r="H555" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I555" s="1" t="s">
         <v>1075</v>
@@ -37635,7 +37689,7 @@
         <v>2</v>
       </c>
       <c r="H556" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I556" s="1" t="s">
         <v>1075</v>
@@ -37664,7 +37718,7 @@
         <v>2</v>
       </c>
       <c r="H557" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I557" s="1" t="s">
         <v>1075</v>
@@ -37693,7 +37747,7 @@
         <v>2</v>
       </c>
       <c r="H558" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I558" s="1" t="s">
         <v>1075</v>
@@ -37857,7 +37911,7 @@
         <v>2</v>
       </c>
       <c r="H564" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I564" s="1" t="s">
         <v>1075</v>
@@ -38048,7 +38102,7 @@
         <v>2</v>
       </c>
       <c r="H571" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I571" s="1" t="s">
         <v>2157</v>
@@ -38077,7 +38131,7 @@
         <v>2</v>
       </c>
       <c r="H572" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I572" s="1" t="s">
         <v>1075</v>
@@ -38106,7 +38160,7 @@
         <v>2</v>
       </c>
       <c r="H573" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I573" s="1" t="s">
         <v>2163</v>
@@ -38135,7 +38189,7 @@
         <v>2</v>
       </c>
       <c r="H574" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I574" s="1" t="s">
         <v>2184</v>
@@ -38164,7 +38218,7 @@
         <v>2</v>
       </c>
       <c r="H575" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I575" s="1" t="s">
         <v>1075</v>
@@ -38274,7 +38328,7 @@
         <v>2</v>
       </c>
       <c r="H579" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I579" s="1" t="s">
         <v>2368</v>
@@ -38492,7 +38546,7 @@
         <v>2</v>
       </c>
       <c r="H587" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I587" s="1" t="s">
         <v>1075</v>
@@ -38521,7 +38575,7 @@
         <v>2</v>
       </c>
       <c r="H588" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I588" s="1" t="s">
         <v>1075</v>
@@ -38550,7 +38604,7 @@
         <v>2</v>
       </c>
       <c r="H589" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I589" s="1" t="s">
         <v>1075</v>
@@ -38633,7 +38687,7 @@
         <v>2</v>
       </c>
       <c r="H592" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I592" s="1" t="s">
         <v>1075</v>
@@ -38878,7 +38932,7 @@
         <v>2</v>
       </c>
       <c r="H601" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I601" s="1" t="s">
         <v>2446</v>
@@ -38988,7 +39042,7 @@
         <v>2</v>
       </c>
       <c r="H605" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I605" s="1" t="s">
         <v>1075</v>
@@ -39152,7 +39206,7 @@
         <v>2</v>
       </c>
       <c r="H611" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I611" s="1" t="s">
         <v>1075</v>
@@ -40855,7 +40909,7 @@
         <v>2</v>
       </c>
       <c r="H674" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I674" s="1" t="s">
         <v>1220</v>
@@ -40938,7 +40992,7 @@
         <v>2</v>
       </c>
       <c r="H677" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I677" s="1" t="s">
         <v>1075</v>
@@ -41318,7 +41372,7 @@
         <v>2</v>
       </c>
       <c r="H691" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I691" s="1" t="s">
         <v>1075</v>
@@ -41347,7 +41401,7 @@
         <v>2</v>
       </c>
       <c r="H692" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I692" s="1" t="s">
         <v>1075</v>
@@ -41457,7 +41511,7 @@
         <v>2</v>
       </c>
       <c r="H696" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I696" s="1" t="s">
         <v>1075</v>
@@ -41594,7 +41648,7 @@
         <v>2</v>
       </c>
       <c r="H701" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I701" s="1" t="s">
         <v>2254</v>
@@ -41650,7 +41704,7 @@
         <v>2</v>
       </c>
       <c r="H703" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I703" s="1" t="s">
         <v>1075</v>
@@ -41733,7 +41787,7 @@
         <v>2</v>
       </c>
       <c r="H706" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I706" s="1" t="s">
         <v>2257</v>
@@ -41897,7 +41951,7 @@
         <v>2</v>
       </c>
       <c r="H712" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I712" s="1" t="s">
         <v>1075</v>
@@ -41926,7 +41980,7 @@
         <v>2</v>
       </c>
       <c r="H713" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I713" s="1" t="s">
         <v>2260</v>
@@ -42036,7 +42090,7 @@
         <v>2</v>
       </c>
       <c r="H717" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I717" s="1" t="s">
         <v>2262</v>
@@ -42254,7 +42308,7 @@
         <v>2</v>
       </c>
       <c r="H725" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I725" s="1" t="s">
         <v>2521</v>
@@ -42472,7 +42526,7 @@
         <v>2</v>
       </c>
       <c r="H733" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I733" s="1" t="s">
         <v>1137</v>
@@ -43500,7 +43554,7 @@
         <v>2</v>
       </c>
       <c r="H771" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I771" s="1" t="s">
         <v>1075</v>
@@ -43529,7 +43583,7 @@
         <v>2</v>
       </c>
       <c r="H772" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I772" s="1" t="s">
         <v>1460</v>
@@ -43801,7 +43855,7 @@
         <v>2</v>
       </c>
       <c r="H782" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I782" s="1" t="s">
         <v>1075</v>
@@ -44019,7 +44073,7 @@
         <v>2</v>
       </c>
       <c r="H790" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I790" s="1" t="s">
         <v>1075</v>
@@ -44048,7 +44102,7 @@
         <v>2</v>
       </c>
       <c r="H791" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I791" s="1" t="s">
         <v>2671</v>
@@ -44077,7 +44131,7 @@
         <v>2</v>
       </c>
       <c r="H792" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I792" s="1" t="s">
         <v>1075</v>
@@ -44106,7 +44160,7 @@
         <v>2</v>
       </c>
       <c r="H793" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I793" s="1" t="s">
         <v>1075</v>
@@ -44135,7 +44189,7 @@
         <v>2</v>
       </c>
       <c r="H794" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I794" s="1" t="s">
         <v>1075</v>
@@ -44164,7 +44218,7 @@
         <v>2</v>
       </c>
       <c r="H795" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I795" s="1" t="s">
         <v>1075</v>
@@ -44247,7 +44301,7 @@
         <v>2</v>
       </c>
       <c r="H798" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I798" s="1" t="s">
         <v>1075</v>
@@ -44519,7 +44573,7 @@
         <v>2</v>
       </c>
       <c r="H808" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I808" s="1" t="s">
         <v>1817</v>
@@ -44575,7 +44629,7 @@
         <v>2</v>
       </c>
       <c r="H810" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I810" s="1" t="s">
         <v>1075</v>
@@ -44604,7 +44658,7 @@
         <v>2</v>
       </c>
       <c r="H811" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I811" s="1" t="s">
         <v>1075</v>
@@ -44633,7 +44687,7 @@
         <v>2</v>
       </c>
       <c r="H812" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I812" s="1" t="s">
         <v>1075</v>
@@ -44662,7 +44716,7 @@
         <v>2</v>
       </c>
       <c r="H813" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I813" s="1" t="s">
         <v>1075</v>
@@ -45123,7 +45177,7 @@
         <v>2</v>
       </c>
       <c r="H830" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I830" s="1" t="s">
         <v>1964</v>
@@ -45206,7 +45260,7 @@
         <v>2</v>
       </c>
       <c r="H833" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I833" s="1" t="s">
         <v>1075</v>
@@ -45235,7 +45289,7 @@
         <v>2</v>
       </c>
       <c r="H834" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I834" s="1" t="s">
         <v>1075</v>
@@ -45264,7 +45318,7 @@
         <v>2</v>
       </c>
       <c r="H835" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I835" s="1" t="s">
         <v>2598</v>
@@ -45914,7 +45968,7 @@
         <v>2</v>
       </c>
       <c r="H859" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I859" s="1" t="s">
         <v>1075</v>
@@ -46051,7 +46105,7 @@
         <v>2</v>
       </c>
       <c r="H864" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I864" s="1" t="s">
         <v>1788</v>
@@ -46161,7 +46215,7 @@
         <v>2</v>
       </c>
       <c r="H868" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I868" s="1" t="s">
         <v>2305</v>
@@ -48188,7 +48242,7 @@
         <v>2</v>
       </c>
       <c r="H943" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I943" s="1" t="s">
         <v>1470</v>
@@ -48325,7 +48379,7 @@
         <v>2</v>
       </c>
       <c r="H948" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I948" s="1" t="s">
         <v>1650</v>
@@ -48354,7 +48408,7 @@
         <v>2</v>
       </c>
       <c r="H949" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I949" s="1" t="s">
         <v>1722</v>
@@ -48788,7 +48842,7 @@
         <v>2</v>
       </c>
       <c r="H965" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I965" s="1" t="s">
         <v>1075</v>
@@ -48979,7 +49033,7 @@
         <v>2</v>
       </c>
       <c r="H972" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I972" s="1" t="s">
         <v>1075</v>
@@ -49035,7 +49089,7 @@
         <v>2</v>
       </c>
       <c r="H974" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I974" s="1" t="s">
         <v>2518</v>
@@ -49172,7 +49226,7 @@
         <v>2</v>
       </c>
       <c r="H979" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I979" s="1" t="s">
         <v>2620</v>
@@ -49201,7 +49255,7 @@
         <v>2</v>
       </c>
       <c r="H980" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I980" s="1" t="s">
         <v>2782</v>
@@ -50985,7 +51039,7 @@
         <v>5</v>
       </c>
       <c r="H1046" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I1046" s="1" t="s">
         <v>1075</v>
@@ -51095,7 +51149,7 @@
         <v>5</v>
       </c>
       <c r="H1050" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I1050" s="1" t="s">
         <v>1075</v>
@@ -51205,7 +51259,7 @@
         <v>5</v>
       </c>
       <c r="H1054" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I1054" s="1" t="s">
         <v>1075</v>
@@ -51504,7 +51558,7 @@
         <v>5</v>
       </c>
       <c r="H1065" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I1065" s="1" t="s">
         <v>1075</v>
@@ -52275,7 +52329,7 @@
         <v>5</v>
       </c>
       <c r="H1092" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I1092" s="1" t="s">
         <v>1075</v>
@@ -52713,7 +52767,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="1109" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1109" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1109" s="1" t="s">
         <v>1699</v>
       </c>
@@ -52733,14 +52787,16 @@
         <v>1075</v>
       </c>
       <c r="G1109" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H1109" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H1109" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="I1109" s="1" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="1110" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1110" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1110" s="1" t="s">
         <v>2583</v>
       </c>
@@ -52760,9 +52816,11 @@
         <v>1075</v>
       </c>
       <c r="G1110" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H1110" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H1110" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="I1110" s="1" t="s">
         <v>1075</v>
       </c>
@@ -52794,7 +52852,7 @@
         <v>2673</v>
       </c>
     </row>
-    <row r="1112" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1112" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1112" s="1" t="s">
         <v>2584</v>
       </c>
@@ -52814,9 +52872,11 @@
         <v>1075</v>
       </c>
       <c r="G1112" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H1112" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H1112" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="I1112" s="1" t="s">
         <v>2585</v>
       </c>
@@ -53118,7 +53178,7 @@
         <v>2687</v>
       </c>
     </row>
-    <row r="1124" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1124" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1124" s="1" t="s">
         <v>2664</v>
       </c>
@@ -53138,9 +53198,11 @@
         <v>1075</v>
       </c>
       <c r="G1124" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H1124" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H1124" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="I1124" s="1" t="s">
         <v>2665</v>
       </c>
@@ -53388,7 +53450,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="1134" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1134" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1134" s="1" t="s">
         <v>2768</v>
       </c>
@@ -53408,9 +53470,11 @@
         <v>1075</v>
       </c>
       <c r="G1134" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H1134" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H1134" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="I1134" s="1" t="s">
         <v>2769</v>
       </c>
@@ -53519,7 +53583,7 @@
         <v>2</v>
       </c>
       <c r="H1138" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I1138" s="1" t="s">
         <v>1331</v>
@@ -53791,7 +53855,7 @@
         <v>2</v>
       </c>
       <c r="H1148" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I1148" s="1" t="s">
         <v>1075</v>
@@ -53847,7 +53911,7 @@
         <v>2</v>
       </c>
       <c r="H1150" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I1150" s="1" t="s">
         <v>2004</v>
@@ -53957,7 +54021,7 @@
         <v>2</v>
       </c>
       <c r="H1154" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I1154" s="1" t="s">
         <v>2072</v>
@@ -54013,7 +54077,7 @@
         <v>2</v>
       </c>
       <c r="H1156" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I1156" s="1" t="s">
         <v>1075</v>
@@ -54042,7 +54106,7 @@
         <v>2</v>
       </c>
       <c r="H1157" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I1157" s="1" t="s">
         <v>2414</v>
@@ -54071,7 +54135,7 @@
         <v>2</v>
       </c>
       <c r="H1158" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I1158" s="1" t="s">
         <v>2416</v>
@@ -54100,7 +54164,7 @@
         <v>2</v>
       </c>
       <c r="H1159" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I1159" s="1" t="s">
         <v>2268</v>
@@ -54264,7 +54328,7 @@
         <v>2</v>
       </c>
       <c r="H1165" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I1165" s="1" t="s">
         <v>2914</v>
@@ -54648,7 +54712,7 @@
         <v>2780</v>
       </c>
     </row>
-    <row r="1180" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1180" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1180" s="1" t="s">
         <v>2688</v>
       </c>
@@ -54668,9 +54732,11 @@
         <v>1075</v>
       </c>
       <c r="G1180" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H1180" s="1"/>
+        <v>3</v>
+      </c>
+      <c r="H1180" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="I1180" s="1" t="s">
         <v>1075</v>
       </c>
@@ -54725,7 +54791,7 @@
         <v>2</v>
       </c>
       <c r="H1182" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I1182" s="1" t="s">
         <v>1181</v>
@@ -54970,7 +55036,7 @@
         <v>2</v>
       </c>
       <c r="H1191" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I1191" s="1" t="s">
         <v>1075</v>
@@ -54999,7 +55065,7 @@
         <v>2</v>
       </c>
       <c r="H1192" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I1192" s="1" t="s">
         <v>1075</v>
@@ -55113,7 +55179,7 @@
         <v>2808</v>
       </c>
     </row>
-    <row r="1197" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1197" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1197" s="1" t="s">
         <v>2503</v>
       </c>
@@ -55133,9 +55199,11 @@
         <v>1075</v>
       </c>
       <c r="G1197" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H1197" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H1197" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="I1197" s="1" t="s">
         <v>2505</v>
       </c>
@@ -55842,7 +55910,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="1224" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1224" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1224" s="1" t="s">
         <v>2549</v>
       </c>
@@ -55862,9 +55930,11 @@
         <v>1075</v>
       </c>
       <c r="G1224" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H1224" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H1224" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="I1224" s="1" t="s">
         <v>2551</v>
       </c>
@@ -56274,7 +56344,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="1240" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1240" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1240" s="1" t="s">
         <v>1154</v>
       </c>
@@ -56294,9 +56364,11 @@
         <v>1075</v>
       </c>
       <c r="G1240" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H1240" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H1240" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="I1240" s="1" t="s">
         <v>1075</v>
       </c>
@@ -56382,7 +56454,7 @@
         <v>2873</v>
       </c>
     </row>
-    <row r="1244" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1244" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1244" s="1" t="s">
         <v>2478</v>
       </c>
@@ -56402,9 +56474,11 @@
         <v>1075</v>
       </c>
       <c r="G1244" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H1244" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H1244" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="I1244" s="1" t="s">
         <v>1075</v>
       </c>
@@ -56463,7 +56537,7 @@
         <v>2880</v>
       </c>
     </row>
-    <row r="1247" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1247" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1247" s="1" t="s">
         <v>2745</v>
       </c>
@@ -56483,14 +56557,16 @@
         <v>1075</v>
       </c>
       <c r="G1247" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H1247" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H1247" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="I1247" s="1" t="s">
         <v>2748</v>
       </c>
     </row>
-    <row r="1248" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1248" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1248" s="1" t="s">
         <v>2749</v>
       </c>
@@ -56510,9 +56586,11 @@
         <v>1075</v>
       </c>
       <c r="G1248" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H1248" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H1248" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="I1248" s="1" t="s">
         <v>2750</v>
       </c>
@@ -56783,7 +56861,7 @@
         <v>2</v>
       </c>
       <c r="H1258" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I1258" s="1" t="s">
         <v>1075</v>
@@ -57001,7 +57079,7 @@
         <v>2</v>
       </c>
       <c r="H1266" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I1266" s="1" t="s">
         <v>1075</v>
@@ -57084,7 +57162,7 @@
         <v>2</v>
       </c>
       <c r="H1269" s="1" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="I1269" s="1" t="s">
         <v>2952</v>
@@ -57252,7 +57330,7 @@
         <v>2925</v>
       </c>
     </row>
-    <row r="1276" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1276" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1276" s="1" t="s">
         <v>2897</v>
       </c>
@@ -57272,9 +57350,11 @@
         <v>1075</v>
       </c>
       <c r="G1276" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H1276" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H1276" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="I1276" s="1" t="s">
         <v>2901</v>
       </c>
@@ -57306,7 +57386,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="1278" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1278" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1278" s="1" t="s">
         <v>1900</v>
       </c>
@@ -57326,9 +57406,11 @@
         <v>1075</v>
       </c>
       <c r="G1278" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H1278" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H1278" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="I1278" s="1" t="s">
         <v>1075</v>
       </c>
@@ -57549,7 +57631,7 @@
         <v>2939</v>
       </c>
     </row>
-    <row r="1287" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1287" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1287" s="1" t="s">
         <v>1874</v>
       </c>
@@ -57569,14 +57651,16 @@
         <v>1075</v>
       </c>
       <c r="G1287" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H1287" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H1287" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="I1287" s="1" t="s">
         <v>1877</v>
       </c>
     </row>
-    <row r="1288" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1288" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1288" s="1" t="s">
         <v>1455</v>
       </c>
@@ -57596,9 +57680,11 @@
         <v>1075</v>
       </c>
       <c r="G1288" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H1288" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H1288" t="s">
+        <v>2974</v>
+      </c>
       <c r="I1288" s="1" t="s">
         <v>1075</v>
       </c>
@@ -57630,7 +57716,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="1290" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1290" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1290" s="1" t="s">
         <v>2547</v>
       </c>
@@ -57650,14 +57736,16 @@
         <v>1075</v>
       </c>
       <c r="G1290" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H1290" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H1290" t="s">
+        <v>2975</v>
+      </c>
       <c r="I1290" s="1" t="s">
         <v>1075</v>
       </c>
     </row>
-    <row r="1291" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1291" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1291" s="1" t="s">
         <v>2930</v>
       </c>
@@ -57677,9 +57765,11 @@
         <v>1075</v>
       </c>
       <c r="G1291" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H1291" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H1291" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="I1291" s="1" t="s">
         <v>1075</v>
       </c>
@@ -57738,7 +57828,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="1294" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1294" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1294" s="1" t="s">
         <v>2087</v>
       </c>
@@ -57758,9 +57848,11 @@
         <v>1075</v>
       </c>
       <c r="G1294" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H1294" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H1294" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="I1294" s="1" t="s">
         <v>2090</v>
       </c>

--- a/data/chapter2/FRED/subsets/species.xlsx
+++ b/data/chapter2/FRED/subsets/species.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://westernsydneyedu-my.sharepoint.com/personal/90963425_westernsydney_edu_au/Documents/PhD/code/data/chapter2/FRED/subsets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="526" documentId="8_{81FDA0CF-33C4-43D2-B8CA-CC5F96143B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D97DE75E-1679-42F4-9C00-D4BEAF07C48B}"/>
+  <xr:revisionPtr revIDLastSave="551" documentId="8_{81FDA0CF-33C4-43D2-B8CA-CC5F96143B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51A66BA3-5075-499F-9386-79CC72B50FEA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="456" activeTab="3" xr2:uid="{A5444074-DC77-415C-A9E2-2BBA8270EAFC}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14087" uniqueCount="2977">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14153" uniqueCount="2977">
   <si>
     <t>F00645</t>
   </si>
@@ -35146,9 +35146,11 @@
         <v>1075</v>
       </c>
       <c r="G464" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H464" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H464" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="I464" s="1" t="s">
         <v>1359</v>
       </c>
@@ -35173,9 +35175,11 @@
         <v>1075</v>
       </c>
       <c r="G465" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H465" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H465" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="I465" s="1" t="s">
         <v>2704</v>
       </c>
@@ -35200,9 +35204,11 @@
         <v>1075</v>
       </c>
       <c r="G466" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H466" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H466" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="I466" s="1" t="s">
         <v>1075</v>
       </c>
@@ -36024,9 +36030,11 @@
         <v>1075</v>
       </c>
       <c r="G496" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H496" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H496" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="I496" s="1" t="s">
         <v>1668</v>
       </c>
@@ -36051,9 +36059,11 @@
         <v>1075</v>
       </c>
       <c r="G497" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H497" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H497" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="I497" s="1" t="s">
         <v>1075</v>
       </c>
@@ -36132,9 +36142,11 @@
         <v>1075</v>
       </c>
       <c r="G500" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H500" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H500" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="I500" s="1" t="s">
         <v>1075</v>
       </c>
@@ -36186,9 +36198,11 @@
         <v>1075</v>
       </c>
       <c r="G502" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H502" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H502" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="I502" s="1" t="s">
         <v>1075</v>
       </c>
@@ -36213,9 +36227,11 @@
         <v>1075</v>
       </c>
       <c r="G503" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H503" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H503" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="I503" s="1" t="s">
         <v>1075</v>
       </c>
@@ -36240,9 +36256,11 @@
         <v>1075</v>
       </c>
       <c r="G504" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H504" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H504" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="I504" s="1" t="s">
         <v>2027</v>
       </c>
@@ -36294,9 +36312,11 @@
         <v>1075</v>
       </c>
       <c r="G506" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H506" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H506" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="I506" s="1" t="s">
         <v>1075</v>
       </c>
@@ -36321,9 +36341,11 @@
         <v>1075</v>
       </c>
       <c r="G507" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H507" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H507" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="I507" s="1" t="s">
         <v>1075</v>
       </c>
@@ -36431,9 +36453,11 @@
         <v>1075</v>
       </c>
       <c r="G511" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H511" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H511" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="I511" s="1" t="s">
         <v>2786</v>
       </c>
@@ -37012,9 +37036,11 @@
         <v>1075</v>
       </c>
       <c r="G532" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H532" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="H532" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="I532" s="1" t="s">
         <v>1075</v>
       </c>
@@ -37039,9 +37065,11 @@
         <v>1075</v>
       </c>
       <c r="G533" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H533" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="H533" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="I533" s="1" t="s">
         <v>1740</v>
       </c>
@@ -40096,9 +40124,11 @@
         <v>1075</v>
       </c>
       <c r="G644" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H644" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H644" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="I644" s="1" t="s">
         <v>1075</v>
       </c>
@@ -40231,9 +40261,11 @@
         <v>1075</v>
       </c>
       <c r="G649" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H649" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H649" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="I649" s="1" t="s">
         <v>1075</v>
       </c>
@@ -40258,9 +40290,11 @@
         <v>1075</v>
       </c>
       <c r="G650" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H650" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H650" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="I650" s="1" t="s">
         <v>1075</v>
       </c>
@@ -40339,9 +40373,11 @@
         <v>1075</v>
       </c>
       <c r="G653" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H653" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H653" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="I653" s="1" t="s">
         <v>1075</v>
       </c>
@@ -40690,9 +40726,11 @@
         <v>1075</v>
       </c>
       <c r="G666" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H666" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H666" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="I666" s="1" t="s">
         <v>1767</v>
       </c>

--- a/data/chapter2/FRED/subsets/species.xlsx
+++ b/data/chapter2/FRED/subsets/species.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://westernsydneyedu-my.sharepoint.com/personal/90963425_westernsydney_edu_au/Documents/PhD/code/data/chapter2/FRED/subsets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="667" documentId="8_{81FDA0CF-33C4-43D2-B8CA-CC5F96143B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5FCA0E6-0A85-4C64-9343-999E046C39CC}"/>
+  <xr:revisionPtr revIDLastSave="684" documentId="8_{81FDA0CF-33C4-43D2-B8CA-CC5F96143B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC17E4B3-8AE3-4185-9D2F-E2E2FA36B7DC}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="456" activeTab="3" xr2:uid="{A5444074-DC77-415C-A9E2-2BBA8270EAFC}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15359" uniqueCount="2979">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15365" uniqueCount="2979">
   <si>
     <t>F00645</t>
   </si>
@@ -9773,7 +9773,7 @@
   <autoFilter ref="A1:K1302" xr:uid="{92DE4C38-9658-4F81-87D7-16EF2BBFE835}">
     <filterColumn colId="2">
       <filters>
-        <filter val="Cornaceae"/>
+        <filter val="Cyperaceae"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -24068,7 +24068,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>114</v>
       </c>
@@ -28551,7 +28551,7 @@
         <v>1931</v>
       </c>
     </row>
-    <row r="195" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A195" s="1" t="s">
         <v>23</v>
       </c>
@@ -28575,14 +28575,16 @@
       </c>
       <c r="H195" s="1"/>
       <c r="I195" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J195" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="J195" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K195" s="1" t="s">
         <v>1414</v>
       </c>
     </row>
-    <row r="196" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A196" s="1" t="s">
         <v>202</v>
       </c>
@@ -28613,7 +28615,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="197" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A197" s="1" t="s">
         <v>203</v>
       </c>
@@ -28637,14 +28639,16 @@
       </c>
       <c r="H197" s="1"/>
       <c r="I197" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J197" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="J197" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K197" s="1" t="s">
         <v>1075</v>
       </c>
     </row>
-    <row r="198" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A198" s="1" t="s">
         <v>932</v>
       </c>
@@ -28675,7 +28679,7 @@
         <v>1415</v>
       </c>
     </row>
-    <row r="199" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A199" s="1" t="s">
         <v>204</v>
       </c>
@@ -28699,14 +28703,16 @@
       </c>
       <c r="H199" s="1"/>
       <c r="I199" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J199" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="J199" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K199" s="1" t="s">
         <v>1075</v>
       </c>
     </row>
-    <row r="200" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A200" s="1" t="s">
         <v>205</v>
       </c>
@@ -28770,7 +28776,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="202" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A202" s="1" t="s">
         <v>941</v>
       </c>
@@ -31918,7 +31924,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A302" s="1" t="s">
         <v>269</v>
       </c>
@@ -31949,7 +31955,7 @@
         <v>1575</v>
       </c>
     </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A303" s="1" t="s">
         <v>270</v>
       </c>
@@ -31980,7 +31986,7 @@
         <v>1576</v>
       </c>
     </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A304" s="1" t="s">
         <v>271</v>
       </c>
@@ -32011,7 +32017,7 @@
         <v>1577</v>
       </c>
     </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A305" s="1" t="s">
         <v>272</v>
       </c>
@@ -32042,7 +32048,7 @@
         <v>1578</v>
       </c>
     </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A306" s="1" t="s">
         <v>273</v>
       </c>
@@ -32075,7 +32081,7 @@
         <v>1579</v>
       </c>
     </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A307" s="1" t="s">
         <v>274</v>
       </c>
@@ -35316,7 +35322,7 @@
         <v>2948</v>
       </c>
     </row>
-    <row r="410" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A410" s="1" t="s">
         <v>1408</v>
       </c>
@@ -35380,7 +35386,7 @@
         <v>1763</v>
       </c>
     </row>
-    <row r="412" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A412" s="1" t="s">
         <v>1412</v>
       </c>
@@ -35413,7 +35419,7 @@
         <v>1413</v>
       </c>
     </row>
-    <row r="413" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A413" s="1" t="s">
         <v>1417</v>
       </c>
@@ -37486,7 +37492,7 @@
         <v>1833</v>
       </c>
     </row>
-    <row r="479" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A479" s="1" t="s">
         <v>392</v>
       </c>
@@ -37510,14 +37516,16 @@
       </c>
       <c r="H479" s="1"/>
       <c r="I479" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J479" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="J479" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K479" s="1" t="s">
         <v>1075</v>
       </c>
     </row>
-    <row r="480" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A480" s="1" t="s">
         <v>393</v>
       </c>
@@ -37541,9 +37549,11 @@
       </c>
       <c r="H480" s="1"/>
       <c r="I480" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J480" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="J480" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K480" s="1" t="s">
         <v>1835</v>
       </c>
@@ -42278,9 +42288,11 @@
       </c>
       <c r="H629" s="1"/>
       <c r="I629" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J629" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="J629" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K629" s="1" t="s">
         <v>2047</v>
       </c>

--- a/data/chapter2/FRED/subsets/species.xlsx
+++ b/data/chapter2/FRED/subsets/species.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://westernsydneyedu-my.sharepoint.com/personal/90963425_westernsydney_edu_au/Documents/PhD/code/data/chapter2/FRED/subsets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="684" documentId="8_{81FDA0CF-33C4-43D2-B8CA-CC5F96143B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC17E4B3-8AE3-4185-9D2F-E2E2FA36B7DC}"/>
+  <xr:revisionPtr revIDLastSave="728" documentId="8_{81FDA0CF-33C4-43D2-B8CA-CC5F96143B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2517040B-96C4-48F7-A303-9C797925BA81}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="456" activeTab="3" xr2:uid="{A5444074-DC77-415C-A9E2-2BBA8270EAFC}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15365" uniqueCount="2979">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15379" uniqueCount="2979">
   <si>
     <t>F00645</t>
   </si>
@@ -9569,9 +9569,6 @@
   </cellStyles>
   <dxfs count="22">
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
@@ -9600,6 +9597,9 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -9771,15 +9771,14 @@
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{92DE4C38-9658-4F81-87D7-16EF2BBFE835}" name="species_hand_cleaned__2" displayName="species_hand_cleaned__2" ref="A1:K1302" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:K1302" xr:uid="{92DE4C38-9658-4F81-87D7-16EF2BBFE835}">
-    <filterColumn colId="2">
+    <filterColumn colId="1">
       <filters>
-        <filter val="Cyperaceae"/>
+        <filter val="Myriocarpa"/>
       </filters>
     </filterColumn>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A38:K1294">
-    <sortCondition ref="C2:C1302"/>
-    <sortCondition ref="B2:B1302"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:K1302">
+    <sortCondition ref="A1:A1302"/>
   </sortState>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{F3C746AB-507C-4449-8505-3C28BE556995}" uniqueName="1" name="binominal" queryTableFieldId="1" dataDxfId="13"/>
@@ -9790,9 +9789,9 @@
     <tableColumn id="7" xr3:uid="{B02B66DA-13A9-4CB5-825F-5DED0D566C1B}" uniqueName="7" name="source" queryTableFieldId="7" dataDxfId="8"/>
     <tableColumn id="10" xr3:uid="{F6BD3771-A0D5-4CCB-8468-8606E88AB0D4}" uniqueName="10" name="state_revision_1" queryTableFieldId="9" dataDxfId="7"/>
     <tableColumn id="11" xr3:uid="{0DE42D6D-AC38-4C14-9B14-EA44A12F2B6B}" uniqueName="11" name="revision_1_source" queryTableFieldId="10" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{1C7FC0CD-0226-4186-804A-4BEC0C942A0C}" uniqueName="3" name="state_revision_2" queryTableFieldId="11" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{78268403-965B-4216-A099-3B74CCAFA873}" uniqueName="9" name="revision_2_source" queryTableFieldId="12" dataDxfId="0"/>
-    <tableColumn id="8" xr3:uid="{BF17E376-910E-4BBA-A563-6711F2890154}" uniqueName="8" name="synonyms" queryTableFieldId="8" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{1C7FC0CD-0226-4186-804A-4BEC0C942A0C}" uniqueName="3" name="state_revision_2" queryTableFieldId="11" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{78268403-965B-4216-A099-3B74CCAFA873}" uniqueName="9" name="revision_2_source" queryTableFieldId="12" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{BF17E376-910E-4BBA-A563-6711F2890154}" uniqueName="8" name="synonyms" queryTableFieldId="8" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -20421,7 +20420,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -21828,7 +21827,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -22408,7 +22407,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -22556,9 +22555,11 @@
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J4" s="1"/>
+        <v>3</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K4" s="1" t="s">
         <v>1068</v>
       </c>
@@ -25443,9 +25444,11 @@
       </c>
       <c r="H95" s="1"/>
       <c r="I95" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J95" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="J95" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K95" s="1" t="s">
         <v>1075</v>
       </c>
@@ -26410,9 +26413,11 @@
       </c>
       <c r="H126" s="1"/>
       <c r="I126" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J126" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="J126" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K126" s="1" t="s">
         <v>1298</v>
       </c>
@@ -26702,7 +26707,7 @@
     </row>
     <row r="136" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
-        <v>1006</v>
+        <v>1308</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>1309</v>
@@ -26714,21 +26719,23 @@
         <v>1067</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>2</v>
+        <v>1075</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>2969</v>
+        <v>1075</v>
       </c>
       <c r="G136" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H136" s="1"/>
+      <c r="H136" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="I136" s="1" t="s">
         <v>2</v>
       </c>
       <c r="J136" s="1"/>
       <c r="K136" s="1" t="s">
-        <v>1312</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="137" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -26766,7 +26773,7 @@
     </row>
     <row r="138" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
-        <v>959</v>
+        <v>1310</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>1309</v>
@@ -26778,21 +26785,23 @@
         <v>1067</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>2</v>
+        <v>1075</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>2969</v>
+        <v>1075</v>
       </c>
       <c r="G138" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H138" s="1"/>
+      <c r="H138" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="I138" s="1" t="s">
         <v>2</v>
       </c>
       <c r="J138" s="1"/>
       <c r="K138" s="1" t="s">
-        <v>1315</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="139" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -26954,10 +26963,10 @@
     </row>
     <row r="144" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" s="1" t="s">
-        <v>19</v>
+        <v>1006</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>1324</v>
+        <v>1309</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>1066</v>
@@ -26969,7 +26978,7 @@
         <v>2</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>2970</v>
+        <v>2969</v>
       </c>
       <c r="G144" s="1" t="s">
         <v>2</v>
@@ -26980,7 +26989,7 @@
       </c>
       <c r="J144" s="1"/>
       <c r="K144" s="1" t="s">
-        <v>1325</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -27425,10 +27434,10 @@
     </row>
     <row r="159" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" s="1" t="s">
-        <v>947</v>
+        <v>1313</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>1345</v>
+        <v>1309</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>1066</v>
@@ -27437,21 +27446,23 @@
         <v>1067</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>2</v>
+        <v>1075</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>2969</v>
+        <v>1075</v>
       </c>
       <c r="G159" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H159" s="1"/>
+      <c r="H159" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="I159" s="1" t="s">
         <v>2</v>
       </c>
       <c r="J159" s="1"/>
       <c r="K159" s="1" t="s">
-        <v>1346</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="160" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -28113,10 +28124,10 @@
     </row>
     <row r="181" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" s="1" t="s">
-        <v>192</v>
+        <v>959</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>1381</v>
+        <v>1309</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>1066</v>
@@ -28128,7 +28139,7 @@
         <v>2</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>2968</v>
+        <v>2969</v>
       </c>
       <c r="G181" s="1" t="s">
         <v>2</v>
@@ -28139,7 +28150,7 @@
       </c>
       <c r="J181" s="1"/>
       <c r="K181" s="1" t="s">
-        <v>1382</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="182" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -28354,9 +28365,11 @@
       </c>
       <c r="H188" s="1"/>
       <c r="I188" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J188" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="J188" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K188" s="1" t="s">
         <v>1075</v>
       </c>
@@ -28551,7 +28564,7 @@
         <v>1931</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" s="1" t="s">
         <v>23</v>
       </c>
@@ -28584,7 +28597,7 @@
         <v>1414</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" s="1" t="s">
         <v>202</v>
       </c>
@@ -28615,7 +28628,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197" s="1" t="s">
         <v>203</v>
       </c>
@@ -28648,7 +28661,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" s="1" t="s">
         <v>932</v>
       </c>
@@ -28679,7 +28692,7 @@
         <v>1415</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199" s="1" t="s">
         <v>204</v>
       </c>
@@ -28712,7 +28725,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200" s="1" t="s">
         <v>205</v>
       </c>
@@ -28776,7 +28789,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202" s="1" t="s">
         <v>941</v>
       </c>
@@ -30036,10 +30049,10 @@
     </row>
     <row r="242" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A242" s="1" t="s">
-        <v>231</v>
+        <v>19</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>1482</v>
+        <v>1324</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>1066</v>
@@ -30051,7 +30064,7 @@
         <v>2</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>2968</v>
+        <v>2970</v>
       </c>
       <c r="G242" s="1" t="s">
         <v>2</v>
@@ -30062,7 +30075,7 @@
       </c>
       <c r="J242" s="1"/>
       <c r="K242" s="1" t="s">
-        <v>1483</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="243" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -30100,10 +30113,10 @@
     </row>
     <row r="244" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244" s="1" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>1488</v>
+        <v>1345</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>1066</v>
@@ -30126,7 +30139,7 @@
       </c>
       <c r="J244" s="1"/>
       <c r="K244" s="1" t="s">
-        <v>1489</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="245" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -30589,9 +30602,11 @@
       </c>
       <c r="H259" s="1"/>
       <c r="I259" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J259" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="J259" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K259" s="1" t="s">
         <v>1518</v>
       </c>
@@ -31327,10 +31342,10 @@
     </row>
     <row r="283" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A283" s="1" t="s">
-        <v>257</v>
+        <v>192</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>1546</v>
+        <v>1381</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>1066</v>
@@ -31353,7 +31368,7 @@
       </c>
       <c r="J283" s="1"/>
       <c r="K283" s="1" t="s">
-        <v>1547</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="284" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -32295,9 +32310,11 @@
       </c>
       <c r="H313" s="1"/>
       <c r="I313" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J313" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="J313" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K313" s="1" t="s">
         <v>1075</v>
       </c>
@@ -33343,10 +33360,10 @@
     </row>
     <row r="347" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A347" s="1" t="s">
-        <v>29</v>
+        <v>1391</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>1646</v>
+        <v>1392</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>1066</v>
@@ -33355,21 +33372,23 @@
         <v>1067</v>
       </c>
       <c r="E347" s="1" t="s">
-        <v>2</v>
+        <v>1075</v>
       </c>
       <c r="F347" s="1" t="s">
-        <v>2970</v>
+        <v>1075</v>
       </c>
       <c r="G347" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H347" s="1"/>
+      <c r="H347" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="I347" s="1" t="s">
         <v>2</v>
       </c>
       <c r="J347" s="1"/>
       <c r="K347" s="1" t="s">
-        <v>1647</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="348" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -34117,9 +34136,11 @@
       </c>
       <c r="H371" s="1"/>
       <c r="I371" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J371" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="J371" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K371" s="1" t="s">
         <v>1075</v>
       </c>
@@ -35156,9 +35177,11 @@
       </c>
       <c r="H404" s="1"/>
       <c r="I404" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J404" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="J404" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K404" s="1" t="s">
         <v>1075</v>
       </c>
@@ -35322,7 +35345,7 @@
         <v>2948</v>
       </c>
     </row>
-    <row r="410" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A410" s="1" t="s">
         <v>1408</v>
       </c>
@@ -35386,7 +35409,7 @@
         <v>1763</v>
       </c>
     </row>
-    <row r="412" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A412" s="1" t="s">
         <v>1412</v>
       </c>
@@ -35419,7 +35442,7 @@
         <v>1413</v>
       </c>
     </row>
-    <row r="413" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A413" s="1" t="s">
         <v>1417</v>
       </c>
@@ -37116,10 +37139,10 @@
     </row>
     <row r="467" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A467" s="1" t="s">
-        <v>1308</v>
+        <v>231</v>
       </c>
       <c r="B467" s="1" t="s">
-        <v>1309</v>
+        <v>1482</v>
       </c>
       <c r="C467" s="1" t="s">
         <v>1066</v>
@@ -37128,23 +37151,21 @@
         <v>1067</v>
       </c>
       <c r="E467" s="1" t="s">
-        <v>1075</v>
+        <v>2</v>
       </c>
       <c r="F467" s="1" t="s">
-        <v>1075</v>
+        <v>2968</v>
       </c>
       <c r="G467" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H467" s="1" t="s">
-        <v>2976</v>
-      </c>
+      <c r="H467" s="1"/>
       <c r="I467" s="1" t="s">
         <v>2</v>
       </c>
       <c r="J467" s="1"/>
       <c r="K467" s="1" t="s">
-        <v>1075</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="468" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -37180,10 +37201,10 @@
     </row>
     <row r="469" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A469" s="1" t="s">
-        <v>1310</v>
+        <v>951</v>
       </c>
       <c r="B469" s="1" t="s">
-        <v>1309</v>
+        <v>1488</v>
       </c>
       <c r="C469" s="1" t="s">
         <v>1066</v>
@@ -37192,23 +37213,21 @@
         <v>1067</v>
       </c>
       <c r="E469" s="1" t="s">
-        <v>1075</v>
+        <v>2</v>
       </c>
       <c r="F469" s="1" t="s">
-        <v>1075</v>
+        <v>2969</v>
       </c>
       <c r="G469" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H469" s="1" t="s">
-        <v>2976</v>
-      </c>
+      <c r="H469" s="1"/>
       <c r="I469" s="1" t="s">
         <v>2</v>
       </c>
       <c r="J469" s="1"/>
       <c r="K469" s="1" t="s">
-        <v>1311</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="470" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -37492,7 +37511,7 @@
         <v>1833</v>
       </c>
     </row>
-    <row r="479" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A479" s="1" t="s">
         <v>392</v>
       </c>
@@ -37525,7 +37544,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="480" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A480" s="1" t="s">
         <v>393</v>
       </c>
@@ -37560,10 +37579,10 @@
     </row>
     <row r="481" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A481" s="1" t="s">
-        <v>1313</v>
+        <v>257</v>
       </c>
       <c r="B481" s="1" t="s">
-        <v>1309</v>
+        <v>1546</v>
       </c>
       <c r="C481" s="1" t="s">
         <v>1066</v>
@@ -37572,23 +37591,21 @@
         <v>1067</v>
       </c>
       <c r="E481" s="1" t="s">
-        <v>1075</v>
+        <v>2</v>
       </c>
       <c r="F481" s="1" t="s">
-        <v>1075</v>
+        <v>2968</v>
       </c>
       <c r="G481" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H481" s="1" t="s">
-        <v>2976</v>
-      </c>
+      <c r="H481" s="1"/>
       <c r="I481" s="1" t="s">
         <v>2</v>
       </c>
       <c r="J481" s="1"/>
       <c r="K481" s="1" t="s">
-        <v>1314</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="482" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -37748,10 +37765,10 @@
     </row>
     <row r="487" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A487" s="1" t="s">
-        <v>1391</v>
+        <v>1581</v>
       </c>
       <c r="B487" s="1" t="s">
-        <v>1392</v>
+        <v>1582</v>
       </c>
       <c r="C487" s="1" t="s">
         <v>1066</v>
@@ -37776,12 +37793,12 @@
       </c>
       <c r="J487" s="1"/>
       <c r="K487" s="1" t="s">
-        <v>1393</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="488" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A488" s="1" t="s">
-        <v>1581</v>
+        <v>1584</v>
       </c>
       <c r="B488" s="1" t="s">
         <v>1582</v>
@@ -37809,15 +37826,15 @@
       </c>
       <c r="J488" s="1"/>
       <c r="K488" s="1" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="489" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A489" s="1" t="s">
-        <v>398</v>
+        <v>1630</v>
       </c>
       <c r="B489" s="1" t="s">
-        <v>1850</v>
+        <v>1631</v>
       </c>
       <c r="C489" s="1" t="s">
         <v>1066</v>
@@ -37826,29 +37843,31 @@
         <v>1067</v>
       </c>
       <c r="E489" s="1" t="s">
-        <v>2</v>
+        <v>1075</v>
       </c>
       <c r="F489" s="1" t="s">
-        <v>2968</v>
+        <v>1075</v>
       </c>
       <c r="G489" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H489" s="1"/>
+      <c r="H489" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="I489" s="1" t="s">
         <v>2</v>
       </c>
       <c r="J489" s="1"/>
       <c r="K489" s="1" t="s">
-        <v>1075</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="490" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A490" s="1" t="s">
-        <v>1584</v>
+        <v>29</v>
       </c>
       <c r="B490" s="1" t="s">
-        <v>1582</v>
+        <v>1646</v>
       </c>
       <c r="C490" s="1" t="s">
         <v>1066</v>
@@ -37857,31 +37876,29 @@
         <v>1067</v>
       </c>
       <c r="E490" s="1" t="s">
-        <v>1075</v>
+        <v>2</v>
       </c>
       <c r="F490" s="1" t="s">
-        <v>1075</v>
+        <v>2970</v>
       </c>
       <c r="G490" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H490" s="1" t="s">
-        <v>2976</v>
-      </c>
+      <c r="H490" s="1"/>
       <c r="I490" s="1" t="s">
         <v>2</v>
       </c>
       <c r="J490" s="1"/>
       <c r="K490" s="1" t="s">
-        <v>1585</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="491" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A491" s="1" t="s">
-        <v>1630</v>
+        <v>1666</v>
       </c>
       <c r="B491" s="1" t="s">
-        <v>1631</v>
+        <v>1667</v>
       </c>
       <c r="C491" s="1" t="s">
         <v>1066</v>
@@ -37899,14 +37916,14 @@
         <v>2</v>
       </c>
       <c r="H491" s="1" t="s">
-        <v>2976</v>
+        <v>2975</v>
       </c>
       <c r="I491" s="1" t="s">
         <v>2</v>
       </c>
       <c r="J491" s="1"/>
       <c r="K491" s="1" t="s">
-        <v>1632</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="492" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -38006,10 +38023,10 @@
     </row>
     <row r="495" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A495" s="1" t="s">
-        <v>401</v>
+        <v>1705</v>
       </c>
       <c r="B495" s="1" t="s">
-        <v>1865</v>
+        <v>1706</v>
       </c>
       <c r="C495" s="1" t="s">
         <v>1066</v>
@@ -38018,29 +38035,31 @@
         <v>1067</v>
       </c>
       <c r="E495" s="1" t="s">
-        <v>2</v>
+        <v>1075</v>
       </c>
       <c r="F495" s="1" t="s">
-        <v>2968</v>
+        <v>1075</v>
       </c>
       <c r="G495" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H495" s="1"/>
+      <c r="H495" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="I495" s="1" t="s">
         <v>2</v>
       </c>
       <c r="J495" s="1"/>
       <c r="K495" s="1" t="s">
-        <v>1866</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="496" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A496" s="1" t="s">
-        <v>1666</v>
+        <v>398</v>
       </c>
       <c r="B496" s="1" t="s">
-        <v>1667</v>
+        <v>1850</v>
       </c>
       <c r="C496" s="1" t="s">
         <v>1066</v>
@@ -38049,31 +38068,29 @@
         <v>1067</v>
       </c>
       <c r="E496" s="1" t="s">
-        <v>1075</v>
+        <v>2</v>
       </c>
       <c r="F496" s="1" t="s">
-        <v>1075</v>
+        <v>2968</v>
       </c>
       <c r="G496" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H496" s="1" t="s">
-        <v>2975</v>
-      </c>
+      <c r="H496" s="1"/>
       <c r="I496" s="1" t="s">
         <v>2</v>
       </c>
       <c r="J496" s="1"/>
       <c r="K496" s="1" t="s">
-        <v>1668</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="497" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A497" s="1" t="s">
-        <v>1705</v>
+        <v>1851</v>
       </c>
       <c r="B497" s="1" t="s">
-        <v>1706</v>
+        <v>1850</v>
       </c>
       <c r="C497" s="1" t="s">
         <v>1066</v>
@@ -38091,7 +38108,7 @@
         <v>2</v>
       </c>
       <c r="H497" s="1" t="s">
-        <v>2976</v>
+        <v>2975</v>
       </c>
       <c r="I497" s="1" t="s">
         <v>2</v>
@@ -38125,9 +38142,11 @@
       </c>
       <c r="H498" s="1"/>
       <c r="I498" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J498" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="J498" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K498" s="1" t="s">
         <v>1075</v>
       </c>
@@ -38165,10 +38184,10 @@
     </row>
     <row r="500" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A500" s="1" t="s">
-        <v>1851</v>
+        <v>401</v>
       </c>
       <c r="B500" s="1" t="s">
-        <v>1850</v>
+        <v>1865</v>
       </c>
       <c r="C500" s="1" t="s">
         <v>1066</v>
@@ -38177,23 +38196,21 @@
         <v>1067</v>
       </c>
       <c r="E500" s="1" t="s">
-        <v>1075</v>
+        <v>2</v>
       </c>
       <c r="F500" s="1" t="s">
-        <v>1075</v>
+        <v>2968</v>
       </c>
       <c r="G500" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H500" s="1" t="s">
-        <v>2975</v>
-      </c>
+      <c r="H500" s="1"/>
       <c r="I500" s="1" t="s">
         <v>2</v>
       </c>
       <c r="J500" s="1"/>
       <c r="K500" s="1" t="s">
-        <v>1075</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="501" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -38229,10 +38246,10 @@
     </row>
     <row r="502" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A502" s="1" t="s">
-        <v>2020</v>
+        <v>948</v>
       </c>
       <c r="B502" s="1" t="s">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C502" s="1" t="s">
         <v>1066</v>
@@ -38241,28 +38258,26 @@
         <v>1067</v>
       </c>
       <c r="E502" s="1" t="s">
-        <v>1075</v>
+        <v>2</v>
       </c>
       <c r="F502" s="1" t="s">
-        <v>1075</v>
+        <v>2969</v>
       </c>
       <c r="G502" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H502" s="1" t="s">
-        <v>2975</v>
-      </c>
+      <c r="H502" s="1"/>
       <c r="I502" s="1" t="s">
         <v>2</v>
       </c>
       <c r="J502" s="1"/>
       <c r="K502" s="1" t="s">
-        <v>1075</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="503" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A503" s="1" t="s">
-        <v>2022</v>
+        <v>425</v>
       </c>
       <c r="B503" s="1" t="s">
         <v>2016</v>
@@ -38274,28 +38289,26 @@
         <v>1067</v>
       </c>
       <c r="E503" s="1" t="s">
-        <v>1075</v>
+        <v>2</v>
       </c>
       <c r="F503" s="1" t="s">
-        <v>1075</v>
+        <v>2968</v>
       </c>
       <c r="G503" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H503" s="1" t="s">
-        <v>2975</v>
-      </c>
+      <c r="H503" s="1"/>
       <c r="I503" s="1" t="s">
         <v>2</v>
       </c>
       <c r="J503" s="1"/>
       <c r="K503" s="1" t="s">
-        <v>1075</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="504" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A504" s="1" t="s">
-        <v>2026</v>
+        <v>426</v>
       </c>
       <c r="B504" s="1" t="s">
         <v>2016</v>
@@ -38307,23 +38320,21 @@
         <v>1067</v>
       </c>
       <c r="E504" s="1" t="s">
-        <v>1075</v>
+        <v>2</v>
       </c>
       <c r="F504" s="1" t="s">
-        <v>1075</v>
+        <v>2968</v>
       </c>
       <c r="G504" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H504" s="1" t="s">
-        <v>2975</v>
-      </c>
+      <c r="H504" s="1"/>
       <c r="I504" s="1" t="s">
         <v>2</v>
       </c>
       <c r="J504" s="1"/>
       <c r="K504" s="1" t="s">
-        <v>2027</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="505" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -38359,10 +38370,10 @@
     </row>
     <row r="506" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A506" s="1" t="s">
-        <v>2078</v>
+        <v>427</v>
       </c>
       <c r="B506" s="1" t="s">
-        <v>2079</v>
+        <v>2016</v>
       </c>
       <c r="C506" s="1" t="s">
         <v>1066</v>
@@ -38371,17 +38382,15 @@
         <v>1067</v>
       </c>
       <c r="E506" s="1" t="s">
-        <v>1075</v>
+        <v>2</v>
       </c>
       <c r="F506" s="1" t="s">
-        <v>1075</v>
+        <v>2968</v>
       </c>
       <c r="G506" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H506" s="1" t="s">
-        <v>2975</v>
-      </c>
+      <c r="H506" s="1"/>
       <c r="I506" s="1" t="s">
         <v>2</v>
       </c>
@@ -38392,10 +38401,10 @@
     </row>
     <row r="507" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A507" s="1" t="s">
-        <v>2108</v>
+        <v>428</v>
       </c>
       <c r="B507" s="1" t="s">
-        <v>2106</v>
+        <v>2016</v>
       </c>
       <c r="C507" s="1" t="s">
         <v>1066</v>
@@ -38404,23 +38413,21 @@
         <v>1067</v>
       </c>
       <c r="E507" s="1" t="s">
-        <v>1075</v>
+        <v>2</v>
       </c>
       <c r="F507" s="1" t="s">
-        <v>1075</v>
+        <v>2968</v>
       </c>
       <c r="G507" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H507" s="1" t="s">
-        <v>2975</v>
-      </c>
+      <c r="H507" s="1"/>
       <c r="I507" s="1" t="s">
         <v>2</v>
       </c>
       <c r="J507" s="1"/>
       <c r="K507" s="1" t="s">
-        <v>1075</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="508" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -38456,10 +38463,10 @@
     </row>
     <row r="509" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A509" s="1" t="s">
-        <v>2174</v>
+        <v>429</v>
       </c>
       <c r="B509" s="1" t="s">
-        <v>2175</v>
+        <v>2016</v>
       </c>
       <c r="C509" s="1" t="s">
         <v>1066</v>
@@ -38468,23 +38475,21 @@
         <v>1067</v>
       </c>
       <c r="E509" s="1" t="s">
-        <v>1075</v>
+        <v>2</v>
       </c>
       <c r="F509" s="1" t="s">
-        <v>1075</v>
+        <v>2968</v>
       </c>
       <c r="G509" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H509" s="1" t="s">
-        <v>2976</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H509" s="1"/>
       <c r="I509" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J509" s="1"/>
       <c r="K509" s="1" t="s">
-        <v>1075</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="510" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -38520,10 +38525,10 @@
     </row>
     <row r="511" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A511" s="1" t="s">
-        <v>2784</v>
+        <v>430</v>
       </c>
       <c r="B511" s="1" t="s">
-        <v>2785</v>
+        <v>2016</v>
       </c>
       <c r="C511" s="1" t="s">
         <v>1066</v>
@@ -38532,23 +38537,21 @@
         <v>1067</v>
       </c>
       <c r="E511" s="1" t="s">
-        <v>1075</v>
+        <v>2</v>
       </c>
       <c r="F511" s="1" t="s">
-        <v>1075</v>
+        <v>2968</v>
       </c>
       <c r="G511" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H511" s="1" t="s">
-        <v>2975</v>
-      </c>
+      <c r="H511" s="1"/>
       <c r="I511" s="1" t="s">
         <v>2</v>
       </c>
       <c r="J511" s="1"/>
       <c r="K511" s="1" t="s">
-        <v>2786</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="512" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -41175,10 +41178,10 @@
     </row>
     <row r="594" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A594" s="1" t="s">
-        <v>948</v>
+        <v>2020</v>
       </c>
       <c r="B594" s="1" t="s">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="C594" s="1" t="s">
         <v>1066</v>
@@ -41187,26 +41190,28 @@
         <v>1067</v>
       </c>
       <c r="E594" s="1" t="s">
-        <v>2</v>
+        <v>1075</v>
       </c>
       <c r="F594" s="1" t="s">
-        <v>2969</v>
+        <v>1075</v>
       </c>
       <c r="G594" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H594" s="1"/>
+      <c r="H594" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="I594" s="1" t="s">
         <v>2</v>
       </c>
       <c r="J594" s="1"/>
       <c r="K594" s="1" t="s">
-        <v>2015</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="595" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A595" s="1" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="B595" s="1" t="s">
         <v>2016</v>
@@ -41232,12 +41237,12 @@
       </c>
       <c r="J595" s="1"/>
       <c r="K595" s="1" t="s">
-        <v>2017</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="596" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A596" s="1" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="B596" s="1" t="s">
         <v>2016</v>
@@ -41268,7 +41273,7 @@
     </row>
     <row r="597" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A597" s="1" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="B597" s="1" t="s">
         <v>2016</v>
@@ -41294,12 +41299,12 @@
       </c>
       <c r="J597" s="1"/>
       <c r="K597" s="1" t="s">
-        <v>1075</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="598" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A598" s="1" t="s">
-        <v>428</v>
+        <v>2022</v>
       </c>
       <c r="B598" s="1" t="s">
         <v>2016</v>
@@ -41311,26 +41316,28 @@
         <v>1067</v>
       </c>
       <c r="E598" s="1" t="s">
-        <v>2</v>
+        <v>1075</v>
       </c>
       <c r="F598" s="1" t="s">
-        <v>2968</v>
+        <v>1075</v>
       </c>
       <c r="G598" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H598" s="1"/>
+      <c r="H598" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="I598" s="1" t="s">
         <v>2</v>
       </c>
       <c r="J598" s="1"/>
       <c r="K598" s="1" t="s">
-        <v>2018</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="599" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A599" s="1" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="B599" s="1" t="s">
         <v>2016</v>
@@ -41356,12 +41363,12 @@
       </c>
       <c r="J599" s="1"/>
       <c r="K599" s="1" t="s">
-        <v>2019</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="600" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A600" s="1" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="B600" s="1" t="s">
         <v>2016</v>
@@ -41387,7 +41394,7 @@
       </c>
       <c r="J600" s="1"/>
       <c r="K600" s="1" t="s">
-        <v>1075</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="601" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -41425,7 +41432,7 @@
     </row>
     <row r="602" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A602" s="1" t="s">
-        <v>431</v>
+        <v>45</v>
       </c>
       <c r="B602" s="1" t="s">
         <v>2016</v>
@@ -41440,7 +41447,7 @@
         <v>2</v>
       </c>
       <c r="F602" s="1" t="s">
-        <v>2968</v>
+        <v>2970</v>
       </c>
       <c r="G602" s="1" t="s">
         <v>2</v>
@@ -41451,12 +41458,12 @@
       </c>
       <c r="J602" s="1"/>
       <c r="K602" s="1" t="s">
-        <v>1075</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="603" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A603" s="1" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B603" s="1" t="s">
         <v>2016</v>
@@ -41487,7 +41494,7 @@
     </row>
     <row r="604" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A604" s="1" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B604" s="1" t="s">
         <v>2016</v>
@@ -41513,7 +41520,7 @@
       </c>
       <c r="J604" s="1"/>
       <c r="K604" s="1" t="s">
-        <v>2021</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="605" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -41551,7 +41558,7 @@
     </row>
     <row r="606" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A606" s="1" t="s">
-        <v>434</v>
+        <v>2026</v>
       </c>
       <c r="B606" s="1" t="s">
         <v>2016</v>
@@ -41563,26 +41570,28 @@
         <v>1067</v>
       </c>
       <c r="E606" s="1" t="s">
-        <v>2</v>
+        <v>1075</v>
       </c>
       <c r="F606" s="1" t="s">
-        <v>2968</v>
+        <v>1075</v>
       </c>
       <c r="G606" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H606" s="1"/>
+      <c r="H606" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="I606" s="1" t="s">
         <v>2</v>
       </c>
       <c r="J606" s="1"/>
       <c r="K606" s="1" t="s">
-        <v>2023</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="607" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A607" s="1" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B607" s="1" t="s">
         <v>2016</v>
@@ -41608,12 +41617,12 @@
       </c>
       <c r="J607" s="1"/>
       <c r="K607" s="1" t="s">
-        <v>2024</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="608" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A608" s="1" t="s">
-        <v>45</v>
+        <v>439</v>
       </c>
       <c r="B608" s="1" t="s">
         <v>2016</v>
@@ -41628,7 +41637,7 @@
         <v>2</v>
       </c>
       <c r="F608" s="1" t="s">
-        <v>2970</v>
+        <v>2968</v>
       </c>
       <c r="G608" s="1" t="s">
         <v>2</v>
@@ -41639,12 +41648,12 @@
       </c>
       <c r="J608" s="1"/>
       <c r="K608" s="1" t="s">
-        <v>2025</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="609" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A609" s="1" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="B609" s="1" t="s">
         <v>2016</v>
@@ -41670,12 +41679,12 @@
       </c>
       <c r="J609" s="1"/>
       <c r="K609" s="1" t="s">
-        <v>1075</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="610" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A610" s="1" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B610" s="1" t="s">
         <v>2016</v>
@@ -41739,7 +41748,7 @@
     </row>
     <row r="612" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A612" s="1" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="B612" s="1" t="s">
         <v>2016</v>
@@ -41765,12 +41774,12 @@
       </c>
       <c r="J612" s="1"/>
       <c r="K612" s="1" t="s">
-        <v>2028</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="613" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A613" s="1" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B613" s="1" t="s">
         <v>2016</v>
@@ -41796,12 +41805,12 @@
       </c>
       <c r="J613" s="1"/>
       <c r="K613" s="1" t="s">
-        <v>2029</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="614" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A614" s="1" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="B614" s="1" t="s">
         <v>2016</v>
@@ -41827,15 +41836,15 @@
       </c>
       <c r="J614" s="1"/>
       <c r="K614" s="1" t="s">
-        <v>2030</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="615" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A615" s="1" t="s">
-        <v>441</v>
+        <v>2078</v>
       </c>
       <c r="B615" s="1" t="s">
-        <v>2016</v>
+        <v>2079</v>
       </c>
       <c r="C615" s="1" t="s">
         <v>1066</v>
@@ -41844,15 +41853,17 @@
         <v>1067</v>
       </c>
       <c r="E615" s="1" t="s">
-        <v>2</v>
+        <v>1075</v>
       </c>
       <c r="F615" s="1" t="s">
-        <v>2968</v>
+        <v>1075</v>
       </c>
       <c r="G615" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H615" s="1"/>
+      <c r="H615" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="I615" s="1" t="s">
         <v>2</v>
       </c>
@@ -41863,10 +41874,10 @@
     </row>
     <row r="616" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A616" s="1" t="s">
-        <v>442</v>
+        <v>481</v>
       </c>
       <c r="B616" s="1" t="s">
-        <v>2016</v>
+        <v>2106</v>
       </c>
       <c r="C616" s="1" t="s">
         <v>1066</v>
@@ -41889,15 +41900,15 @@
       </c>
       <c r="J616" s="1"/>
       <c r="K616" s="1" t="s">
-        <v>2031</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="617" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A617" s="1" t="s">
-        <v>443</v>
+        <v>49</v>
       </c>
       <c r="B617" s="1" t="s">
-        <v>2016</v>
+        <v>2106</v>
       </c>
       <c r="C617" s="1" t="s">
         <v>1066</v>
@@ -41909,7 +41920,7 @@
         <v>2</v>
       </c>
       <c r="F617" s="1" t="s">
-        <v>2968</v>
+        <v>2970</v>
       </c>
       <c r="G617" s="1" t="s">
         <v>2</v>
@@ -41920,15 +41931,15 @@
       </c>
       <c r="J617" s="1"/>
       <c r="K617" s="1" t="s">
-        <v>2032</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="618" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A618" s="1" t="s">
-        <v>444</v>
+        <v>2108</v>
       </c>
       <c r="B618" s="1" t="s">
-        <v>2016</v>
+        <v>2106</v>
       </c>
       <c r="C618" s="1" t="s">
         <v>1066</v>
@@ -41937,21 +41948,23 @@
         <v>1067</v>
       </c>
       <c r="E618" s="1" t="s">
-        <v>2</v>
+        <v>1075</v>
       </c>
       <c r="F618" s="1" t="s">
-        <v>2968</v>
+        <v>1075</v>
       </c>
       <c r="G618" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H618" s="1"/>
+      <c r="H618" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="I618" s="1" t="s">
         <v>2</v>
       </c>
       <c r="J618" s="1"/>
       <c r="K618" s="1" t="s">
-        <v>2033</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="619" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -43361,7 +43374,7 @@
     </row>
     <row r="664" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A664" s="1" t="s">
-        <v>481</v>
+        <v>994</v>
       </c>
       <c r="B664" s="1" t="s">
         <v>2106</v>
@@ -43373,29 +43386,29 @@
         <v>1067</v>
       </c>
       <c r="E664" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F664" s="1" t="s">
-        <v>2968</v>
+        <v>2969</v>
       </c>
       <c r="G664" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H664" s="1"/>
       <c r="I664" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J664" s="1"/>
       <c r="K664" s="1" t="s">
-        <v>1075</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="665" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A665" s="1" t="s">
-        <v>49</v>
+        <v>519</v>
       </c>
       <c r="B665" s="1" t="s">
-        <v>2106</v>
+        <v>2173</v>
       </c>
       <c r="C665" s="1" t="s">
         <v>1066</v>
@@ -43404,21 +43417,21 @@
         <v>1067</v>
       </c>
       <c r="E665" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F665" s="1" t="s">
-        <v>2970</v>
+        <v>2968</v>
       </c>
       <c r="G665" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H665" s="1"/>
       <c r="I665" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J665" s="1"/>
       <c r="K665" s="1" t="s">
-        <v>2107</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="666" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -43456,10 +43469,10 @@
     </row>
     <row r="667" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A667" s="1" t="s">
-        <v>994</v>
+        <v>2174</v>
       </c>
       <c r="B667" s="1" t="s">
-        <v>2106</v>
+        <v>2175</v>
       </c>
       <c r="C667" s="1" t="s">
         <v>1066</v>
@@ -43468,21 +43481,23 @@
         <v>1067</v>
       </c>
       <c r="E667" s="1" t="s">
-        <v>3</v>
+        <v>1075</v>
       </c>
       <c r="F667" s="1" t="s">
-        <v>2969</v>
+        <v>1075</v>
       </c>
       <c r="G667" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H667" s="1"/>
+        <v>5</v>
+      </c>
+      <c r="H667" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="I667" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J667" s="1"/>
       <c r="K667" s="1" t="s">
-        <v>2109</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="668" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -45247,10 +45262,10 @@
     </row>
     <row r="724" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A724" s="1" t="s">
-        <v>519</v>
+        <v>565</v>
       </c>
       <c r="B724" s="1" t="s">
-        <v>2173</v>
+        <v>2232</v>
       </c>
       <c r="C724" s="1" t="s">
         <v>1066</v>
@@ -45259,21 +45274,21 @@
         <v>1067</v>
       </c>
       <c r="E724" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F724" s="1" t="s">
         <v>2968</v>
       </c>
       <c r="G724" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H724" s="1"/>
       <c r="I724" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J724" s="1"/>
       <c r="K724" s="1" t="s">
-        <v>1075</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="725" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -46836,7 +46851,7 @@
     </row>
     <row r="775" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A775" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B775" s="1" t="s">
         <v>2232</v>
@@ -46862,12 +46877,12 @@
       </c>
       <c r="J775" s="1"/>
       <c r="K775" s="1" t="s">
-        <v>2233</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="776" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A776" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B776" s="1" t="s">
         <v>2232</v>
@@ -46893,15 +46908,15 @@
       </c>
       <c r="J776" s="1"/>
       <c r="K776" s="1" t="s">
-        <v>2234</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="777" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A777" s="1" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="B777" s="1" t="s">
-        <v>2232</v>
+        <v>2239</v>
       </c>
       <c r="C777" s="1" t="s">
         <v>1066</v>
@@ -46924,7 +46939,7 @@
       </c>
       <c r="J777" s="1"/>
       <c r="K777" s="1" t="s">
-        <v>2235</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="778" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -46991,10 +47006,10 @@
     </row>
     <row r="780" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A780" s="1" t="s">
-        <v>570</v>
+        <v>589</v>
       </c>
       <c r="B780" s="1" t="s">
-        <v>2239</v>
+        <v>2277</v>
       </c>
       <c r="C780" s="1" t="s">
         <v>1066</v>
@@ -47017,7 +47032,7 @@
       </c>
       <c r="J780" s="1"/>
       <c r="K780" s="1" t="s">
-        <v>2240</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="781" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -47844,10 +47859,10 @@
     </row>
     <row r="807" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A807" s="1" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
       <c r="B807" s="1" t="s">
-        <v>2277</v>
+        <v>2399</v>
       </c>
       <c r="C807" s="1" t="s">
         <v>1066</v>
@@ -47856,21 +47871,21 @@
         <v>1067</v>
       </c>
       <c r="E807" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F807" s="1" t="s">
-        <v>2968</v>
+        <v>2969</v>
       </c>
       <c r="G807" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H807" s="1"/>
       <c r="I807" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J807" s="1"/>
       <c r="K807" s="1" t="s">
-        <v>1075</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="808" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -50512,7 +50527,9 @@
       <c r="I891" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J891" s="1"/>
+      <c r="J891" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K891" s="1" t="s">
         <v>2385</v>
       </c>
@@ -50605,9 +50622,11 @@
       </c>
       <c r="H894" s="1"/>
       <c r="I894" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J894" s="1"/>
+        <v>5</v>
+      </c>
+      <c r="J894" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K894" s="1" t="s">
         <v>1075</v>
       </c>
@@ -50707,10 +50726,10 @@
     </row>
     <row r="898" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A898" s="1" t="s">
-        <v>1027</v>
+        <v>708</v>
       </c>
       <c r="B898" s="1" t="s">
-        <v>2399</v>
+        <v>2514</v>
       </c>
       <c r="C898" s="1" t="s">
         <v>1066</v>
@@ -50719,21 +50738,21 @@
         <v>1067</v>
       </c>
       <c r="E898" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F898" s="1" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="G898" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H898" s="1"/>
       <c r="I898" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J898" s="1"/>
       <c r="K898" s="1" t="s">
-        <v>2400</v>
+        <v>2515</v>
       </c>
     </row>
     <row r="899" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -53219,10 +53238,10 @@
     </row>
     <row r="978" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A978" s="1" t="s">
-        <v>708</v>
+        <v>845</v>
       </c>
       <c r="B978" s="1" t="s">
-        <v>2514</v>
+        <v>2764</v>
       </c>
       <c r="C978" s="1" t="s">
         <v>1066</v>
@@ -53245,7 +53264,7 @@
       </c>
       <c r="J978" s="1"/>
       <c r="K978" s="1" t="s">
-        <v>2515</v>
+        <v>2765</v>
       </c>
     </row>
     <row r="979" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -58533,9 +58552,11 @@
       </c>
       <c r="H1146" s="1"/>
       <c r="I1146" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1146" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="J1146" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K1146" s="1" t="s">
         <v>2723</v>
       </c>
@@ -59209,10 +59230,10 @@
     </row>
     <row r="1168" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1168" s="1" t="s">
-        <v>845</v>
+        <v>2784</v>
       </c>
       <c r="B1168" s="1" t="s">
-        <v>2764</v>
+        <v>2785</v>
       </c>
       <c r="C1168" s="1" t="s">
         <v>1066</v>
@@ -59221,21 +59242,23 @@
         <v>1067</v>
       </c>
       <c r="E1168" s="1" t="s">
-        <v>2</v>
+        <v>1075</v>
       </c>
       <c r="F1168" s="1" t="s">
-        <v>2968</v>
+        <v>1075</v>
       </c>
       <c r="G1168" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H1168" s="1"/>
+      <c r="H1168" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="I1168" s="1" t="s">
         <v>2</v>
       </c>
       <c r="J1168" s="1"/>
       <c r="K1168" s="1" t="s">
-        <v>2765</v>
+        <v>2786</v>
       </c>
     </row>
     <row r="1169" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -61167,9 +61190,11 @@
       </c>
       <c r="H1230" s="1"/>
       <c r="I1230" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1230" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="J1230" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K1230" s="1" t="s">
         <v>2858</v>
       </c>
@@ -62995,7 +63020,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="1289" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1289" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1289" s="1" t="s">
         <v>2313</v>
       </c>
@@ -63021,9 +63046,11 @@
         <v>2976</v>
       </c>
       <c r="I1289" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J1289" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="J1289" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K1289" s="1" t="s">
         <v>1075</v>
       </c>

--- a/data/chapter2/FRED/subsets/species.xlsx
+++ b/data/chapter2/FRED/subsets/species.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://westernsydneyedu-my.sharepoint.com/personal/90963425_westernsydney_edu_au/Documents/PhD/code/data/chapter2/FRED/subsets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="728" documentId="8_{81FDA0CF-33C4-43D2-B8CA-CC5F96143B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2517040B-96C4-48F7-A303-9C797925BA81}"/>
+  <xr:revisionPtr revIDLastSave="730" documentId="8_{81FDA0CF-33C4-43D2-B8CA-CC5F96143B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6C4BD4F-BA9C-4628-A213-F529C9C523BD}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="456" activeTab="3" xr2:uid="{A5444074-DC77-415C-A9E2-2BBA8270EAFC}"/>
   </bookViews>
@@ -9771,9 +9771,9 @@
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{92DE4C38-9658-4F81-87D7-16EF2BBFE835}" name="species_hand_cleaned__2" displayName="species_hand_cleaned__2" ref="A1:K1302" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:K1302" xr:uid="{92DE4C38-9658-4F81-87D7-16EF2BBFE835}">
-    <filterColumn colId="1">
+    <filterColumn colId="2">
       <filters>
-        <filter val="Myriocarpa"/>
+        <filter val="Fabaceae"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -22531,7 +22531,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>75</v>
       </c>
@@ -22564,7 +22564,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>76</v>
       </c>
@@ -22595,7 +22595,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>77</v>
       </c>
@@ -25265,7 +25265,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
         <v>12</v>
       </c>
@@ -25296,7 +25296,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
         <v>1045</v>
       </c>
@@ -25641,7 +25641,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="102" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
         <v>144</v>
       </c>
@@ -25672,7 +25672,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="103" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
         <v>145</v>
       </c>
@@ -26705,7 +26705,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="136" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
         <v>1308</v>
       </c>
@@ -26771,7 +26771,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="138" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
         <v>1310</v>
       </c>
@@ -26961,7 +26961,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="144" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A144" s="1" t="s">
         <v>1006</v>
       </c>
@@ -27432,7 +27432,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="159" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A159" s="1" t="s">
         <v>1313</v>
       </c>
@@ -28122,7 +28122,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="181" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A181" s="1" t="s">
         <v>959</v>
       </c>
@@ -30047,7 +30047,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="242" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A242" s="1" t="s">
         <v>19</v>
       </c>
@@ -30111,7 +30111,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="244" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A244" s="1" t="s">
         <v>947</v>
       </c>
@@ -31340,7 +31340,7 @@
         <v>2804</v>
       </c>
     </row>
-    <row r="283" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A283" s="1" t="s">
         <v>192</v>
       </c>
@@ -33358,7 +33358,7 @@
         <v>1645</v>
       </c>
     </row>
-    <row r="347" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A347" s="1" t="s">
         <v>1391</v>
       </c>
@@ -37137,7 +37137,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="467" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A467" s="1" t="s">
         <v>231</v>
       </c>
@@ -37199,7 +37199,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="469" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A469" s="1" t="s">
         <v>951</v>
       </c>
@@ -37577,7 +37577,7 @@
         <v>1835</v>
       </c>
     </row>
-    <row r="481" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A481" s="1" t="s">
         <v>257</v>
       </c>
@@ -37763,7 +37763,7 @@
         <v>1844</v>
       </c>
     </row>
-    <row r="487" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A487" s="1" t="s">
         <v>1581</v>
       </c>
@@ -37796,7 +37796,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="488" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A488" s="1" t="s">
         <v>1584</v>
       </c>
@@ -37829,7 +37829,7 @@
         <v>1585</v>
       </c>
     </row>
-    <row r="489" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A489" s="1" t="s">
         <v>1630</v>
       </c>
@@ -37862,7 +37862,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="490" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A490" s="1" t="s">
         <v>29</v>
       </c>
@@ -37893,7 +37893,7 @@
         <v>1647</v>
       </c>
     </row>
-    <row r="491" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A491" s="1" t="s">
         <v>1666</v>
       </c>
@@ -38021,7 +38021,7 @@
         <v>1864</v>
       </c>
     </row>
-    <row r="495" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A495" s="1" t="s">
         <v>1705</v>
       </c>
@@ -38054,7 +38054,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="496" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A496" s="1" t="s">
         <v>398</v>
       </c>
@@ -38085,7 +38085,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="497" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A497" s="1" t="s">
         <v>1851</v>
       </c>
@@ -38182,7 +38182,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="500" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A500" s="1" t="s">
         <v>401</v>
       </c>
@@ -38244,7 +38244,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="502" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A502" s="1" t="s">
         <v>948</v>
       </c>
@@ -38275,7 +38275,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="503" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A503" s="1" t="s">
         <v>425</v>
       </c>
@@ -38306,7 +38306,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="504" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A504" s="1" t="s">
         <v>426</v>
       </c>
@@ -38368,7 +38368,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="506" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A506" s="1" t="s">
         <v>427</v>
       </c>
@@ -38399,7 +38399,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="507" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A507" s="1" t="s">
         <v>428</v>
       </c>
@@ -38461,7 +38461,7 @@
         <v>1887</v>
       </c>
     </row>
-    <row r="509" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A509" s="1" t="s">
         <v>429</v>
       </c>
@@ -38523,7 +38523,7 @@
         <v>1894</v>
       </c>
     </row>
-    <row r="511" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A511" s="1" t="s">
         <v>430</v>
       </c>
@@ -41176,7 +41176,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="594" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A594" s="1" t="s">
         <v>2020</v>
       </c>
@@ -41209,7 +41209,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="595" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A595" s="1" t="s">
         <v>431</v>
       </c>
@@ -41240,7 +41240,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="596" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A596" s="1" t="s">
         <v>432</v>
       </c>
@@ -41271,7 +41271,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="597" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A597" s="1" t="s">
         <v>433</v>
       </c>
@@ -41302,7 +41302,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="598" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A598" s="1" t="s">
         <v>2022</v>
       </c>
@@ -41335,7 +41335,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="599" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A599" s="1" t="s">
         <v>434</v>
       </c>
@@ -41366,7 +41366,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="600" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A600" s="1" t="s">
         <v>435</v>
       </c>
@@ -41430,7 +41430,7 @@
         <v>2446</v>
       </c>
     </row>
-    <row r="602" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A602" s="1" t="s">
         <v>45</v>
       </c>
@@ -41461,7 +41461,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="603" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A603" s="1" t="s">
         <v>436</v>
       </c>
@@ -41492,7 +41492,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="604" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A604" s="1" t="s">
         <v>437</v>
       </c>
@@ -41556,7 +41556,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="606" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A606" s="1" t="s">
         <v>2026</v>
       </c>
@@ -41589,7 +41589,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="607" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A607" s="1" t="s">
         <v>438</v>
       </c>
@@ -41620,7 +41620,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="608" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A608" s="1" t="s">
         <v>439</v>
       </c>
@@ -41651,7 +41651,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="609" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A609" s="1" t="s">
         <v>440</v>
       </c>
@@ -41682,7 +41682,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="610" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A610" s="1" t="s">
         <v>441</v>
       </c>
@@ -41746,7 +41746,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="612" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A612" s="1" t="s">
         <v>442</v>
       </c>
@@ -41777,7 +41777,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="613" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A613" s="1" t="s">
         <v>443</v>
       </c>
@@ -41808,7 +41808,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="614" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A614" s="1" t="s">
         <v>444</v>
       </c>
@@ -41839,7 +41839,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="615" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A615" s="1" t="s">
         <v>2078</v>
       </c>
@@ -41872,7 +41872,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="616" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A616" s="1" t="s">
         <v>481</v>
       </c>
@@ -41903,7 +41903,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="617" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A617" s="1" t="s">
         <v>49</v>
       </c>
@@ -41934,7 +41934,7 @@
         <v>2107</v>
       </c>
     </row>
-    <row r="618" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A618" s="1" t="s">
         <v>2108</v>
       </c>
@@ -43372,7 +43372,7 @@
         <v>2105</v>
       </c>
     </row>
-    <row r="664" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A664" s="1" t="s">
         <v>994</v>
       </c>
@@ -43403,7 +43403,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="665" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A665" s="1" t="s">
         <v>519</v>
       </c>
@@ -43467,7 +43467,7 @@
         <v>1767</v>
       </c>
     </row>
-    <row r="667" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A667" s="1" t="s">
         <v>2174</v>
       </c>
@@ -45260,7 +45260,7 @@
         <v>2172</v>
       </c>
     </row>
-    <row r="724" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="724" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A724" s="1" t="s">
         <v>565</v>
       </c>
@@ -46849,7 +46849,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="775" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="775" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A775" s="1" t="s">
         <v>566</v>
       </c>
@@ -46880,7 +46880,7 @@
         <v>2234</v>
       </c>
     </row>
-    <row r="776" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="776" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A776" s="1" t="s">
         <v>567</v>
       </c>
@@ -46911,7 +46911,7 @@
         <v>2235</v>
       </c>
     </row>
-    <row r="777" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="777" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A777" s="1" t="s">
         <v>570</v>
       </c>
@@ -47004,7 +47004,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="780" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="780" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A780" s="1" t="s">
         <v>589</v>
       </c>
@@ -47857,7 +47857,7 @@
         <v>2276</v>
       </c>
     </row>
-    <row r="807" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="807" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A807" s="1" t="s">
         <v>1027</v>
       </c>
@@ -50724,7 +50724,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="898" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="898" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A898" s="1" t="s">
         <v>708</v>
       </c>
@@ -53236,7 +53236,7 @@
         <v>2513</v>
       </c>
     </row>
-    <row r="978" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="978" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A978" s="1" t="s">
         <v>845</v>
       </c>
@@ -59228,7 +59228,7 @@
         <v>2763</v>
       </c>
     </row>
-    <row r="1168" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1168" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1168" s="1" t="s">
         <v>2784</v>
       </c>
@@ -59887,7 +59887,7 @@
         <v>2795</v>
       </c>
     </row>
-    <row r="1189" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1189" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1189" s="1" t="s">
         <v>860</v>
       </c>
@@ -61104,7 +61104,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="1228" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1228" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1228" s="1" t="s">
         <v>1015</v>
       </c>
@@ -61767,7 +61767,7 @@
         <v>2750</v>
       </c>
     </row>
-    <row r="1249" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1249" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1249" s="1" t="s">
         <v>899</v>
       </c>
@@ -61798,7 +61798,7 @@
         <v>2886</v>
       </c>
     </row>
-    <row r="1250" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1250" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1250" s="1" t="s">
         <v>900</v>
       </c>
@@ -61829,7 +61829,7 @@
         <v>2887</v>
       </c>
     </row>
-    <row r="1251" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1251" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1251" s="1" t="s">
         <v>938</v>
       </c>
@@ -61860,7 +61860,7 @@
         <v>2888</v>
       </c>
     </row>
-    <row r="1252" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1252" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1252" s="1" t="s">
         <v>901</v>
       </c>
@@ -61891,7 +61891,7 @@
         <v>2889</v>
       </c>
     </row>
-    <row r="1253" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1253" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1253" s="1" t="s">
         <v>902</v>
       </c>
@@ -62079,7 +62079,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="1259" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1259" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1259" s="1" t="s">
         <v>70</v>
       </c>
@@ -62738,7 +62738,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="1280" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1280" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1280" s="1" t="s">
         <v>1016</v>
       </c>
@@ -62769,7 +62769,7 @@
         <v>2932</v>
       </c>
     </row>
-    <row r="1281" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1281" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1281" s="1" t="s">
         <v>72</v>
       </c>
@@ -63020,7 +63020,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="1289" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1289" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1289" s="1" t="s">
         <v>2313</v>
       </c>
@@ -63432,7 +63432,7 @@
         <v>2963</v>
       </c>
     </row>
-    <row r="1302" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1302" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1302" s="1" t="s">
         <v>930</v>
       </c>

--- a/data/chapter2/FRED/subsets/species.xlsx
+++ b/data/chapter2/FRED/subsets/species.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://westernsydneyedu-my.sharepoint.com/personal/90963425_westernsydney_edu_au/Documents/PhD/code/data/chapter2/FRED/subsets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="730" documentId="8_{81FDA0CF-33C4-43D2-B8CA-CC5F96143B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6C4BD4F-BA9C-4628-A213-F529C9C523BD}"/>
+  <xr:revisionPtr revIDLastSave="738" documentId="8_{81FDA0CF-33C4-43D2-B8CA-CC5F96143B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00D8A1E6-40F6-4111-9A85-996DE538BE4B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="456" activeTab="3" xr2:uid="{A5444074-DC77-415C-A9E2-2BBA8270EAFC}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15379" uniqueCount="2979">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15383" uniqueCount="2979">
   <si>
     <t>F00645</t>
   </si>
@@ -43396,9 +43396,11 @@
       </c>
       <c r="H664" s="1"/>
       <c r="I664" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J664" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="J664" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K664" s="1" t="s">
         <v>2109</v>
       </c>
@@ -43427,9 +43429,11 @@
       </c>
       <c r="H665" s="1"/>
       <c r="I665" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J665" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="J665" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K665" s="1" t="s">
         <v>1075</v>
       </c>
@@ -47881,9 +47885,11 @@
       </c>
       <c r="H807" s="1"/>
       <c r="I807" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J807" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="J807" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K807" s="1" t="s">
         <v>2400</v>
       </c>
@@ -61884,9 +61890,11 @@
       </c>
       <c r="H1252" s="1"/>
       <c r="I1252" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1252" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="J1252" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K1252" s="1" t="s">
         <v>2889</v>
       </c>

--- a/data/chapter2/FRED/subsets/species.xlsx
+++ b/data/chapter2/FRED/subsets/species.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://westernsydneyedu-my.sharepoint.com/personal/90963425_westernsydney_edu_au/Documents/PhD/code/data/chapter2/FRED/subsets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="738" documentId="8_{81FDA0CF-33C4-43D2-B8CA-CC5F96143B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00D8A1E6-40F6-4111-9A85-996DE538BE4B}"/>
+  <xr:revisionPtr revIDLastSave="813" documentId="8_{81FDA0CF-33C4-43D2-B8CA-CC5F96143B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87EEBF4A-DAA0-4826-94E6-4564C75A0E5B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="456" activeTab="3" xr2:uid="{A5444074-DC77-415C-A9E2-2BBA8270EAFC}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15383" uniqueCount="2979">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15411" uniqueCount="2979">
   <si>
     <t>F00645</t>
   </si>
@@ -9771,9 +9771,9 @@
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{92DE4C38-9658-4F81-87D7-16EF2BBFE835}" name="species_hand_cleaned__2" displayName="species_hand_cleaned__2" ref="A1:K1302" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:K1302" xr:uid="{92DE4C38-9658-4F81-87D7-16EF2BBFE835}">
-    <filterColumn colId="2">
+    <filterColumn colId="1">
       <filters>
-        <filter val="Fabaceae"/>
+        <filter val="Oreocnide"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -22531,7 +22531,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>75</v>
       </c>
@@ -22564,7 +22564,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>76</v>
       </c>
@@ -22595,7 +22595,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>77</v>
       </c>
@@ -25265,7 +25265,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
         <v>12</v>
       </c>
@@ -25296,7 +25296,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
         <v>1045</v>
       </c>
@@ -25351,9 +25351,11 @@
       </c>
       <c r="H92" s="1"/>
       <c r="I92" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J92" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K92" s="1" t="s">
         <v>1242</v>
       </c>
@@ -25641,7 +25643,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
         <v>144</v>
       </c>
@@ -25672,7 +25674,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
         <v>145</v>
       </c>
@@ -25789,9 +25791,11 @@
       </c>
       <c r="H106" s="1"/>
       <c r="I106" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J106" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="J106" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K106" s="1" t="s">
         <v>1264</v>
       </c>
@@ -26705,7 +26709,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
         <v>1308</v>
       </c>
@@ -26771,7 +26775,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
         <v>1310</v>
       </c>
@@ -26961,7 +26965,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" s="1" t="s">
         <v>1006</v>
       </c>
@@ -27432,7 +27436,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" s="1" t="s">
         <v>1313</v>
       </c>
@@ -27929,9 +27933,11 @@
       </c>
       <c r="H174" s="1"/>
       <c r="I174" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J174" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="J174" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K174" s="1" t="s">
         <v>1370</v>
       </c>
@@ -28122,7 +28128,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" s="1" t="s">
         <v>959</v>
       </c>
@@ -29156,9 +29162,11 @@
       </c>
       <c r="H213" s="1"/>
       <c r="I213" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J213" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="J213" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K213" s="1" t="s">
         <v>1436</v>
       </c>
@@ -29470,9 +29478,11 @@
       </c>
       <c r="H223" s="1"/>
       <c r="I223" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J223" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="J223" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K223" s="1" t="s">
         <v>1444</v>
       </c>
@@ -30047,7 +30057,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A242" s="1" t="s">
         <v>19</v>
       </c>
@@ -30111,7 +30121,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244" s="1" t="s">
         <v>947</v>
       </c>
@@ -31267,9 +31277,11 @@
       </c>
       <c r="H280" s="1"/>
       <c r="I280" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J280" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="J280" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K280" s="1" t="s">
         <v>1538</v>
       </c>
@@ -31340,7 +31352,7 @@
         <v>2804</v>
       </c>
     </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A283" s="1" t="s">
         <v>192</v>
       </c>
@@ -31494,9 +31506,11 @@
       </c>
       <c r="H287" s="1"/>
       <c r="I287" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J287" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="J287" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K287" s="1" t="s">
         <v>1075</v>
       </c>
@@ -31525,9 +31539,11 @@
       </c>
       <c r="H288" s="1"/>
       <c r="I288" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J288" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="J288" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K288" s="1" t="s">
         <v>1555</v>
       </c>
@@ -33358,7 +33374,7 @@
         <v>1645</v>
       </c>
     </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A347" s="1" t="s">
         <v>1391</v>
       </c>
@@ -33572,9 +33588,11 @@
       </c>
       <c r="H353" s="1"/>
       <c r="I353" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J353" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="J353" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K353" s="1" t="s">
         <v>1663</v>
       </c>
@@ -33791,9 +33809,11 @@
       </c>
       <c r="H360" s="1"/>
       <c r="I360" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J360" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="J360" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K360" s="1" t="s">
         <v>1678</v>
       </c>
@@ -35210,9 +35230,11 @@
       </c>
       <c r="H405" s="1"/>
       <c r="I405" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J405" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="J405" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K405" s="1" t="s">
         <v>1751</v>
       </c>
@@ -36811,9 +36833,11 @@
       </c>
       <c r="H456" s="1"/>
       <c r="I456" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J456" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="J456" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K456" s="1" t="s">
         <v>1811</v>
       </c>
@@ -36842,9 +36866,11 @@
       </c>
       <c r="H457" s="1"/>
       <c r="I457" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J457" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="J457" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K457" s="1" t="s">
         <v>1812</v>
       </c>
@@ -37137,7 +37163,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="467" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A467" s="1" t="s">
         <v>231</v>
       </c>
@@ -37199,7 +37225,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="469" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A469" s="1" t="s">
         <v>951</v>
       </c>
@@ -37577,7 +37603,7 @@
         <v>1835</v>
       </c>
     </row>
-    <row r="481" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A481" s="1" t="s">
         <v>257</v>
       </c>
@@ -37763,7 +37789,7 @@
         <v>1844</v>
       </c>
     </row>
-    <row r="487" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A487" s="1" t="s">
         <v>1581</v>
       </c>
@@ -37796,7 +37822,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="488" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A488" s="1" t="s">
         <v>1584</v>
       </c>
@@ -37829,7 +37855,7 @@
         <v>1585</v>
       </c>
     </row>
-    <row r="489" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A489" s="1" t="s">
         <v>1630</v>
       </c>
@@ -37862,7 +37888,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="490" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A490" s="1" t="s">
         <v>29</v>
       </c>
@@ -37893,7 +37919,7 @@
         <v>1647</v>
       </c>
     </row>
-    <row r="491" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A491" s="1" t="s">
         <v>1666</v>
       </c>
@@ -38021,7 +38047,7 @@
         <v>1864</v>
       </c>
     </row>
-    <row r="495" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A495" s="1" t="s">
         <v>1705</v>
       </c>
@@ -38054,7 +38080,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="496" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A496" s="1" t="s">
         <v>398</v>
       </c>
@@ -38085,7 +38111,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="497" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A497" s="1" t="s">
         <v>1851</v>
       </c>
@@ -38182,7 +38208,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="500" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A500" s="1" t="s">
         <v>401</v>
       </c>
@@ -38237,14 +38263,16 @@
       </c>
       <c r="H501" s="1"/>
       <c r="I501" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J501" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="J501" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K501" s="1" t="s">
         <v>1075</v>
       </c>
     </row>
-    <row r="502" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A502" s="1" t="s">
         <v>948</v>
       </c>
@@ -38275,7 +38303,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="503" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A503" s="1" t="s">
         <v>425</v>
       </c>
@@ -38306,7 +38334,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="504" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A504" s="1" t="s">
         <v>426</v>
       </c>
@@ -38368,7 +38396,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="506" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A506" s="1" t="s">
         <v>427</v>
       </c>
@@ -38399,7 +38427,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="507" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A507" s="1" t="s">
         <v>428</v>
       </c>
@@ -38461,7 +38489,7 @@
         <v>1887</v>
       </c>
     </row>
-    <row r="509" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A509" s="1" t="s">
         <v>429</v>
       </c>
@@ -38523,7 +38551,7 @@
         <v>1894</v>
       </c>
     </row>
-    <row r="511" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A511" s="1" t="s">
         <v>430</v>
       </c>
@@ -41176,7 +41204,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="594" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A594" s="1" t="s">
         <v>2020</v>
       </c>
@@ -41209,7 +41237,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="595" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A595" s="1" t="s">
         <v>431</v>
       </c>
@@ -41240,7 +41268,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="596" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A596" s="1" t="s">
         <v>432</v>
       </c>
@@ -41271,7 +41299,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="597" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A597" s="1" t="s">
         <v>433</v>
       </c>
@@ -41302,7 +41330,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="598" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A598" s="1" t="s">
         <v>2022</v>
       </c>
@@ -41335,7 +41363,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="599" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A599" s="1" t="s">
         <v>434</v>
       </c>
@@ -41366,7 +41394,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="600" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A600" s="1" t="s">
         <v>435</v>
       </c>
@@ -41430,7 +41458,7 @@
         <v>2446</v>
       </c>
     </row>
-    <row r="602" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A602" s="1" t="s">
         <v>45</v>
       </c>
@@ -41461,7 +41489,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="603" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A603" s="1" t="s">
         <v>436</v>
       </c>
@@ -41492,7 +41520,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="604" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A604" s="1" t="s">
         <v>437</v>
       </c>
@@ -41556,7 +41584,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="606" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A606" s="1" t="s">
         <v>2026</v>
       </c>
@@ -41589,7 +41617,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="607" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A607" s="1" t="s">
         <v>438</v>
       </c>
@@ -41620,7 +41648,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="608" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A608" s="1" t="s">
         <v>439</v>
       </c>
@@ -41651,7 +41679,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="609" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A609" s="1" t="s">
         <v>440</v>
       </c>
@@ -41682,7 +41710,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="610" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A610" s="1" t="s">
         <v>441</v>
       </c>
@@ -41746,7 +41774,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="612" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A612" s="1" t="s">
         <v>442</v>
       </c>
@@ -41777,7 +41805,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="613" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A613" s="1" t="s">
         <v>443</v>
       </c>
@@ -41808,7 +41836,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="614" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A614" s="1" t="s">
         <v>444</v>
       </c>
@@ -41839,7 +41867,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="615" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A615" s="1" t="s">
         <v>2078</v>
       </c>
@@ -41872,7 +41900,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="616" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A616" s="1" t="s">
         <v>481</v>
       </c>
@@ -41903,7 +41931,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="617" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A617" s="1" t="s">
         <v>49</v>
       </c>
@@ -41934,7 +41962,7 @@
         <v>2107</v>
       </c>
     </row>
-    <row r="618" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A618" s="1" t="s">
         <v>2108</v>
       </c>
@@ -42863,9 +42891,11 @@
       </c>
       <c r="H647" s="1"/>
       <c r="I647" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J647" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="J647" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K647" s="1" t="s">
         <v>2076</v>
       </c>
@@ -43372,7 +43402,7 @@
         <v>2105</v>
       </c>
     </row>
-    <row r="664" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A664" s="1" t="s">
         <v>994</v>
       </c>
@@ -43405,7 +43435,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="665" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A665" s="1" t="s">
         <v>519</v>
       </c>
@@ -43471,7 +43501,7 @@
         <v>1767</v>
       </c>
     </row>
-    <row r="667" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A667" s="1" t="s">
         <v>2174</v>
       </c>
@@ -44123,9 +44153,11 @@
       </c>
       <c r="H687" s="1"/>
       <c r="I687" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J687" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="J687" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K687" s="1" t="s">
         <v>1075</v>
       </c>
@@ -45164,9 +45196,11 @@
       </c>
       <c r="H720" s="1"/>
       <c r="I720" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J720" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="J720" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K720" s="1" t="s">
         <v>2166</v>
       </c>
@@ -45264,7 +45298,7 @@
         <v>2172</v>
       </c>
     </row>
-    <row r="724" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="724" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A724" s="1" t="s">
         <v>565</v>
       </c>
@@ -46853,7 +46887,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="775" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="775" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A775" s="1" t="s">
         <v>566</v>
       </c>
@@ -46884,7 +46918,7 @@
         <v>2234</v>
       </c>
     </row>
-    <row r="776" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="776" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A776" s="1" t="s">
         <v>567</v>
       </c>
@@ -46915,7 +46949,7 @@
         <v>2235</v>
       </c>
     </row>
-    <row r="777" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="777" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A777" s="1" t="s">
         <v>570</v>
       </c>
@@ -47008,7 +47042,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="780" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="780" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A780" s="1" t="s">
         <v>589</v>
       </c>
@@ -47861,7 +47895,7 @@
         <v>2276</v>
       </c>
     </row>
-    <row r="807" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="807" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A807" s="1" t="s">
         <v>1027</v>
       </c>
@@ -49556,9 +49590,11 @@
       </c>
       <c r="H860" s="1"/>
       <c r="I860" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J860" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="J860" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K860" s="1" t="s">
         <v>2352</v>
       </c>
@@ -49587,9 +49623,11 @@
       </c>
       <c r="H861" s="1"/>
       <c r="I861" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J861" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="J861" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K861" s="1" t="s">
         <v>2353</v>
       </c>
@@ -49649,9 +49687,11 @@
       </c>
       <c r="H863" s="1"/>
       <c r="I863" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J863" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="J863" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K863" s="1" t="s">
         <v>2355</v>
       </c>
@@ -50507,7 +50547,7 @@
         <v>2383</v>
       </c>
     </row>
-    <row r="891" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="891" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A891" s="1" t="s">
         <v>649</v>
       </c>
@@ -50531,7 +50571,7 @@
       </c>
       <c r="H891" s="1"/>
       <c r="I891" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J891" s="1" t="s">
         <v>2975</v>
@@ -50730,7 +50770,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="898" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="898" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A898" s="1" t="s">
         <v>708</v>
       </c>
@@ -51194,9 +51234,11 @@
       </c>
       <c r="H912" s="1"/>
       <c r="I912" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J912" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="J912" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K912" s="1" t="s">
         <v>2419</v>
       </c>
@@ -51921,9 +51963,11 @@
       </c>
       <c r="H935" s="1"/>
       <c r="I935" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J935" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="J935" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K935" s="1" t="s">
         <v>2457</v>
       </c>
@@ -53242,7 +53286,7 @@
         <v>2513</v>
       </c>
     </row>
-    <row r="978" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="978" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A978" s="1" t="s">
         <v>845</v>
       </c>
@@ -53299,9 +53343,11 @@
         <v>2976</v>
       </c>
       <c r="I979" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J979" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="J979" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K979" s="1" t="s">
         <v>2620</v>
       </c>
@@ -58277,9 +58323,11 @@
       </c>
       <c r="H1137" s="1"/>
       <c r="I1137" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J1137" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="J1137" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K1137" s="1" t="s">
         <v>2709</v>
       </c>
@@ -59234,7 +59282,7 @@
         <v>2763</v>
       </c>
     </row>
-    <row r="1168" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1168" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1168" s="1" t="s">
         <v>2784</v>
       </c>
@@ -59893,7 +59941,7 @@
         <v>2795</v>
       </c>
     </row>
-    <row r="1189" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1189" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1189" s="1" t="s">
         <v>860</v>
       </c>
@@ -60264,9 +60312,11 @@
       </c>
       <c r="H1200" s="1"/>
       <c r="I1200" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1200" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="J1200" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K1200" s="1" t="s">
         <v>2816</v>
       </c>
@@ -60450,9 +60500,11 @@
       </c>
       <c r="H1206" s="1"/>
       <c r="I1206" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="J1206" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="J1206" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K1206" s="1" t="s">
         <v>2823</v>
       </c>
@@ -61110,7 +61162,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="1228" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1228" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1228" s="1" t="s">
         <v>1015</v>
       </c>
@@ -61417,9 +61469,11 @@
       </c>
       <c r="H1237" s="1"/>
       <c r="I1237" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1237" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="J1237" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K1237" s="1" t="s">
         <v>2865</v>
       </c>
@@ -61773,7 +61827,7 @@
         <v>2750</v>
       </c>
     </row>
-    <row r="1249" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1249" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1249" s="1" t="s">
         <v>899</v>
       </c>
@@ -61804,7 +61858,7 @@
         <v>2886</v>
       </c>
     </row>
-    <row r="1250" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1250" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1250" s="1" t="s">
         <v>900</v>
       </c>
@@ -61835,7 +61889,7 @@
         <v>2887</v>
       </c>
     </row>
-    <row r="1251" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1251" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1251" s="1" t="s">
         <v>938</v>
       </c>
@@ -61866,7 +61920,7 @@
         <v>2888</v>
       </c>
     </row>
-    <row r="1252" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1252" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1252" s="1" t="s">
         <v>901</v>
       </c>
@@ -61899,7 +61953,7 @@
         <v>2889</v>
       </c>
     </row>
-    <row r="1253" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1253" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1253" s="1" t="s">
         <v>902</v>
       </c>
@@ -62087,7 +62141,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="1259" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1259" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1259" s="1" t="s">
         <v>70</v>
       </c>
@@ -62580,9 +62634,11 @@
       </c>
       <c r="H1274" s="1"/>
       <c r="I1274" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1274" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="J1274" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K1274" s="1" t="s">
         <v>2924</v>
       </c>
@@ -62746,7 +62802,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="1280" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1280" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1280" s="1" t="s">
         <v>1016</v>
       </c>
@@ -62777,7 +62833,7 @@
         <v>2932</v>
       </c>
     </row>
-    <row r="1281" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1281" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1281" s="1" t="s">
         <v>72</v>
       </c>
@@ -63440,7 +63496,7 @@
         <v>2963</v>
       </c>
     </row>
-    <row r="1302" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1302" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1302" s="1" t="s">
         <v>930</v>
       </c>

--- a/data/chapter2/FRED/subsets/species.xlsx
+++ b/data/chapter2/FRED/subsets/species.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://westernsydneyedu-my.sharepoint.com/personal/90963425_westernsydney_edu_au/Documents/PhD/code/data/chapter2/FRED/subsets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="813" documentId="8_{81FDA0CF-33C4-43D2-B8CA-CC5F96143B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87EEBF4A-DAA0-4826-94E6-4564C75A0E5B}"/>
+  <xr:revisionPtr revIDLastSave="896" documentId="8_{81FDA0CF-33C4-43D2-B8CA-CC5F96143B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADD079F2-51F8-46AB-A110-F06B2B368BBD}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="456" activeTab="3" xr2:uid="{A5444074-DC77-415C-A9E2-2BBA8270EAFC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="426" firstSheet="1" activeTab="3" xr2:uid="{A5444074-DC77-415C-A9E2-2BBA8270EAFC}"/>
   </bookViews>
   <sheets>
     <sheet name="FRED4" sheetId="8" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15411" uniqueCount="2979">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15436" uniqueCount="2979">
   <si>
     <t>F00645</t>
   </si>
@@ -9771,13 +9771,13 @@
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{92DE4C38-9658-4F81-87D7-16EF2BBFE835}" name="species_hand_cleaned__2" displayName="species_hand_cleaned__2" ref="A1:K1302" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:K1302" xr:uid="{92DE4C38-9658-4F81-87D7-16EF2BBFE835}">
-    <filterColumn colId="1">
+    <filterColumn colId="2">
       <filters>
-        <filter val="Oreocnide"/>
+        <filter val="Aspleniaceae"/>
       </filters>
     </filterColumn>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:K1302">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A993:K1180">
     <sortCondition ref="A1:A1302"/>
   </sortState>
   <tableColumns count="11">
@@ -23339,9 +23339,11 @@
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J28" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K28" s="1" t="s">
         <v>1102</v>
       </c>
@@ -24810,9 +24812,11 @@
       </c>
       <c r="H75" s="1"/>
       <c r="I75" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J75" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="J75" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="K75" s="1" t="s">
         <v>1210</v>
       </c>
@@ -26393,7 +26397,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="126" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A126" s="1" t="s">
         <v>157</v>
       </c>
@@ -26605,9 +26609,11 @@
       </c>
       <c r="H132" s="1"/>
       <c r="I132" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J132" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="J132" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K132" s="1" t="s">
         <v>1075</v>
       </c>
@@ -26636,14 +26642,16 @@
       </c>
       <c r="H133" s="1"/>
       <c r="I133" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J133" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="J133" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K133" s="1" t="s">
         <v>1075</v>
       </c>
     </row>
-    <row r="134" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A134" s="1" t="s">
         <v>1351</v>
       </c>
@@ -26676,7 +26684,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="135" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A135" s="1" t="s">
         <v>1353</v>
       </c>
@@ -28475,10 +28483,10 @@
     </row>
     <row r="192" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" s="1" t="s">
-        <v>201</v>
+        <v>1329</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>1406</v>
+        <v>1330</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>1115</v>
@@ -28487,21 +28495,23 @@
         <v>1116</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>2</v>
+        <v>1075</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>2968</v>
+        <v>1075</v>
       </c>
       <c r="G192" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H192" s="1"/>
+      <c r="H192" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="I192" s="1" t="s">
         <v>2</v>
       </c>
       <c r="J192" s="1"/>
       <c r="K192" s="1" t="s">
-        <v>1407</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="193" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -29582,10 +29592,10 @@
     </row>
     <row r="227" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227" s="1" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>1451</v>
+        <v>1406</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>1115</v>
@@ -29608,7 +29618,7 @@
       </c>
       <c r="J227" s="1"/>
       <c r="K227" s="1" t="s">
-        <v>1452</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="228" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -30238,19 +30248,21 @@
       </c>
       <c r="H247" s="1"/>
       <c r="I247" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J247" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="J247" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="K247" s="1" t="s">
         <v>1494</v>
       </c>
     </row>
     <row r="248" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A248" s="1" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>1495</v>
+        <v>1451</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>1115</v>
@@ -30273,7 +30285,7 @@
       </c>
       <c r="J248" s="1"/>
       <c r="K248" s="1" t="s">
-        <v>1496</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="249" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -30404,10 +30416,10 @@
     </row>
     <row r="253" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253" s="1" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>1507</v>
+        <v>1495</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>1115</v>
@@ -30430,12 +30442,12 @@
       </c>
       <c r="J253" s="1"/>
       <c r="K253" s="1" t="s">
-        <v>1075</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="254" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A254" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B254" s="1" t="s">
         <v>1507</v>
@@ -30461,7 +30473,7 @@
       </c>
       <c r="J254" s="1"/>
       <c r="K254" s="1" t="s">
-        <v>1508</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="255" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -31676,10 +31688,10 @@
     </row>
     <row r="293" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A293" s="1" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>1565</v>
+        <v>1507</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>1115</v>
@@ -31702,12 +31714,12 @@
       </c>
       <c r="J293" s="1"/>
       <c r="K293" s="1" t="s">
-        <v>1075</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="294" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A294" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B294" s="1" t="s">
         <v>1565</v>
@@ -31738,7 +31750,7 @@
     </row>
     <row r="295" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A295" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B295" s="1" t="s">
         <v>1565</v>
@@ -31764,12 +31776,12 @@
       </c>
       <c r="J295" s="1"/>
       <c r="K295" s="1" t="s">
-        <v>1566</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="296" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A296" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B296" s="1" t="s">
         <v>1565</v>
@@ -31795,12 +31807,12 @@
       </c>
       <c r="J296" s="1"/>
       <c r="K296" s="1" t="s">
-        <v>1075</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="297" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A297" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B297" s="1" t="s">
         <v>1565</v>
@@ -31831,10 +31843,10 @@
     </row>
     <row r="298" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A298" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>1115</v>
@@ -31857,7 +31869,7 @@
       </c>
       <c r="J298" s="1"/>
       <c r="K298" s="1" t="s">
-        <v>1568</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="299" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -32514,9 +32526,11 @@
       </c>
       <c r="H319" s="1"/>
       <c r="I319" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J319" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="J319" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="K319" s="1" t="s">
         <v>1599</v>
       </c>
@@ -33975,10 +33989,10 @@
     </row>
     <row r="366" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A366" s="1" t="s">
-        <v>318</v>
+        <v>267</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>1689</v>
+        <v>1567</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>1115</v>
@@ -34001,7 +34015,7 @@
       </c>
       <c r="J366" s="1"/>
       <c r="K366" s="1" t="s">
-        <v>1690</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="367" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -36247,10 +36261,10 @@
     </row>
     <row r="438" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A438" s="1" t="s">
-        <v>367</v>
+        <v>318</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>1789</v>
+        <v>1689</v>
       </c>
       <c r="C438" s="1" t="s">
         <v>1115</v>
@@ -36273,12 +36287,12 @@
       </c>
       <c r="J438" s="1"/>
       <c r="K438" s="1" t="s">
-        <v>1790</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="439" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A439" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B439" s="1" t="s">
         <v>1789</v>
@@ -36304,7 +36318,7 @@
       </c>
       <c r="J439" s="1"/>
       <c r="K439" s="1" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="440" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -36592,10 +36606,10 @@
     </row>
     <row r="449" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A449" s="1" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="B449" s="1" t="s">
-        <v>1805</v>
+        <v>1789</v>
       </c>
       <c r="C449" s="1" t="s">
         <v>1115</v>
@@ -36618,12 +36632,12 @@
       </c>
       <c r="J449" s="1"/>
       <c r="K449" s="1" t="s">
-        <v>1075</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="450" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A450" s="1" t="s">
-        <v>377</v>
+        <v>1804</v>
       </c>
       <c r="B450" s="1" t="s">
         <v>1805</v>
@@ -36635,15 +36649,17 @@
         <v>1116</v>
       </c>
       <c r="E450" s="1" t="s">
-        <v>2</v>
+        <v>1075</v>
       </c>
       <c r="F450" s="1" t="s">
-        <v>2968</v>
+        <v>1075</v>
       </c>
       <c r="G450" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H450" s="1"/>
+      <c r="H450" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="I450" s="1" t="s">
         <v>2</v>
       </c>
@@ -36654,7 +36670,7 @@
     </row>
     <row r="451" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A451" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B451" s="1" t="s">
         <v>1805</v>
@@ -36685,10 +36701,10 @@
     </row>
     <row r="452" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A452" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="C452" s="1" t="s">
         <v>1115</v>
@@ -36716,10 +36732,10 @@
     </row>
     <row r="453" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A453" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B453" s="1" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="C453" s="1" t="s">
         <v>1115</v>
@@ -36742,7 +36758,7 @@
       </c>
       <c r="J453" s="1"/>
       <c r="K453" s="1" t="s">
-        <v>1807</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="454" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -37280,9 +37296,11 @@
       </c>
       <c r="H470" s="1"/>
       <c r="I470" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J470" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="J470" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="K470" s="1" t="s">
         <v>1823</v>
       </c>
@@ -37636,10 +37654,10 @@
     </row>
     <row r="482" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A482" s="1" t="s">
-        <v>394</v>
+        <v>379</v>
       </c>
       <c r="B482" s="1" t="s">
-        <v>1839</v>
+        <v>1806</v>
       </c>
       <c r="C482" s="1" t="s">
         <v>1115</v>
@@ -37648,29 +37666,29 @@
         <v>1116</v>
       </c>
       <c r="E482" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F482" s="1" t="s">
         <v>2968</v>
       </c>
       <c r="G482" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H482" s="1"/>
       <c r="I482" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J482" s="1"/>
       <c r="K482" s="1" t="s">
-        <v>1840</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="483" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A483" s="1" t="s">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="B483" s="1" t="s">
-        <v>1839</v>
+        <v>1806</v>
       </c>
       <c r="C483" s="1" t="s">
         <v>1115</v>
@@ -37693,7 +37711,7 @@
       </c>
       <c r="J483" s="1"/>
       <c r="K483" s="1" t="s">
-        <v>1841</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="484" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -40181,9 +40199,11 @@
       </c>
       <c r="H561" s="1"/>
       <c r="I561" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J561" s="1"/>
+        <v>5</v>
+      </c>
+      <c r="J561" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K561" s="1" t="s">
         <v>1075</v>
       </c>
@@ -42121,10 +42141,10 @@
     </row>
     <row r="623" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A623" s="1" t="s">
-        <v>448</v>
+        <v>394</v>
       </c>
       <c r="B623" s="1" t="s">
-        <v>2042</v>
+        <v>1839</v>
       </c>
       <c r="C623" s="1" t="s">
         <v>1115</v>
@@ -42133,29 +42153,29 @@
         <v>1116</v>
       </c>
       <c r="E623" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F623" s="1" t="s">
         <v>2968</v>
       </c>
       <c r="G623" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H623" s="1"/>
       <c r="I623" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J623" s="1"/>
       <c r="K623" s="1" t="s">
-        <v>1075</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="624" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A624" s="1" t="s">
-        <v>449</v>
+        <v>395</v>
       </c>
       <c r="B624" s="1" t="s">
-        <v>2042</v>
+        <v>1839</v>
       </c>
       <c r="C624" s="1" t="s">
         <v>1115</v>
@@ -42174,11 +42194,13 @@
       </c>
       <c r="H624" s="1"/>
       <c r="I624" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J624" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="J624" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K624" s="1" t="s">
-        <v>1075</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="625" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -42424,9 +42446,11 @@
       </c>
       <c r="H632" s="1"/>
       <c r="I632" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J632" s="1"/>
+        <v>5</v>
+      </c>
+      <c r="J632" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K632" s="1" t="s">
         <v>2052</v>
       </c>
@@ -42650,10 +42674,10 @@
     </row>
     <row r="640" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A640" s="1" t="s">
-        <v>463</v>
+        <v>2002</v>
       </c>
       <c r="B640" s="1" t="s">
-        <v>2065</v>
+        <v>2003</v>
       </c>
       <c r="C640" s="1" t="s">
         <v>1115</v>
@@ -42662,29 +42686,31 @@
         <v>1116</v>
       </c>
       <c r="E640" s="1" t="s">
-        <v>2</v>
+        <v>1075</v>
       </c>
       <c r="F640" s="1" t="s">
-        <v>2968</v>
+        <v>1075</v>
       </c>
       <c r="G640" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H640" s="1"/>
+      <c r="H640" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="I640" s="1" t="s">
         <v>2</v>
       </c>
       <c r="J640" s="1"/>
       <c r="K640" s="1" t="s">
-        <v>2066</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="641" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A641" s="1" t="s">
-        <v>464</v>
+        <v>448</v>
       </c>
       <c r="B641" s="1" t="s">
-        <v>2065</v>
+        <v>2042</v>
       </c>
       <c r="C641" s="1" t="s">
         <v>1115</v>
@@ -42712,10 +42738,10 @@
     </row>
     <row r="642" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A642" s="1" t="s">
-        <v>465</v>
+        <v>449</v>
       </c>
       <c r="B642" s="1" t="s">
-        <v>2065</v>
+        <v>2042</v>
       </c>
       <c r="C642" s="1" t="s">
         <v>1115</v>
@@ -42738,7 +42764,7 @@
       </c>
       <c r="J642" s="1"/>
       <c r="K642" s="1" t="s">
-        <v>2067</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="643" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -50547,7 +50573,7 @@
         <v>2383</v>
       </c>
     </row>
-    <row r="891" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="891" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A891" s="1" t="s">
         <v>649</v>
       </c>
@@ -50896,10 +50922,10 @@
     </row>
     <row r="902" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A902" s="1" t="s">
-        <v>656</v>
+        <v>463</v>
       </c>
       <c r="B902" s="1" t="s">
-        <v>2405</v>
+        <v>2065</v>
       </c>
       <c r="C902" s="1" t="s">
         <v>1115</v>
@@ -50922,15 +50948,15 @@
       </c>
       <c r="J902" s="1"/>
       <c r="K902" s="1" t="s">
-        <v>1075</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="903" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A903" s="1" t="s">
-        <v>657</v>
+        <v>464</v>
       </c>
       <c r="B903" s="1" t="s">
-        <v>2406</v>
+        <v>2065</v>
       </c>
       <c r="C903" s="1" t="s">
         <v>1115</v>
@@ -50953,15 +50979,15 @@
       </c>
       <c r="J903" s="1"/>
       <c r="K903" s="1" t="s">
-        <v>2407</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="904" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A904" s="1" t="s">
-        <v>658</v>
+        <v>465</v>
       </c>
       <c r="B904" s="1" t="s">
-        <v>2406</v>
+        <v>2065</v>
       </c>
       <c r="C904" s="1" t="s">
         <v>1115</v>
@@ -50984,15 +51010,15 @@
       </c>
       <c r="J904" s="1"/>
       <c r="K904" s="1" t="s">
-        <v>2408</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="905" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A905" s="1" t="s">
-        <v>659</v>
+        <v>2070</v>
       </c>
       <c r="B905" s="1" t="s">
-        <v>2406</v>
+        <v>2071</v>
       </c>
       <c r="C905" s="1" t="s">
         <v>1115</v>
@@ -51001,29 +51027,31 @@
         <v>1116</v>
       </c>
       <c r="E905" s="1" t="s">
-        <v>2</v>
+        <v>1075</v>
       </c>
       <c r="F905" s="1" t="s">
-        <v>2968</v>
+        <v>1075</v>
       </c>
       <c r="G905" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H905" s="1"/>
+      <c r="H905" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="I905" s="1" t="s">
         <v>2</v>
       </c>
       <c r="J905" s="1"/>
       <c r="K905" s="1" t="s">
-        <v>2409</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="906" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A906" s="1" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="B906" s="1" t="s">
-        <v>2406</v>
+        <v>2405</v>
       </c>
       <c r="C906" s="1" t="s">
         <v>1115</v>
@@ -51046,12 +51074,12 @@
       </c>
       <c r="J906" s="1"/>
       <c r="K906" s="1" t="s">
-        <v>2410</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="907" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A907" s="1" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="B907" s="1" t="s">
         <v>2406</v>
@@ -51077,7 +51105,7 @@
       </c>
       <c r="J907" s="1"/>
       <c r="K907" s="1" t="s">
-        <v>2411</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="908" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -51181,7 +51209,7 @@
     </row>
     <row r="911" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A911" s="1" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="B911" s="1" t="s">
         <v>2406</v>
@@ -51207,7 +51235,7 @@
       </c>
       <c r="J911" s="1"/>
       <c r="K911" s="1" t="s">
-        <v>2417</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="912" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -53752,19 +53780,21 @@
       </c>
       <c r="H992" s="1"/>
       <c r="I992" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J992" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="J992" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="K992" s="1" t="s">
         <v>2536</v>
       </c>
     </row>
     <row r="993" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A993" s="1" t="s">
-        <v>717</v>
+        <v>1691</v>
       </c>
       <c r="B993" s="1" t="s">
-        <v>2537</v>
+        <v>1692</v>
       </c>
       <c r="C993" s="1" t="s">
         <v>1693</v>
@@ -53773,26 +53803,28 @@
         <v>1166</v>
       </c>
       <c r="E993" s="1" t="s">
-        <v>1</v>
+        <v>1075</v>
       </c>
       <c r="F993" s="1" t="s">
-        <v>2968</v>
+        <v>1075</v>
       </c>
       <c r="G993" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H993" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H993" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="I993" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J993" s="1"/>
       <c r="K993" s="1" t="s">
-        <v>2538</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="994" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A994" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B994" s="1" t="s">
         <v>2537</v>
@@ -53804,26 +53836,28 @@
         <v>1166</v>
       </c>
       <c r="E994" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F994" s="1" t="s">
         <v>2968</v>
       </c>
       <c r="G994" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H994" s="1"/>
       <c r="I994" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J994" s="1"/>
+      <c r="J994" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="K994" s="1" t="s">
-        <v>1075</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="995" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A995" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B995" s="1" t="s">
         <v>2537</v>
@@ -53835,17 +53869,17 @@
         <v>1166</v>
       </c>
       <c r="E995" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F995" s="1" t="s">
         <v>2968</v>
       </c>
       <c r="G995" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H995" s="1"/>
       <c r="I995" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J995" s="1"/>
       <c r="K995" s="1" t="s">
@@ -53854,7 +53888,7 @@
     </row>
     <row r="996" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A996" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B996" s="1" t="s">
         <v>2537</v>
@@ -53866,26 +53900,28 @@
         <v>1166</v>
       </c>
       <c r="E996" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F996" s="1" t="s">
         <v>2968</v>
       </c>
       <c r="G996" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H996" s="1"/>
       <c r="I996" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J996" s="1"/>
+      <c r="J996" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="K996" s="1" t="s">
-        <v>2539</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="997" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A997" s="1" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B997" s="1" t="s">
         <v>2537</v>
@@ -53911,12 +53947,12 @@
       </c>
       <c r="J997" s="1"/>
       <c r="K997" s="1" t="s">
-        <v>2540</v>
+        <v>2539</v>
       </c>
     </row>
     <row r="998" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A998" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B998" s="1" t="s">
         <v>2537</v>
@@ -53928,26 +53964,26 @@
         <v>1166</v>
       </c>
       <c r="E998" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F998" s="1" t="s">
         <v>2968</v>
       </c>
       <c r="G998" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H998" s="1"/>
       <c r="I998" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J998" s="1"/>
       <c r="K998" s="1" t="s">
-        <v>2541</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="999" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A999" s="1" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B999" s="1" t="s">
         <v>2537</v>
@@ -53959,26 +53995,28 @@
         <v>1166</v>
       </c>
       <c r="E999" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F999" s="1" t="s">
         <v>2968</v>
       </c>
       <c r="G999" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H999" s="1"/>
       <c r="I999" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J999" s="1"/>
+        <v>3</v>
+      </c>
+      <c r="J999" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="K999" s="1" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
     </row>
     <row r="1000" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1000" s="1" t="s">
-        <v>57</v>
+        <v>723</v>
       </c>
       <c r="B1000" s="1" t="s">
         <v>2537</v>
@@ -53990,21 +54028,23 @@
         <v>1166</v>
       </c>
       <c r="E1000" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1000" s="1" t="s">
-        <v>2970</v>
+        <v>2968</v>
       </c>
       <c r="G1000" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1000" s="1"/>
       <c r="I1000" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="J1000" s="1"/>
+        <v>3</v>
+      </c>
+      <c r="J1000" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="K1000" s="1" t="s">
-        <v>1075</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="1001" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -55370,9 +55410,11 @@
       </c>
       <c r="H1044" s="1"/>
       <c r="I1044" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1044" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="J1044" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="K1044" s="1" t="s">
         <v>2582</v>
       </c>
@@ -55467,9 +55509,11 @@
       </c>
       <c r="H1047" s="1"/>
       <c r="I1047" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1047" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="J1047" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="K1047" s="1" t="s">
         <v>2586</v>
       </c>
@@ -55823,10 +55867,10 @@
     </row>
     <row r="1059" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1059" s="1" t="s">
-        <v>771</v>
+        <v>659</v>
       </c>
       <c r="B1059" s="1" t="s">
-        <v>2609</v>
+        <v>2406</v>
       </c>
       <c r="C1059" s="1" t="s">
         <v>1115</v>
@@ -55849,15 +55893,15 @@
       </c>
       <c r="J1059" s="1"/>
       <c r="K1059" s="1" t="s">
-        <v>2610</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="1060" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1060" s="1" t="s">
-        <v>772</v>
+        <v>660</v>
       </c>
       <c r="B1060" s="1" t="s">
-        <v>2609</v>
+        <v>2406</v>
       </c>
       <c r="C1060" s="1" t="s">
         <v>1115</v>
@@ -55880,7 +55924,7 @@
       </c>
       <c r="J1060" s="1"/>
       <c r="K1060" s="1" t="s">
-        <v>1075</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="1061" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -56943,9 +56987,11 @@
       </c>
       <c r="H1093" s="1"/>
       <c r="I1093" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1093" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="J1093" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K1093" s="1" t="s">
         <v>2647</v>
       </c>
@@ -57317,9 +57363,11 @@
       </c>
       <c r="H1105" s="1"/>
       <c r="I1105" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1105" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="J1105" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="K1105" s="1" t="s">
         <v>1075</v>
       </c>
@@ -57487,10 +57535,10 @@
     </row>
     <row r="1111" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1111" s="1" t="s">
-        <v>974</v>
+        <v>661</v>
       </c>
       <c r="B1111" s="1" t="s">
-        <v>2672</v>
+        <v>2406</v>
       </c>
       <c r="C1111" s="1" t="s">
         <v>1115</v>
@@ -57499,21 +57547,21 @@
         <v>1116</v>
       </c>
       <c r="E1111" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F1111" s="1" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="G1111" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1111" s="1"/>
       <c r="I1111" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J1111" s="1"/>
       <c r="K1111" s="1" t="s">
-        <v>2673</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="1112" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -57666,9 +57714,11 @@
       </c>
       <c r="H1116" s="1"/>
       <c r="I1116" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1116" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="J1116" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="K1116" s="1" t="s">
         <v>2681</v>
       </c>
@@ -57799,10 +57849,10 @@
     </row>
     <row r="1121" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1121" s="1" t="s">
-        <v>816</v>
+        <v>2412</v>
       </c>
       <c r="B1121" s="1" t="s">
-        <v>2683</v>
+        <v>2406</v>
       </c>
       <c r="C1121" s="1" t="s">
         <v>1115</v>
@@ -57811,29 +57861,31 @@
         <v>1116</v>
       </c>
       <c r="E1121" s="1" t="s">
-        <v>2</v>
+        <v>1075</v>
       </c>
       <c r="F1121" s="1" t="s">
-        <v>2968</v>
+        <v>1075</v>
       </c>
       <c r="G1121" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H1121" s="1"/>
+      <c r="H1121" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="I1121" s="1" t="s">
         <v>2</v>
       </c>
       <c r="J1121" s="1"/>
       <c r="K1121" s="1" t="s">
-        <v>2684</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="1122" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1122" s="1" t="s">
-        <v>817</v>
+        <v>2413</v>
       </c>
       <c r="B1122" s="1" t="s">
-        <v>2683</v>
+        <v>2406</v>
       </c>
       <c r="C1122" s="1" t="s">
         <v>1115</v>
@@ -57842,21 +57894,23 @@
         <v>1116</v>
       </c>
       <c r="E1122" s="1" t="s">
-        <v>2</v>
+        <v>1075</v>
       </c>
       <c r="F1122" s="1" t="s">
-        <v>2968</v>
+        <v>1075</v>
       </c>
       <c r="G1122" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H1122" s="1"/>
+      <c r="H1122" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="I1122" s="1" t="s">
         <v>2</v>
       </c>
       <c r="J1122" s="1"/>
       <c r="K1122" s="1" t="s">
-        <v>2685</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="1123" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -57925,10 +57979,10 @@
     </row>
     <row r="1125" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1125" s="1" t="s">
-        <v>819</v>
+        <v>57</v>
       </c>
       <c r="B1125" s="1" t="s">
-        <v>2689</v>
+        <v>2537</v>
       </c>
       <c r="C1125" s="1" t="s">
         <v>1693</v>
@@ -57940,23 +57994,25 @@
         <v>1</v>
       </c>
       <c r="F1125" s="1" t="s">
-        <v>2968</v>
+        <v>2970</v>
       </c>
       <c r="G1125" s="1" t="s">
         <v>1</v>
       </c>
       <c r="H1125" s="1"/>
       <c r="I1125" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="J1125" s="1"/>
+        <v>3</v>
+      </c>
+      <c r="J1125" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="K1125" s="1" t="s">
-        <v>2690</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="1126" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1126" s="1" t="s">
-        <v>820</v>
+        <v>2688</v>
       </c>
       <c r="B1126" s="1" t="s">
         <v>2689</v>
@@ -57968,26 +58024,28 @@
         <v>1166</v>
       </c>
       <c r="E1126" s="1" t="s">
-        <v>3</v>
+        <v>1075</v>
       </c>
       <c r="F1126" s="1" t="s">
-        <v>2968</v>
+        <v>1075</v>
       </c>
       <c r="G1126" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H1126" s="1"/>
+      <c r="H1126" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="I1126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="J1126" s="1"/>
       <c r="K1126" s="1" t="s">
-        <v>2691</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="1127" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1127" s="1" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B1127" s="1" t="s">
         <v>2689</v>
@@ -57999,21 +58057,23 @@
         <v>1166</v>
       </c>
       <c r="E1127" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F1127" s="1" t="s">
         <v>2968</v>
       </c>
       <c r="G1127" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1127" s="1"/>
       <c r="I1127" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J1127" s="1"/>
+      <c r="J1127" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="K1127" s="1" t="s">
-        <v>2692</v>
+        <v>2690</v>
       </c>
     </row>
     <row r="1128" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -58164,9 +58224,11 @@
       </c>
       <c r="H1132" s="1"/>
       <c r="I1132" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1132" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="J1132" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="K1132" s="1" t="s">
         <v>2700</v>
       </c>
@@ -58237,10 +58299,10 @@
     </row>
     <row r="1135" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1135" s="1" t="s">
-        <v>828</v>
+        <v>2415</v>
       </c>
       <c r="B1135" s="1" t="s">
-        <v>2705</v>
+        <v>2406</v>
       </c>
       <c r="C1135" s="1" t="s">
         <v>1115</v>
@@ -58249,21 +58311,23 @@
         <v>1116</v>
       </c>
       <c r="E1135" s="1" t="s">
-        <v>2</v>
+        <v>1075</v>
       </c>
       <c r="F1135" s="1" t="s">
-        <v>2968</v>
+        <v>1075</v>
       </c>
       <c r="G1135" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H1135" s="1"/>
+      <c r="H1135" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="I1135" s="1" t="s">
         <v>2</v>
       </c>
       <c r="J1135" s="1"/>
       <c r="K1135" s="1" t="s">
-        <v>1075</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="1136" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -58334,10 +58398,10 @@
     </row>
     <row r="1138" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1138" s="1" t="s">
-        <v>1329</v>
+        <v>662</v>
       </c>
       <c r="B1138" s="1" t="s">
-        <v>1330</v>
+        <v>2406</v>
       </c>
       <c r="C1138" s="1" t="s">
         <v>1115</v>
@@ -58346,23 +58410,21 @@
         <v>1116</v>
       </c>
       <c r="E1138" s="1" t="s">
-        <v>1075</v>
+        <v>2</v>
       </c>
       <c r="F1138" s="1" t="s">
-        <v>1075</v>
+        <v>2968</v>
       </c>
       <c r="G1138" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H1138" s="1" t="s">
-        <v>2976</v>
-      </c>
+      <c r="H1138" s="1"/>
       <c r="I1138" s="1" t="s">
         <v>2</v>
       </c>
       <c r="J1138" s="1"/>
       <c r="K1138" s="1" t="s">
-        <v>1331</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="1139" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -58648,10 +58710,10 @@
     </row>
     <row r="1148" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1148" s="1" t="s">
-        <v>1804</v>
+        <v>771</v>
       </c>
       <c r="B1148" s="1" t="s">
-        <v>1805</v>
+        <v>2609</v>
       </c>
       <c r="C1148" s="1" t="s">
         <v>1115</v>
@@ -58660,23 +58722,21 @@
         <v>1116</v>
       </c>
       <c r="E1148" s="1" t="s">
-        <v>1075</v>
+        <v>2</v>
       </c>
       <c r="F1148" s="1" t="s">
-        <v>1075</v>
+        <v>2968</v>
       </c>
       <c r="G1148" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H1148" s="1" t="s">
-        <v>2976</v>
-      </c>
+      <c r="H1148" s="1"/>
       <c r="I1148" s="1" t="s">
         <v>2</v>
       </c>
       <c r="J1148" s="1"/>
       <c r="K1148" s="1" t="s">
-        <v>1075</v>
+        <v>2610</v>
       </c>
     </row>
     <row r="1149" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -58712,10 +58772,10 @@
     </row>
     <row r="1150" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1150" s="1" t="s">
-        <v>2002</v>
+        <v>772</v>
       </c>
       <c r="B1150" s="1" t="s">
-        <v>2003</v>
+        <v>2609</v>
       </c>
       <c r="C1150" s="1" t="s">
         <v>1115</v>
@@ -58724,23 +58784,21 @@
         <v>1116</v>
       </c>
       <c r="E1150" s="1" t="s">
-        <v>1075</v>
+        <v>2</v>
       </c>
       <c r="F1150" s="1" t="s">
-        <v>1075</v>
+        <v>2968</v>
       </c>
       <c r="G1150" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H1150" s="1" t="s">
-        <v>2976</v>
-      </c>
+      <c r="H1150" s="1"/>
       <c r="I1150" s="1" t="s">
         <v>2</v>
       </c>
       <c r="J1150" s="1"/>
       <c r="K1150" s="1" t="s">
-        <v>2004</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="1151" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -58838,10 +58896,10 @@
     </row>
     <row r="1154" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1154" s="1" t="s">
-        <v>2070</v>
+        <v>974</v>
       </c>
       <c r="B1154" s="1" t="s">
-        <v>2071</v>
+        <v>2672</v>
       </c>
       <c r="C1154" s="1" t="s">
         <v>1115</v>
@@ -58850,31 +58908,31 @@
         <v>1116</v>
       </c>
       <c r="E1154" s="1" t="s">
-        <v>1075</v>
+        <v>3</v>
       </c>
       <c r="F1154" s="1" t="s">
-        <v>1075</v>
+        <v>2969</v>
       </c>
       <c r="G1154" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1154" s="1" t="s">
-        <v>2976</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="H1154" s="1"/>
       <c r="I1154" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J1154" s="1"/>
+      <c r="J1154" s="1" t="s">
+        <v>2975</v>
+      </c>
       <c r="K1154" s="1" t="s">
-        <v>2072</v>
+        <v>2673</v>
       </c>
     </row>
     <row r="1155" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1155" s="1" t="s">
-        <v>841</v>
+        <v>816</v>
       </c>
       <c r="B1155" s="1" t="s">
-        <v>2743</v>
+        <v>2683</v>
       </c>
       <c r="C1155" s="1" t="s">
         <v>1115</v>
@@ -58897,15 +58955,15 @@
       </c>
       <c r="J1155" s="1"/>
       <c r="K1155" s="1" t="s">
-        <v>2744</v>
+        <v>2684</v>
       </c>
     </row>
     <row r="1156" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1156" s="1" t="s">
-        <v>2412</v>
+        <v>817</v>
       </c>
       <c r="B1156" s="1" t="s">
-        <v>2406</v>
+        <v>2683</v>
       </c>
       <c r="C1156" s="1" t="s">
         <v>1115</v>
@@ -58914,31 +58972,29 @@
         <v>1116</v>
       </c>
       <c r="E1156" s="1" t="s">
-        <v>1075</v>
+        <v>2</v>
       </c>
       <c r="F1156" s="1" t="s">
-        <v>1075</v>
+        <v>2968</v>
       </c>
       <c r="G1156" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H1156" s="1" t="s">
-        <v>2976</v>
-      </c>
+      <c r="H1156" s="1"/>
       <c r="I1156" s="1" t="s">
         <v>2</v>
       </c>
       <c r="J1156" s="1"/>
       <c r="K1156" s="1" t="s">
-        <v>1075</v>
+        <v>2685</v>
       </c>
     </row>
     <row r="1157" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1157" s="1" t="s">
-        <v>2413</v>
+        <v>828</v>
       </c>
       <c r="B1157" s="1" t="s">
-        <v>2406</v>
+        <v>2705</v>
       </c>
       <c r="C1157" s="1" t="s">
         <v>1115</v>
@@ -58947,31 +59003,29 @@
         <v>1116</v>
       </c>
       <c r="E1157" s="1" t="s">
-        <v>1075</v>
+        <v>2</v>
       </c>
       <c r="F1157" s="1" t="s">
-        <v>1075</v>
+        <v>2968</v>
       </c>
       <c r="G1157" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H1157" s="1" t="s">
-        <v>2976</v>
-      </c>
+      <c r="H1157" s="1"/>
       <c r="I1157" s="1" t="s">
         <v>2</v>
       </c>
       <c r="J1157" s="1"/>
       <c r="K1157" s="1" t="s">
-        <v>2414</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="1158" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1158" s="1" t="s">
-        <v>2415</v>
+        <v>841</v>
       </c>
       <c r="B1158" s="1" t="s">
-        <v>2406</v>
+        <v>2743</v>
       </c>
       <c r="C1158" s="1" t="s">
         <v>1115</v>
@@ -58980,23 +59034,21 @@
         <v>1116</v>
       </c>
       <c r="E1158" s="1" t="s">
-        <v>1075</v>
+        <v>2</v>
       </c>
       <c r="F1158" s="1" t="s">
-        <v>1075</v>
+        <v>2968</v>
       </c>
       <c r="G1158" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H1158" s="1" t="s">
-        <v>2976</v>
-      </c>
+      <c r="H1158" s="1"/>
       <c r="I1158" s="1" t="s">
         <v>2</v>
       </c>
       <c r="J1158" s="1"/>
       <c r="K1158" s="1" t="s">
-        <v>2416</v>
+        <v>2744</v>
       </c>
     </row>
     <row r="1159" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -59348,10 +59400,10 @@
     </row>
     <row r="1170" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1170" s="1" t="s">
-        <v>1691</v>
+        <v>820</v>
       </c>
       <c r="B1170" s="1" t="s">
-        <v>1692</v>
+        <v>2689</v>
       </c>
       <c r="C1170" s="1" t="s">
         <v>1693</v>
@@ -59360,23 +59412,21 @@
         <v>1166</v>
       </c>
       <c r="E1170" s="1" t="s">
-        <v>1075</v>
+        <v>3</v>
       </c>
       <c r="F1170" s="1" t="s">
-        <v>1075</v>
+        <v>2968</v>
       </c>
       <c r="G1170" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1170" s="1" t="s">
-        <v>2976</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="H1170" s="1"/>
       <c r="I1170" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J1170" s="1"/>
       <c r="K1170" s="1" t="s">
-        <v>1694</v>
+        <v>2691</v>
       </c>
     </row>
     <row r="1171" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -59660,7 +59710,7 @@
     </row>
     <row r="1180" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1180" s="1" t="s">
-        <v>2688</v>
+        <v>821</v>
       </c>
       <c r="B1180" s="1" t="s">
         <v>2689</v>
@@ -59672,23 +59722,21 @@
         <v>1166</v>
       </c>
       <c r="E1180" s="1" t="s">
-        <v>1075</v>
+        <v>3</v>
       </c>
       <c r="F1180" s="1" t="s">
-        <v>1075</v>
+        <v>2968</v>
       </c>
       <c r="G1180" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H1180" s="1" t="s">
-        <v>2975</v>
-      </c>
+      <c r="H1180" s="1"/>
       <c r="I1180" s="1" t="s">
         <v>3</v>
       </c>
       <c r="J1180" s="1"/>
       <c r="K1180" s="1" t="s">
-        <v>1075</v>
+        <v>2692</v>
       </c>
     </row>
     <row r="1181" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -62227,9 +62275,11 @@
       </c>
       <c r="H1261" s="1"/>
       <c r="I1261" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1261" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="J1261" s="1" t="s">
+        <v>2976</v>
+      </c>
       <c r="K1261" s="1" t="s">
         <v>1075</v>
       </c>

--- a/data/chapter2/FRED/subsets/species.xlsx
+++ b/data/chapter2/FRED/subsets/species.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://westernsydneyedu-my.sharepoint.com/personal/90963425_westernsydney_edu_au/Documents/PhD/code/data/chapter2/FRED/subsets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="897" documentId="8_{81FDA0CF-33C4-43D2-B8CA-CC5F96143B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A3B0F71-CA45-45D3-8B2E-0D866692243A}"/>
+  <xr:revisionPtr revIDLastSave="900" documentId="8_{81FDA0CF-33C4-43D2-B8CA-CC5F96143B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B8F9DD8-A2C8-4380-9759-3BE4458004B3}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="426" firstSheet="1" activeTab="3" xr2:uid="{A5444074-DC77-415C-A9E2-2BBA8270EAFC}"/>
   </bookViews>
@@ -22418,8 +22418,8 @@
     <col min="1" max="1" width="31" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.6328125" customWidth="1"/>
+    <col min="5" max="5" width="15.453125" customWidth="1"/>
     <col min="6" max="6" width="17.26953125" customWidth="1"/>
     <col min="7" max="7" width="17.7265625" customWidth="1"/>
     <col min="8" max="8" width="26.1796875" bestFit="1" customWidth="1"/>
